--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -16,20 +16,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -48,22 +47,14 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,116 +420,116 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V572"/>
+  <dimension ref="A1:V573"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>CÓDIGO_INSTITUCIÓN</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>NOMBRE_INSTITUCIÓN</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>SECTOR</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO_OFERTA_PROGRAMA</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>MUNICIPIO_OFERTA_PROGRAMA</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>CÓDIGO_SNIES_DEL_PROGRAMA</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>NOMBRE_DEL_PROGRAMA</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MODALIDAD</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>NÚMERO_CRÉDITOS</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>NÚMERO_PERIODOS_DE_DURACIÓN</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>PERIODICIDAD</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>COSTO_MATRÍCULA_ESTUD_NUEVOS</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>PERIODICIDAD_ADMISIONES</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>FECHA_DE_REGISTRO_EN_SNIES</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_AMPLIO</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_ESPECÍFIC</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>CINE_F_2013_AC_CAMPO_DETALLADO</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>NÚCLEO_BÁSICO_DEL_CONOCIMIENTO</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>PROGINSTI</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>FECHA_OBTENCION</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>DIVISIÓN UNINORTE</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Estado</t>
         </is>
@@ -598,7 +589,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N2" s="2" t="n">
+      <c r="N2" s="1" t="n">
         <v>45496</v>
       </c>
       <c r="O2" t="inlineStr">
@@ -696,7 +687,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N3" s="2" t="n">
+      <c r="N3" s="1" t="n">
         <v>45392</v>
       </c>
       <c r="O3" t="inlineStr">
@@ -794,7 +785,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N4" s="2" t="n">
+      <c r="N4" s="1" t="n">
         <v>45392</v>
       </c>
       <c r="O4" t="inlineStr">
@@ -892,7 +883,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N5" s="2" t="n">
+      <c r="N5" s="1" t="n">
         <v>45461</v>
       </c>
       <c r="O5" t="inlineStr">
@@ -990,7 +981,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N6" s="2" t="n">
+      <c r="N6" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="O6" t="inlineStr">
@@ -1088,7 +1079,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N7" s="2" t="n">
+      <c r="N7" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="O7" t="inlineStr">
@@ -1186,7 +1177,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N8" s="2" t="n">
+      <c r="N8" s="1" t="n">
         <v>45247</v>
       </c>
       <c r="O8" t="inlineStr">
@@ -1284,7 +1275,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N9" s="2" t="n">
+      <c r="N9" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="O9" t="inlineStr">
@@ -1382,7 +1373,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N10" s="2" t="n">
+      <c r="N10" s="1" t="n">
         <v>45343</v>
       </c>
       <c r="O10" t="inlineStr">
@@ -1480,7 +1471,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N11" s="2" t="n">
+      <c r="N11" s="1" t="n">
         <v>45496</v>
       </c>
       <c r="O11" t="inlineStr">
@@ -1578,7 +1569,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N12" s="2" t="n">
+      <c r="N12" s="1" t="n">
         <v>45469</v>
       </c>
       <c r="O12" t="inlineStr">
@@ -1676,7 +1667,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N13" s="2" t="n">
+      <c r="N13" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="O13" t="inlineStr">
@@ -1774,7 +1765,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N14" s="2" t="n">
+      <c r="N14" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="O14" t="inlineStr">
@@ -1872,7 +1863,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N15" s="2" t="n">
+      <c r="N15" s="1" t="n">
         <v>45260</v>
       </c>
       <c r="O15" t="inlineStr">
@@ -1970,7 +1961,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N16" s="2" t="n">
+      <c r="N16" s="1" t="n">
         <v>45462</v>
       </c>
       <c r="O16" t="inlineStr">
@@ -2068,7 +2059,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N17" s="2" t="n">
+      <c r="N17" s="1" t="n">
         <v>45428</v>
       </c>
       <c r="O17" t="inlineStr">
@@ -2166,7 +2157,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N18" s="2" t="n">
+      <c r="N18" s="1" t="n">
         <v>45462</v>
       </c>
       <c r="O18" t="inlineStr">
@@ -2264,7 +2255,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N19" s="2" t="n">
+      <c r="N19" s="1" t="n">
         <v>45462</v>
       </c>
       <c r="O19" t="inlineStr">
@@ -2362,7 +2353,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N20" s="2" t="n">
+      <c r="N20" s="1" t="n">
         <v>45287</v>
       </c>
       <c r="O20" t="inlineStr">
@@ -2460,7 +2451,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N21" s="2" t="n">
+      <c r="N21" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="O21" t="inlineStr">
@@ -2558,7 +2549,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N22" s="2" t="n">
+      <c r="N22" s="1" t="n">
         <v>45484</v>
       </c>
       <c r="O22" t="inlineStr">
@@ -2656,7 +2647,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="N23" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="O23" t="inlineStr">
@@ -2754,7 +2745,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="N24" s="1" t="n">
         <v>45393</v>
       </c>
       <c r="O24" t="inlineStr">
@@ -2852,7 +2843,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="N25" s="1" t="n">
         <v>45489</v>
       </c>
       <c r="O25" t="inlineStr">
@@ -2950,7 +2941,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="N26" s="1" t="n">
         <v>45155</v>
       </c>
       <c r="O26" t="inlineStr">
@@ -3048,7 +3039,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N27" s="2" t="n">
+      <c r="N27" s="1" t="n">
         <v>45407</v>
       </c>
       <c r="O27" t="inlineStr">
@@ -3146,7 +3137,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N28" s="2" t="n">
+      <c r="N28" s="1" t="n">
         <v>45155</v>
       </c>
       <c r="O28" t="inlineStr">
@@ -3244,7 +3235,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="N29" s="1" t="n">
         <v>45419</v>
       </c>
       <c r="O29" t="inlineStr">
@@ -3342,7 +3333,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N30" s="2" t="n">
+      <c r="N30" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="O30" t="inlineStr">
@@ -3440,7 +3431,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N31" s="2" t="n">
+      <c r="N31" s="1" t="n">
         <v>45414</v>
       </c>
       <c r="O31" t="inlineStr">
@@ -3538,7 +3529,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="N32" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="O32" t="inlineStr">
@@ -3636,7 +3627,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N33" s="2" t="n">
+      <c r="N33" s="1" t="n">
         <v>45457</v>
       </c>
       <c r="O33" t="inlineStr">
@@ -3736,7 +3727,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N34" s="2" t="n">
+      <c r="N34" s="1" t="n">
         <v>44405</v>
       </c>
       <c r="O34" t="inlineStr">
@@ -3834,7 +3825,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N35" s="2" t="n">
+      <c r="N35" s="1" t="n">
         <v>45400</v>
       </c>
       <c r="O35" t="inlineStr">
@@ -3932,7 +3923,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N36" s="2" t="n">
+      <c r="N36" s="1" t="n">
         <v>45393</v>
       </c>
       <c r="O36" t="inlineStr">
@@ -4030,7 +4021,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N37" s="2" t="n">
+      <c r="N37" s="1" t="n">
         <v>45393</v>
       </c>
       <c r="O37" t="inlineStr">
@@ -4128,7 +4119,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N38" s="2" t="n">
+      <c r="N38" s="1" t="n">
         <v>45138</v>
       </c>
       <c r="O38" t="inlineStr">
@@ -4226,7 +4217,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N39" s="2" t="n">
+      <c r="N39" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="O39" t="inlineStr">
@@ -4324,7 +4315,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N40" s="2" t="n">
+      <c r="N40" s="1" t="n">
         <v>45274</v>
       </c>
       <c r="O40" t="inlineStr">
@@ -4422,7 +4413,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N41" s="2" t="n">
+      <c r="N41" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="O41" t="inlineStr">
@@ -4520,7 +4511,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N42" s="2" t="n">
+      <c r="N42" s="1" t="n">
         <v>45393</v>
       </c>
       <c r="O42" t="inlineStr">
@@ -4618,7 +4609,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N43" s="2" t="n">
+      <c r="N43" s="1" t="n">
         <v>45393</v>
       </c>
       <c r="O43" t="inlineStr">
@@ -4716,7 +4707,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N44" s="2" t="n">
+      <c r="N44" s="1" t="n">
         <v>45286</v>
       </c>
       <c r="O44" t="inlineStr">
@@ -4814,7 +4805,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N45" s="2" t="n">
+      <c r="N45" s="1" t="n">
         <v>43153</v>
       </c>
       <c r="O45" t="inlineStr">
@@ -4912,7 +4903,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N46" s="2" t="n">
+      <c r="N46" s="1" t="n">
         <v>45282</v>
       </c>
       <c r="O46" t="inlineStr">
@@ -5010,7 +5001,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N47" s="2" t="n">
+      <c r="N47" s="1" t="n">
         <v>43895</v>
       </c>
       <c r="O47" t="inlineStr">
@@ -5108,7 +5099,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N48" s="2" t="n">
+      <c r="N48" s="1" t="n">
         <v>45278</v>
       </c>
       <c r="O48" t="inlineStr">
@@ -5206,7 +5197,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N49" s="2" t="n">
+      <c r="N49" s="1" t="n">
         <v>44658</v>
       </c>
       <c r="O49" t="inlineStr">
@@ -5304,7 +5295,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N50" s="2" t="n">
+      <c r="N50" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="O50" t="inlineStr">
@@ -5402,7 +5393,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N51" s="2" t="n">
+      <c r="N51" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="O51" t="inlineStr">
@@ -5500,7 +5491,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N52" s="2" t="n">
+      <c r="N52" s="1" t="n">
         <v>44153</v>
       </c>
       <c r="O52" t="inlineStr">
@@ -5598,7 +5589,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N53" s="2" t="n">
+      <c r="N53" s="1" t="n">
         <v>44153</v>
       </c>
       <c r="O53" t="inlineStr">
@@ -5696,7 +5687,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N54" s="2" t="n">
+      <c r="N54" s="1" t="n">
         <v>45266</v>
       </c>
       <c r="O54" t="inlineStr">
@@ -5794,7 +5785,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N55" s="2" t="n">
+      <c r="N55" s="1" t="n">
         <v>45254</v>
       </c>
       <c r="O55" t="inlineStr">
@@ -5892,7 +5883,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N56" s="2" t="n">
+      <c r="N56" s="1" t="n">
         <v>45449</v>
       </c>
       <c r="O56" t="inlineStr">
@@ -5990,7 +5981,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N57" s="2" t="n">
+      <c r="N57" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="O57" t="inlineStr">
@@ -6088,7 +6079,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N58" s="2" t="n">
+      <c r="N58" s="1" t="n">
         <v>42586</v>
       </c>
       <c r="O58" t="inlineStr">
@@ -6186,7 +6177,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N59" s="2" t="n">
+      <c r="N59" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="O59" t="inlineStr">
@@ -6284,7 +6275,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N60" s="2" t="n">
+      <c r="N60" s="1" t="n">
         <v>45489</v>
       </c>
       <c r="O60" t="inlineStr">
@@ -6382,7 +6373,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N61" s="2" t="n">
+      <c r="N61" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="O61" t="inlineStr">
@@ -6480,7 +6471,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N62" s="2" t="n">
+      <c r="N62" s="1" t="n">
         <v>45323</v>
       </c>
       <c r="O62" t="inlineStr">
@@ -6578,7 +6569,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N63" s="2" t="n">
+      <c r="N63" s="1" t="n">
         <v>43776</v>
       </c>
       <c r="O63" t="inlineStr">
@@ -6676,7 +6667,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N64" s="2" t="n">
+      <c r="N64" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O64" t="inlineStr">
@@ -6774,7 +6765,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N65" s="2" t="n">
+      <c r="N65" s="1" t="n">
         <v>43776</v>
       </c>
       <c r="O65" t="inlineStr">
@@ -6872,7 +6863,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N66" s="2" t="n">
+      <c r="N66" s="1" t="n">
         <v>45211</v>
       </c>
       <c r="O66" t="inlineStr">
@@ -6970,7 +6961,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N67" s="2" t="n">
+      <c r="N67" s="1" t="n">
         <v>45211</v>
       </c>
       <c r="O67" t="inlineStr">
@@ -7068,7 +7059,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N68" s="2" t="n">
+      <c r="N68" s="1" t="n">
         <v>43495</v>
       </c>
       <c r="O68" t="inlineStr">
@@ -7166,7 +7157,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N69" s="2" t="n">
+      <c r="N69" s="1" t="n">
         <v>43292</v>
       </c>
       <c r="O69" t="inlineStr">
@@ -7264,7 +7255,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N70" s="2" t="n">
+      <c r="N70" s="1" t="n">
         <v>45272</v>
       </c>
       <c r="O70" t="inlineStr">
@@ -7362,7 +7353,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N71" s="2" t="n">
+      <c r="N71" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="O71" t="inlineStr">
@@ -7460,7 +7451,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N72" s="2" t="n">
+      <c r="N72" s="1" t="n">
         <v>44986</v>
       </c>
       <c r="O72" t="inlineStr">
@@ -7558,7 +7549,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N73" s="2" t="n">
+      <c r="N73" s="1" t="n">
         <v>45189</v>
       </c>
       <c r="O73" t="inlineStr">
@@ -7656,7 +7647,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N74" s="2" t="n">
+      <c r="N74" s="1" t="n">
         <v>45117</v>
       </c>
       <c r="O74" t="inlineStr">
@@ -7754,7 +7745,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N75" s="2" t="n">
+      <c r="N75" s="1" t="n">
         <v>45461</v>
       </c>
       <c r="O75" t="inlineStr">
@@ -7852,7 +7843,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N76" s="2" t="n">
+      <c r="N76" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="O76" t="inlineStr">
@@ -7950,7 +7941,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N77" s="2" t="n">
+      <c r="N77" s="1" t="n">
         <v>45272</v>
       </c>
       <c r="O77" t="inlineStr">
@@ -8048,7 +8039,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N78" s="2" t="n">
+      <c r="N78" s="1" t="n">
         <v>44705</v>
       </c>
       <c r="O78" t="inlineStr">
@@ -8146,7 +8137,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N79" s="2" t="n">
+      <c r="N79" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="O79" t="inlineStr">
@@ -8244,7 +8235,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N80" s="2" t="n">
+      <c r="N80" s="1" t="n">
         <v>45272</v>
       </c>
       <c r="O80" t="inlineStr">
@@ -8344,7 +8335,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N81" s="2" t="n">
+      <c r="N81" s="1" t="n">
         <v>45463</v>
       </c>
       <c r="O81" t="inlineStr">
@@ -8442,7 +8433,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N82" s="2" t="n">
+      <c r="N82" s="1" t="n">
         <v>45267</v>
       </c>
       <c r="O82" t="inlineStr">
@@ -8540,7 +8531,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N83" s="2" t="n">
+      <c r="N83" s="1" t="n">
         <v>45369</v>
       </c>
       <c r="O83" t="inlineStr">
@@ -8638,7 +8629,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N84" s="2" t="n">
+      <c r="N84" s="1" t="n">
         <v>45267</v>
       </c>
       <c r="O84" t="inlineStr">
@@ -8736,7 +8727,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N85" s="2" t="n">
+      <c r="N85" s="1" t="n">
         <v>45369</v>
       </c>
       <c r="O85" t="inlineStr">
@@ -8834,7 +8825,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N86" s="2" t="n">
+      <c r="N86" s="1" t="n">
         <v>45370</v>
       </c>
       <c r="O86" t="inlineStr">
@@ -8932,7 +8923,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N87" s="2" t="n">
+      <c r="N87" s="1" t="n">
         <v>45362</v>
       </c>
       <c r="O87" t="inlineStr">
@@ -9030,7 +9021,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N88" s="2" t="n">
+      <c r="N88" s="1" t="n">
         <v>45477</v>
       </c>
       <c r="O88" t="inlineStr">
@@ -9128,7 +9119,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N89" s="2" t="n">
+      <c r="N89" s="1" t="n">
         <v>44153</v>
       </c>
       <c r="O89" t="inlineStr">
@@ -9226,7 +9217,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N90" s="2" t="n">
+      <c r="N90" s="1" t="n">
         <v>45477</v>
       </c>
       <c r="O90" t="inlineStr">
@@ -9324,7 +9315,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N91" s="2" t="n">
+      <c r="N91" s="1" t="n">
         <v>45477</v>
       </c>
       <c r="O91" t="inlineStr">
@@ -9422,7 +9413,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N92" s="2" t="n">
+      <c r="N92" s="1" t="n">
         <v>45477</v>
       </c>
       <c r="O92" t="inlineStr">
@@ -9520,7 +9511,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N93" s="2" t="n">
+      <c r="N93" s="1" t="n">
         <v>44789</v>
       </c>
       <c r="O93" t="inlineStr">
@@ -9618,7 +9609,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N94" s="2" t="n">
+      <c r="N94" s="1" t="n">
         <v>43593</v>
       </c>
       <c r="O94" t="inlineStr">
@@ -9716,7 +9707,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N95" s="2" t="n">
+      <c r="N95" s="1" t="n">
         <v>45414</v>
       </c>
       <c r="O95" t="inlineStr">
@@ -9814,7 +9805,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N96" s="2" t="n">
+      <c r="N96" s="1" t="n">
         <v>45362</v>
       </c>
       <c r="O96" t="inlineStr">
@@ -9912,7 +9903,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N97" s="2" t="n">
+      <c r="N97" s="1" t="n">
         <v>45392</v>
       </c>
       <c r="O97" t="inlineStr">
@@ -10010,7 +10001,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N98" s="2" t="n">
+      <c r="N98" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="O98" t="inlineStr">
@@ -10108,7 +10099,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N99" s="2" t="n">
+      <c r="N99" s="1" t="n">
         <v>45301</v>
       </c>
       <c r="O99" t="inlineStr">
@@ -10206,7 +10197,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N100" s="2" t="n">
+      <c r="N100" s="1" t="n">
         <v>43237</v>
       </c>
       <c r="O100" t="inlineStr">
@@ -10306,7 +10297,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N101" s="2" t="n">
+      <c r="N101" s="1" t="n">
         <v>43251</v>
       </c>
       <c r="O101" t="inlineStr">
@@ -10404,7 +10395,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N102" s="2" t="n">
+      <c r="N102" s="1" t="n">
         <v>43251</v>
       </c>
       <c r="O102" t="inlineStr">
@@ -10502,7 +10493,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N103" s="2" t="n">
+      <c r="N103" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="O103" t="inlineStr">
@@ -10600,7 +10591,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N104" s="2" t="n">
+      <c r="N104" s="1" t="n">
         <v>45497</v>
       </c>
       <c r="O104" t="inlineStr">
@@ -10698,7 +10689,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N105" s="2" t="n">
+      <c r="N105" s="1" t="n">
         <v>45489</v>
       </c>
       <c r="O105" t="inlineStr">
@@ -10796,7 +10787,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N106" s="2" t="n">
+      <c r="N106" s="1" t="n">
         <v>45468</v>
       </c>
       <c r="O106" t="inlineStr">
@@ -10894,7 +10885,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N107" s="2" t="n">
+      <c r="N107" s="1" t="n">
         <v>45293</v>
       </c>
       <c r="O107" t="inlineStr">
@@ -10992,7 +10983,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N108" s="2" t="n">
+      <c r="N108" s="1" t="n">
         <v>45316</v>
       </c>
       <c r="O108" t="inlineStr">
@@ -11090,7 +11081,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N109" s="2" t="n">
+      <c r="N109" s="1" t="n">
         <v>45468</v>
       </c>
       <c r="O109" t="inlineStr">
@@ -11188,7 +11179,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N110" s="2" t="n">
+      <c r="N110" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="O110" t="inlineStr">
@@ -11286,7 +11277,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N111" s="2" t="n">
+      <c r="N111" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="O111" t="inlineStr">
@@ -11384,7 +11375,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N112" s="2" t="n">
+      <c r="N112" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="O112" t="inlineStr">
@@ -11482,7 +11473,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N113" s="2" t="n">
+      <c r="N113" s="1" t="n">
         <v>45362</v>
       </c>
       <c r="O113" t="inlineStr">
@@ -11580,7 +11571,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N114" s="2" t="n">
+      <c r="N114" s="1" t="n">
         <v>45272</v>
       </c>
       <c r="O114" t="inlineStr">
@@ -11678,7 +11669,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N115" s="2" t="n">
+      <c r="N115" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="O115" t="inlineStr">
@@ -11776,7 +11767,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N116" s="2" t="n">
+      <c r="N116" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="O116" t="inlineStr">
@@ -11874,7 +11865,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N117" s="2" t="n">
+      <c r="N117" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="O117" t="inlineStr">
@@ -11972,7 +11963,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N118" s="2" t="n">
+      <c r="N118" s="1" t="n">
         <v>45392</v>
       </c>
       <c r="O118" t="inlineStr">
@@ -12070,7 +12061,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N119" s="2" t="n">
+      <c r="N119" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="O119" t="inlineStr">
@@ -12168,7 +12159,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N120" s="2" t="n">
+      <c r="N120" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="O120" t="inlineStr">
@@ -12266,7 +12257,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N121" s="2" t="n">
+      <c r="N121" s="1" t="n">
         <v>45489</v>
       </c>
       <c r="O121" t="inlineStr">
@@ -12364,7 +12355,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N122" s="2" t="n">
+      <c r="N122" s="1" t="n">
         <v>45476</v>
       </c>
       <c r="O122" t="inlineStr">
@@ -12462,7 +12453,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N123" s="2" t="n">
+      <c r="N123" s="1" t="n">
         <v>45484</v>
       </c>
       <c r="O123" t="inlineStr">
@@ -12560,7 +12551,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N124" s="2" t="n">
+      <c r="N124" s="1" t="n">
         <v>45397</v>
       </c>
       <c r="O124" t="inlineStr">
@@ -12658,7 +12649,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N125" s="2" t="n">
+      <c r="N125" s="1" t="n">
         <v>45317</v>
       </c>
       <c r="O125" t="inlineStr">
@@ -12756,7 +12747,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N126" s="2" t="n">
+      <c r="N126" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="O126" t="inlineStr">
@@ -12854,7 +12845,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N127" s="2" t="n">
+      <c r="N127" s="1" t="n">
         <v>45483</v>
       </c>
       <c r="O127" t="inlineStr">
@@ -12952,7 +12943,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N128" s="2" t="n">
+      <c r="N128" s="1" t="n">
         <v>45483</v>
       </c>
       <c r="O128" t="inlineStr">
@@ -13050,7 +13041,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N129" s="2" t="n">
+      <c r="N129" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="O129" t="inlineStr">
@@ -13150,7 +13141,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N130" s="2" t="n">
+      <c r="N130" s="1" t="n">
         <v>45369</v>
       </c>
       <c r="O130" t="inlineStr">
@@ -13248,7 +13239,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N131" s="2" t="n">
+      <c r="N131" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="O131" t="inlineStr">
@@ -13346,7 +13337,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N132" s="2" t="n">
+      <c r="N132" s="1" t="n">
         <v>45464</v>
       </c>
       <c r="O132" t="inlineStr">
@@ -13444,7 +13435,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N133" s="2" t="n">
+      <c r="N133" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="O133" t="inlineStr">
@@ -13542,7 +13533,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N134" s="2" t="n">
+      <c r="N134" s="1" t="n">
         <v>45308</v>
       </c>
       <c r="O134" t="inlineStr">
@@ -13640,7 +13631,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N135" s="2" t="n">
+      <c r="N135" s="1" t="n">
         <v>45117</v>
       </c>
       <c r="O135" t="inlineStr">
@@ -13738,7 +13729,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N136" s="2" t="n">
+      <c r="N136" s="1" t="n">
         <v>45320</v>
       </c>
       <c r="O136" t="inlineStr">
@@ -13836,7 +13827,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N137" s="2" t="n">
+      <c r="N137" s="1" t="n">
         <v>43826</v>
       </c>
       <c r="O137" t="inlineStr">
@@ -13934,7 +13925,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N138" s="2" t="n">
+      <c r="N138" s="1" t="n">
         <v>45435</v>
       </c>
       <c r="O138" t="inlineStr">
@@ -14032,7 +14023,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N139" s="2" t="n">
+      <c r="N139" s="1" t="n">
         <v>45133</v>
       </c>
       <c r="O139" t="inlineStr">
@@ -14130,7 +14121,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N140" s="2" t="n">
+      <c r="N140" s="1" t="n">
         <v>44432</v>
       </c>
       <c r="O140" t="inlineStr">
@@ -14228,7 +14219,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N141" s="2" t="n">
+      <c r="N141" s="1" t="n">
         <v>44094</v>
       </c>
       <c r="O141" t="inlineStr">
@@ -14326,7 +14317,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N142" s="2" t="n">
+      <c r="N142" s="1" t="n">
         <v>45393</v>
       </c>
       <c r="O142" t="inlineStr">
@@ -14424,7 +14415,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N143" s="2" t="n">
+      <c r="N143" s="1" t="n">
         <v>45432</v>
       </c>
       <c r="O143" t="inlineStr">
@@ -14522,7 +14513,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N144" s="2" t="n">
+      <c r="N144" s="1" t="n">
         <v>45334</v>
       </c>
       <c r="O144" t="inlineStr">
@@ -14620,7 +14611,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N145" s="2" t="n">
+      <c r="N145" s="1" t="n">
         <v>45342</v>
       </c>
       <c r="O145" t="inlineStr">
@@ -14718,7 +14709,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N146" s="2" t="n">
+      <c r="N146" s="1" t="n">
         <v>45432</v>
       </c>
       <c r="O146" t="inlineStr">
@@ -14816,7 +14807,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N147" s="2" t="n">
+      <c r="N147" s="1" t="n">
         <v>45411</v>
       </c>
       <c r="O147" t="inlineStr">
@@ -14914,7 +14905,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N148" s="2" t="n">
+      <c r="N148" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="O148" t="inlineStr">
@@ -15012,7 +15003,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N149" s="2" t="n">
+      <c r="N149" s="1" t="n">
         <v>45404</v>
       </c>
       <c r="O149" t="inlineStr">
@@ -15110,7 +15101,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N150" s="2" t="n">
+      <c r="N150" s="1" t="n">
         <v>45301</v>
       </c>
       <c r="O150" t="inlineStr">
@@ -15208,7 +15199,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N151" s="2" t="n">
+      <c r="N151" s="1" t="n">
         <v>45428</v>
       </c>
       <c r="O151" t="inlineStr">
@@ -15306,7 +15297,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N152" s="2" t="n">
+      <c r="N152" s="1" t="n">
         <v>45432</v>
       </c>
       <c r="O152" t="inlineStr">
@@ -15404,7 +15395,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N153" s="2" t="n">
+      <c r="N153" s="1" t="n">
         <v>45411</v>
       </c>
       <c r="O153" t="inlineStr">
@@ -15502,7 +15493,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N154" s="2" t="n">
+      <c r="N154" s="1" t="n">
         <v>45477</v>
       </c>
       <c r="O154" t="inlineStr">
@@ -15600,7 +15591,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N155" s="2" t="n">
+      <c r="N155" s="1" t="n">
         <v>45482</v>
       </c>
       <c r="O155" t="inlineStr">
@@ -15698,7 +15689,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N156" s="2" t="n">
+      <c r="N156" s="1" t="n">
         <v>45477</v>
       </c>
       <c r="O156" t="inlineStr">
@@ -15796,7 +15787,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N157" s="2" t="n">
+      <c r="N157" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="O157" t="inlineStr">
@@ -15894,7 +15885,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N158" s="2" t="n">
+      <c r="N158" s="1" t="n">
         <v>45414</v>
       </c>
       <c r="O158" t="inlineStr">
@@ -15992,7 +15983,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N159" s="2" t="n">
+      <c r="N159" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="O159" t="inlineStr">
@@ -16090,7 +16081,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N160" s="2" t="n">
+      <c r="N160" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="O160" t="inlineStr">
@@ -16188,7 +16179,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N161" s="2" t="n">
+      <c r="N161" s="1" t="n">
         <v>45428</v>
       </c>
       <c r="O161" t="inlineStr">
@@ -16286,7 +16277,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N162" s="2" t="n">
+      <c r="N162" s="1" t="n">
         <v>45482</v>
       </c>
       <c r="O162" t="inlineStr">
@@ -16384,7 +16375,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N163" s="2" t="n">
+      <c r="N163" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="O163" t="inlineStr">
@@ -16482,7 +16473,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N164" s="2" t="n">
+      <c r="N164" s="1" t="n">
         <v>45469</v>
       </c>
       <c r="O164" t="inlineStr">
@@ -16580,7 +16571,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N165" s="2" t="n">
+      <c r="N165" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="O165" t="inlineStr">
@@ -16678,7 +16669,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N166" s="2" t="n">
+      <c r="N166" s="1" t="n">
         <v>45377</v>
       </c>
       <c r="O166" t="inlineStr">
@@ -16776,7 +16767,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N167" s="2" t="n">
+      <c r="N167" s="1" t="n">
         <v>45296</v>
       </c>
       <c r="O167" t="inlineStr">
@@ -16874,7 +16865,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N168" s="2" t="n">
+      <c r="N168" s="1" t="n">
         <v>45435</v>
       </c>
       <c r="O168" t="inlineStr">
@@ -16972,7 +16963,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N169" s="2" t="n">
+      <c r="N169" s="1" t="n">
         <v>45390</v>
       </c>
       <c r="O169" t="inlineStr">
@@ -17070,7 +17061,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N170" s="2" t="n">
+      <c r="N170" s="1" t="n">
         <v>45393</v>
       </c>
       <c r="O170" t="inlineStr">
@@ -17168,7 +17159,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N171" s="2" t="n">
+      <c r="N171" s="1" t="n">
         <v>45404</v>
       </c>
       <c r="O171" t="inlineStr">
@@ -17266,7 +17257,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N172" s="2" t="n">
+      <c r="N172" s="1" t="n">
         <v>45390</v>
       </c>
       <c r="O172" t="inlineStr">
@@ -17364,7 +17355,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N173" s="2" t="n">
+      <c r="N173" s="1" t="n">
         <v>45411</v>
       </c>
       <c r="O173" t="inlineStr">
@@ -17462,7 +17453,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N174" s="2" t="n">
+      <c r="N174" s="1" t="n">
         <v>45411</v>
       </c>
       <c r="O174" t="inlineStr">
@@ -17560,7 +17551,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N175" s="2" t="n">
+      <c r="N175" s="1" t="n">
         <v>44561</v>
       </c>
       <c r="O175" t="inlineStr">
@@ -17658,7 +17649,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N176" s="2" t="n">
+      <c r="N176" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="O176" t="inlineStr">
@@ -17756,7 +17747,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N177" s="2" t="n">
+      <c r="N177" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="O177" t="inlineStr">
@@ -17854,7 +17845,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N178" s="2" t="n">
+      <c r="N178" s="1" t="n">
         <v>45450</v>
       </c>
       <c r="O178" t="inlineStr">
@@ -17952,7 +17943,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N179" s="2" t="n">
+      <c r="N179" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="O179" t="inlineStr">
@@ -18050,7 +18041,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N180" s="2" t="n">
+      <c r="N180" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="O180" t="inlineStr">
@@ -18148,7 +18139,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N181" s="2" t="n">
+      <c r="N181" s="1" t="n">
         <v>45482</v>
       </c>
       <c r="O181" t="inlineStr">
@@ -18246,7 +18237,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N182" s="2" t="n">
+      <c r="N182" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="O182" t="inlineStr">
@@ -18344,7 +18335,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N183" s="2" t="n">
+      <c r="N183" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="O183" t="inlineStr">
@@ -18442,7 +18433,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N184" s="2" t="n">
+      <c r="N184" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="O184" t="inlineStr">
@@ -18540,7 +18531,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N185" s="2" t="n">
+      <c r="N185" s="1" t="n">
         <v>45355</v>
       </c>
       <c r="O185" t="inlineStr">
@@ -18638,7 +18629,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N186" s="2" t="n">
+      <c r="N186" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="O186" t="inlineStr">
@@ -18736,7 +18727,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N187" s="2" t="n">
+      <c r="N187" s="1" t="n">
         <v>45448</v>
       </c>
       <c r="O187" t="inlineStr">
@@ -18834,7 +18825,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N188" s="2" t="n">
+      <c r="N188" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="O188" t="inlineStr">
@@ -18932,7 +18923,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N189" s="2" t="n">
+      <c r="N189" s="1" t="n">
         <v>45392</v>
       </c>
       <c r="O189" t="inlineStr">
@@ -19030,7 +19021,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N190" s="2" t="n">
+      <c r="N190" s="1" t="n">
         <v>45394</v>
       </c>
       <c r="O190" t="inlineStr">
@@ -19128,7 +19119,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N191" s="2" t="n">
+      <c r="N191" s="1" t="n">
         <v>45358</v>
       </c>
       <c r="O191" t="inlineStr">
@@ -19226,7 +19217,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N192" s="2" t="n">
+      <c r="N192" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="O192" t="inlineStr">
@@ -19324,7 +19315,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N193" s="2" t="n">
+      <c r="N193" s="1" t="n">
         <v>45441</v>
       </c>
       <c r="O193" t="inlineStr">
@@ -19422,7 +19413,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N194" s="2" t="n">
+      <c r="N194" s="1" t="n">
         <v>45362</v>
       </c>
       <c r="O194" t="inlineStr">
@@ -19520,7 +19511,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N195" s="2" t="n">
+      <c r="N195" s="1" t="n">
         <v>45362</v>
       </c>
       <c r="O195" t="inlineStr">
@@ -19618,7 +19609,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N196" s="2" t="n">
+      <c r="N196" s="1" t="n">
         <v>45393</v>
       </c>
       <c r="O196" t="inlineStr">
@@ -19716,7 +19707,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N197" s="2" t="n">
+      <c r="N197" s="1" t="n">
         <v>45370</v>
       </c>
       <c r="O197" t="inlineStr">
@@ -19814,7 +19805,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N198" s="2" t="n">
+      <c r="N198" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="O198" t="inlineStr">
@@ -19912,7 +19903,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N199" s="2" t="n">
+      <c r="N199" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="O199" t="inlineStr">
@@ -20010,7 +20001,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N200" s="2" t="n">
+      <c r="N200" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="O200" t="inlineStr">
@@ -20108,7 +20099,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N201" s="2" t="n">
+      <c r="N201" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="O201" t="inlineStr">
@@ -20206,7 +20197,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N202" s="2" t="n">
+      <c r="N202" s="1" t="n">
         <v>45387</v>
       </c>
       <c r="O202" t="inlineStr">
@@ -20304,7 +20295,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N203" s="2" t="n">
+      <c r="N203" s="1" t="n">
         <v>45392</v>
       </c>
       <c r="O203" t="inlineStr">
@@ -20402,7 +20393,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N204" s="2" t="n">
+      <c r="N204" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="O204" t="inlineStr">
@@ -20500,7 +20491,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N205" s="2" t="n">
+      <c r="N205" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="O205" t="inlineStr">
@@ -20598,7 +20589,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N206" s="2" t="n">
+      <c r="N206" s="1" t="n">
         <v>45469</v>
       </c>
       <c r="O206" t="inlineStr">
@@ -20696,7 +20687,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N207" s="2" t="n">
+      <c r="N207" s="1" t="n">
         <v>45421</v>
       </c>
       <c r="O207" t="inlineStr">
@@ -20794,7 +20785,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N208" s="2" t="n">
+      <c r="N208" s="1" t="n">
         <v>45421</v>
       </c>
       <c r="O208" t="inlineStr">
@@ -20892,7 +20883,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N209" s="2" t="n">
+      <c r="N209" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="O209" t="inlineStr">
@@ -20990,7 +20981,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N210" s="2" t="n">
+      <c r="N210" s="1" t="n">
         <v>45301</v>
       </c>
       <c r="O210" t="inlineStr">
@@ -21088,7 +21079,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N211" s="2" t="n">
+      <c r="N211" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="O211" t="inlineStr">
@@ -21186,7 +21177,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N212" s="2" t="n">
+      <c r="N212" s="1" t="n">
         <v>45366</v>
       </c>
       <c r="O212" t="inlineStr">
@@ -21284,7 +21275,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N213" s="2" t="n">
+      <c r="N213" s="1" t="n">
         <v>45272</v>
       </c>
       <c r="O213" t="inlineStr">
@@ -21382,7 +21373,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N214" s="2" t="n">
+      <c r="N214" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="O214" t="inlineStr">
@@ -21480,7 +21471,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N215" s="2" t="n">
+      <c r="N215" s="1" t="n">
         <v>45467</v>
       </c>
       <c r="O215" t="inlineStr">
@@ -21578,7 +21569,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N216" s="2" t="n">
+      <c r="N216" s="1" t="n">
         <v>44344</v>
       </c>
       <c r="O216" t="inlineStr">
@@ -21678,7 +21669,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N217" s="2" t="n">
+      <c r="N217" s="1" t="n">
         <v>45301</v>
       </c>
       <c r="O217" t="inlineStr">
@@ -21778,7 +21769,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N218" s="2" t="n">
+      <c r="N218" s="1" t="n">
         <v>45356</v>
       </c>
       <c r="O218" t="inlineStr">
@@ -21876,7 +21867,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N219" s="2" t="n">
+      <c r="N219" s="1" t="n">
         <v>45427</v>
       </c>
       <c r="O219" t="inlineStr">
@@ -21974,7 +21965,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N220" s="2" t="n">
+      <c r="N220" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="O220" t="inlineStr">
@@ -22072,7 +22063,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N221" s="2" t="n">
+      <c r="N221" s="1" t="n">
         <v>45411</v>
       </c>
       <c r="O221" t="inlineStr">
@@ -22170,7 +22161,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N222" s="2" t="n">
+      <c r="N222" s="1" t="n">
         <v>45307</v>
       </c>
       <c r="O222" t="inlineStr">
@@ -22268,7 +22259,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N223" s="2" t="n">
+      <c r="N223" s="1" t="n">
         <v>45355</v>
       </c>
       <c r="O223" t="inlineStr">
@@ -22366,7 +22357,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N224" s="2" t="n">
+      <c r="N224" s="1" t="n">
         <v>45407</v>
       </c>
       <c r="O224" t="inlineStr">
@@ -22464,7 +22455,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N225" s="2" t="n">
+      <c r="N225" s="1" t="n">
         <v>45371</v>
       </c>
       <c r="O225" t="inlineStr">
@@ -22562,7 +22553,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N226" s="2" t="n">
+      <c r="N226" s="1" t="n">
         <v>45306</v>
       </c>
       <c r="O226" t="inlineStr">
@@ -22660,7 +22651,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N227" s="2" t="n">
+      <c r="N227" s="1" t="n">
         <v>45491</v>
       </c>
       <c r="O227" t="inlineStr">
@@ -22758,7 +22749,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N228" s="2" t="n">
+      <c r="N228" s="1" t="n">
         <v>45414</v>
       </c>
       <c r="O228" t="inlineStr">
@@ -22856,7 +22847,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N229" s="2" t="n">
+      <c r="N229" s="1" t="n">
         <v>45301</v>
       </c>
       <c r="O229" t="inlineStr">
@@ -22954,7 +22945,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N230" s="2" t="n">
+      <c r="N230" s="1" t="n">
         <v>45471</v>
       </c>
       <c r="O230" t="inlineStr">
@@ -23052,7 +23043,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N231" s="2" t="n">
+      <c r="N231" s="1" t="n">
         <v>45377</v>
       </c>
       <c r="O231" t="inlineStr">
@@ -23150,7 +23141,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N232" s="2" t="n">
+      <c r="N232" s="1" t="n">
         <v>45502</v>
       </c>
       <c r="O232" t="inlineStr">
@@ -23248,7 +23239,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N233" s="2" t="n">
+      <c r="N233" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="O233" t="inlineStr">
@@ -23346,7 +23337,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N234" s="2" t="n">
+      <c r="N234" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="O234" t="inlineStr">
@@ -23444,7 +23435,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N235" s="2" t="n">
+      <c r="N235" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="O235" t="inlineStr">
@@ -23542,7 +23533,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N236" s="2" t="n">
+      <c r="N236" s="1" t="n">
         <v>45482</v>
       </c>
       <c r="O236" t="inlineStr">
@@ -23640,7 +23631,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N237" s="2" t="n">
+      <c r="N237" s="1" t="n">
         <v>45491</v>
       </c>
       <c r="O237" t="inlineStr">
@@ -23738,7 +23729,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N238" s="2" t="n">
+      <c r="N238" s="1" t="n">
         <v>45477</v>
       </c>
       <c r="O238" t="inlineStr">
@@ -23836,7 +23827,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N239" s="2" t="n">
+      <c r="N239" s="1" t="n">
         <v>45510</v>
       </c>
       <c r="O239" t="inlineStr">
@@ -23934,7 +23925,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N240" s="2" t="n">
+      <c r="N240" s="1" t="n">
         <v>45510</v>
       </c>
       <c r="O240" t="inlineStr">
@@ -24032,7 +24023,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N241" s="2" t="n">
+      <c r="N241" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="O241" t="inlineStr">
@@ -24130,7 +24121,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N242" s="2" t="n">
+      <c r="N242" s="1" t="n">
         <v>45509</v>
       </c>
       <c r="O242" t="inlineStr">
@@ -24228,7 +24219,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N243" s="2" t="n">
+      <c r="N243" s="1" t="n">
         <v>45485</v>
       </c>
       <c r="O243" t="inlineStr">
@@ -24326,7 +24317,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N244" s="2" t="n">
+      <c r="N244" s="1" t="n">
         <v>45482</v>
       </c>
       <c r="O244" t="inlineStr">
@@ -24424,7 +24415,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N245" s="2" t="n">
+      <c r="N245" s="1" t="n">
         <v>45477</v>
       </c>
       <c r="O245" t="inlineStr">
@@ -24522,7 +24513,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N246" s="2" t="n">
+      <c r="N246" s="1" t="n">
         <v>42240</v>
       </c>
       <c r="O246" t="inlineStr">
@@ -24622,7 +24613,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N247" s="2" t="n">
+      <c r="N247" s="1" t="n">
         <v>42435</v>
       </c>
       <c r="O247" t="inlineStr">
@@ -24722,7 +24713,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N248" s="2" t="n">
+      <c r="N248" s="1" t="n">
         <v>44952</v>
       </c>
       <c r="O248" t="inlineStr">
@@ -24822,7 +24813,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N249" s="2" t="n">
+      <c r="N249" s="1" t="n">
         <v>45180</v>
       </c>
       <c r="O249" t="inlineStr">
@@ -24922,7 +24913,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N250" s="2" t="n">
+      <c r="N250" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O250" t="inlineStr">
@@ -25020,7 +25011,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N251" s="2" t="n">
+      <c r="N251" s="1" t="n">
         <v>45490</v>
       </c>
       <c r="O251" t="inlineStr">
@@ -25118,7 +25109,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N252" s="2" t="n">
+      <c r="N252" s="1" t="n">
         <v>45490</v>
       </c>
       <c r="O252" t="inlineStr">
@@ -25216,7 +25207,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N253" s="2" t="n">
+      <c r="N253" s="1" t="n">
         <v>45519</v>
       </c>
       <c r="O253" t="inlineStr">
@@ -25316,7 +25307,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N254" s="2" t="n">
+      <c r="N254" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O254" t="inlineStr">
@@ -25416,7 +25407,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N255" s="2" t="n">
+      <c r="N255" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O255" t="inlineStr">
@@ -25516,7 +25507,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N256" s="2" t="n">
+      <c r="N256" s="1" t="n">
         <v>44971</v>
       </c>
       <c r="O256" t="inlineStr">
@@ -25616,7 +25607,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N257" s="2" t="n">
+      <c r="N257" s="1" t="n">
         <v>44971</v>
       </c>
       <c r="O257" t="inlineStr">
@@ -25716,7 +25707,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N258" s="2" t="n">
+      <c r="N258" s="1" t="n">
         <v>39459</v>
       </c>
       <c r="O258" t="inlineStr">
@@ -25814,7 +25805,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N259" s="2" t="n">
+      <c r="N259" s="1" t="n">
         <v>45491</v>
       </c>
       <c r="O259" t="inlineStr">
@@ -25914,7 +25905,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N260" s="2" t="n">
+      <c r="N260" s="1" t="n">
         <v>45034</v>
       </c>
       <c r="O260" t="inlineStr">
@@ -26012,7 +26003,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N261" s="2" t="n">
+      <c r="N261" s="1" t="n">
         <v>45504</v>
       </c>
       <c r="O261" t="inlineStr">
@@ -26110,7 +26101,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N262" s="2" t="n">
+      <c r="N262" s="1" t="n">
         <v>45519</v>
       </c>
       <c r="O262" t="inlineStr">
@@ -26208,7 +26199,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N263" s="2" t="n">
+      <c r="N263" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="O263" t="inlineStr">
@@ -26306,7 +26297,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N264" s="2" t="n">
+      <c r="N264" s="1" t="n">
         <v>45518</v>
       </c>
       <c r="O264" t="inlineStr">
@@ -26404,7 +26395,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N265" s="2" t="n">
+      <c r="N265" s="1" t="n">
         <v>45491</v>
       </c>
       <c r="O265" t="inlineStr">
@@ -26502,7 +26493,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N266" s="2" t="n">
+      <c r="N266" s="1" t="n">
         <v>45491</v>
       </c>
       <c r="O266" t="inlineStr">
@@ -26600,7 +26591,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N267" s="2" t="n">
+      <c r="N267" s="1" t="n">
         <v>45518</v>
       </c>
       <c r="O267" t="inlineStr">
@@ -26698,7 +26689,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N268" s="2" t="n">
+      <c r="N268" s="1" t="n">
         <v>45518</v>
       </c>
       <c r="O268" t="inlineStr">
@@ -26798,7 +26789,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N269" s="2" t="n">
+      <c r="N269" s="1" t="n">
         <v>44950</v>
       </c>
       <c r="O269" t="inlineStr">
@@ -26896,7 +26887,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N270" s="2" t="n">
+      <c r="N270" s="1" t="n">
         <v>45524</v>
       </c>
       <c r="O270" t="inlineStr">
@@ -26994,7 +26985,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N271" s="2" t="n">
+      <c r="N271" s="1" t="n">
         <v>45524</v>
       </c>
       <c r="O271" t="inlineStr">
@@ -27092,7 +27083,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N272" s="2" t="n">
+      <c r="N272" s="1" t="n">
         <v>45482</v>
       </c>
       <c r="O272" t="inlineStr">
@@ -27190,7 +27181,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N273" s="2" t="n">
+      <c r="N273" s="1" t="n">
         <v>45392</v>
       </c>
       <c r="O273" t="inlineStr">
@@ -27288,7 +27279,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N274" s="2" t="n">
+      <c r="N274" s="1" t="n">
         <v>45140</v>
       </c>
       <c r="O274" t="inlineStr">
@@ -27386,7 +27377,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N275" s="2" t="n">
+      <c r="N275" s="1" t="n">
         <v>44153</v>
       </c>
       <c r="O275" t="inlineStr">
@@ -27484,7 +27475,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N276" s="2" t="n">
+      <c r="N276" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="O276" t="inlineStr">
@@ -27582,7 +27573,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N277" s="2" t="n">
+      <c r="N277" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="O277" t="inlineStr">
@@ -27680,7 +27671,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N278" s="2" t="n">
+      <c r="N278" s="1" t="n">
         <v>44498</v>
       </c>
       <c r="O278" t="inlineStr">
@@ -27778,7 +27769,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N279" s="2" t="n">
+      <c r="N279" s="1" t="n">
         <v>43826</v>
       </c>
       <c r="O279" t="inlineStr">
@@ -27876,7 +27867,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N280" s="2" t="n">
+      <c r="N280" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="O280" t="inlineStr">
@@ -27974,7 +27965,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N281" s="2" t="n">
+      <c r="N281" s="1" t="n">
         <v>44769</v>
       </c>
       <c r="O281" t="inlineStr">
@@ -28072,7 +28063,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N282" s="2" t="n">
+      <c r="N282" s="1" t="n">
         <v>45573</v>
       </c>
       <c r="O282" t="inlineStr">
@@ -28170,7 +28161,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N283" s="2" t="n">
+      <c r="N283" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="O283" t="inlineStr">
@@ -28268,7 +28259,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N284" s="2" t="n">
+      <c r="N284" s="1" t="n">
         <v>45562</v>
       </c>
       <c r="O284" t="inlineStr">
@@ -28366,7 +28357,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N285" s="2" t="n">
+      <c r="N285" s="1" t="n">
         <v>45390</v>
       </c>
       <c r="O285" t="inlineStr">
@@ -28464,7 +28455,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N286" s="2" t="n">
+      <c r="N286" s="1" t="n">
         <v>45565</v>
       </c>
       <c r="O286" t="inlineStr">
@@ -28562,7 +28553,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N287" s="2" t="n">
+      <c r="N287" s="1" t="n">
         <v>45580</v>
       </c>
       <c r="O287" t="inlineStr">
@@ -28660,7 +28651,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N288" s="2" t="n">
+      <c r="N288" s="1" t="n">
         <v>45580</v>
       </c>
       <c r="O288" t="inlineStr">
@@ -28758,7 +28749,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N289" s="2" t="n">
+      <c r="N289" s="1" t="n">
         <v>45580</v>
       </c>
       <c r="O289" t="inlineStr">
@@ -28856,7 +28847,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N290" s="2" t="n">
+      <c r="N290" s="1" t="n">
         <v>44302</v>
       </c>
       <c r="O290" t="inlineStr">
@@ -28954,7 +28945,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N291" s="2" t="n">
+      <c r="N291" s="1" t="n">
         <v>45587</v>
       </c>
       <c r="O291" t="inlineStr">
@@ -29052,7 +29043,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N292" s="2" t="n">
+      <c r="N292" s="1" t="n">
         <v>45586</v>
       </c>
       <c r="O292" t="inlineStr">
@@ -29150,7 +29141,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N293" s="2" t="n">
+      <c r="N293" s="1" t="n">
         <v>45560</v>
       </c>
       <c r="O293" t="inlineStr">
@@ -29248,7 +29239,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N294" s="2" t="n">
+      <c r="N294" s="1" t="n">
         <v>45587</v>
       </c>
       <c r="O294" t="inlineStr">
@@ -29346,7 +29337,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N295" s="2" t="n">
+      <c r="N295" s="1" t="n">
         <v>45568</v>
       </c>
       <c r="O295" t="inlineStr">
@@ -29444,7 +29435,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N296" s="2" t="n">
+      <c r="N296" s="1" t="n">
         <v>45569</v>
       </c>
       <c r="O296" t="inlineStr">
@@ -29542,7 +29533,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N297" s="2" t="n">
+      <c r="N297" s="1" t="n">
         <v>45586</v>
       </c>
       <c r="O297" t="inlineStr">
@@ -29640,7 +29631,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N298" s="2" t="n">
+      <c r="N298" s="1" t="n">
         <v>45560</v>
       </c>
       <c r="O298" t="inlineStr">
@@ -29738,7 +29729,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N299" s="2" t="n">
+      <c r="N299" s="1" t="n">
         <v>45568</v>
       </c>
       <c r="O299" t="inlineStr">
@@ -29836,7 +29827,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N300" s="2" t="n">
+      <c r="N300" s="1" t="n">
         <v>45362</v>
       </c>
       <c r="O300" t="inlineStr">
@@ -29934,7 +29925,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N301" s="2" t="n">
+      <c r="N301" s="1" t="n">
         <v>45587</v>
       </c>
       <c r="O301" t="inlineStr">
@@ -30032,7 +30023,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N302" s="2" t="n">
+      <c r="N302" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="O302" t="inlineStr">
@@ -30130,7 +30121,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N303" s="2" t="n">
+      <c r="N303" s="1" t="n">
         <v>45555</v>
       </c>
       <c r="O303" t="inlineStr">
@@ -30228,7 +30219,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N304" s="2" t="n">
+      <c r="N304" s="1" t="n">
         <v>45580</v>
       </c>
       <c r="O304" t="inlineStr">
@@ -30326,7 +30317,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N305" s="2" t="n">
+      <c r="N305" s="1" t="n">
         <v>45275</v>
       </c>
       <c r="O305" t="inlineStr">
@@ -30424,7 +30415,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N306" s="2" t="n">
+      <c r="N306" s="1" t="n">
         <v>45586</v>
       </c>
       <c r="O306" t="inlineStr">
@@ -30522,7 +30513,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N307" s="2" t="n">
+      <c r="N307" s="1" t="n">
         <v>45589</v>
       </c>
       <c r="O307" t="inlineStr">
@@ -30620,7 +30611,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N308" s="2" t="n">
+      <c r="N308" s="1" t="n">
         <v>45572</v>
       </c>
       <c r="O308" t="inlineStr">
@@ -30718,7 +30709,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N309" s="2" t="n">
+      <c r="N309" s="1" t="n">
         <v>45572</v>
       </c>
       <c r="O309" t="inlineStr">
@@ -30816,7 +30807,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N310" s="2" t="n">
+      <c r="N310" s="1" t="n">
         <v>43812</v>
       </c>
       <c r="O310" t="inlineStr">
@@ -30914,7 +30905,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N311" s="2" t="n">
+      <c r="N311" s="1" t="n">
         <v>45594</v>
       </c>
       <c r="O311" t="inlineStr">
@@ -31012,7 +31003,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N312" s="2" t="n">
+      <c r="N312" s="1" t="n">
         <v>45546</v>
       </c>
       <c r="O312" t="inlineStr">
@@ -31110,7 +31101,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N313" s="2" t="n">
+      <c r="N313" s="1" t="n">
         <v>45593</v>
       </c>
       <c r="O313" t="inlineStr">
@@ -31208,7 +31199,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N314" s="2" t="n">
+      <c r="N314" s="1" t="n">
         <v>45505</v>
       </c>
       <c r="O314" t="inlineStr">
@@ -31306,7 +31297,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N315" s="2" t="n">
+      <c r="N315" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="O315" t="inlineStr">
@@ -31404,7 +31395,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N316" s="2" t="n">
+      <c r="N316" s="1" t="n">
         <v>45576</v>
       </c>
       <c r="O316" t="inlineStr">
@@ -31502,7 +31493,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N317" s="2" t="n">
+      <c r="N317" s="1" t="n">
         <v>45588</v>
       </c>
       <c r="O317" t="inlineStr">
@@ -31600,7 +31591,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N318" s="2" t="n">
+      <c r="N318" s="1" t="n">
         <v>45488</v>
       </c>
       <c r="O318" t="inlineStr">
@@ -31698,7 +31689,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N319" s="2" t="n">
+      <c r="N319" s="1" t="n">
         <v>45554</v>
       </c>
       <c r="O319" t="inlineStr">
@@ -31796,7 +31787,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N320" s="2" t="n">
+      <c r="N320" s="1" t="n">
         <v>45469</v>
       </c>
       <c r="O320" t="inlineStr">
@@ -31894,7 +31885,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N321" s="2" t="n">
+      <c r="N321" s="1" t="n">
         <v>45499</v>
       </c>
       <c r="O321" t="inlineStr">
@@ -31994,7 +31985,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N322" s="2" t="n">
+      <c r="N322" s="1" t="n">
         <v>45278</v>
       </c>
       <c r="O322" t="inlineStr">
@@ -32092,7 +32083,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N323" s="2" t="n">
+      <c r="N323" s="1" t="n">
         <v>45488</v>
       </c>
       <c r="O323" t="inlineStr">
@@ -32190,7 +32181,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N324" s="2" t="n">
+      <c r="N324" s="1" t="n">
         <v>45467</v>
       </c>
       <c r="O324" t="inlineStr">
@@ -32288,7 +32279,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N325" s="2" t="n">
+      <c r="N325" s="1" t="n">
         <v>45601</v>
       </c>
       <c r="O325" t="inlineStr">
@@ -32386,7 +32377,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N326" s="2" t="n">
+      <c r="N326" s="1" t="n">
         <v>45603</v>
       </c>
       <c r="O326" t="inlineStr">
@@ -32484,7 +32475,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N327" s="2" t="n">
+      <c r="N327" s="1" t="n">
         <v>45483</v>
       </c>
       <c r="O327" t="inlineStr">
@@ -32582,7 +32573,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N328" s="2" t="n">
+      <c r="N328" s="1" t="n">
         <v>45623</v>
       </c>
       <c r="O328" t="inlineStr">
@@ -32680,7 +32671,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N329" s="2" t="n">
+      <c r="N329" s="1" t="n">
         <v>45614</v>
       </c>
       <c r="O329" t="inlineStr">
@@ -32778,7 +32769,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N330" s="2" t="n">
+      <c r="N330" s="1" t="n">
         <v>45546</v>
       </c>
       <c r="O330" t="inlineStr">
@@ -32876,7 +32867,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N331" s="2" t="n">
+      <c r="N331" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="O331" t="inlineStr">
@@ -32974,7 +32965,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N332" s="2" t="n">
+      <c r="N332" s="1" t="n">
         <v>45614</v>
       </c>
       <c r="O332" t="inlineStr">
@@ -33072,7 +33063,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N333" s="2" t="n">
+      <c r="N333" s="1" t="n">
         <v>45614</v>
       </c>
       <c r="O333" t="inlineStr">
@@ -33172,7 +33163,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N334" s="2" t="n">
+      <c r="N334" s="1" t="n">
         <v>43251</v>
       </c>
       <c r="O334" t="inlineStr">
@@ -33270,7 +33261,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N335" s="2" t="n">
+      <c r="N335" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="O335" t="inlineStr">
@@ -33368,7 +33359,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N336" s="2" t="n">
+      <c r="N336" s="1" t="n">
         <v>45559</v>
       </c>
       <c r="O336" t="inlineStr">
@@ -33466,7 +33457,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N337" s="2" t="n">
+      <c r="N337" s="1" t="n">
         <v>45625</v>
       </c>
       <c r="O337" t="inlineStr">
@@ -33564,7 +33555,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N338" s="2" t="n">
+      <c r="N338" s="1" t="n">
         <v>45498</v>
       </c>
       <c r="O338" t="inlineStr">
@@ -33662,7 +33653,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N339" s="2" t="n">
+      <c r="N339" s="1" t="n">
         <v>45603</v>
       </c>
       <c r="O339" t="inlineStr">
@@ -33760,7 +33751,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N340" s="2" t="n">
+      <c r="N340" s="1" t="n">
         <v>45603</v>
       </c>
       <c r="O340" t="inlineStr">
@@ -33858,7 +33849,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N341" s="2" t="n">
+      <c r="N341" s="1" t="n">
         <v>45546</v>
       </c>
       <c r="O341" t="inlineStr">
@@ -33956,7 +33947,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N342" s="2" t="n">
+      <c r="N342" s="1" t="n">
         <v>45602</v>
       </c>
       <c r="O342" t="inlineStr">
@@ -34054,7 +34045,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N343" s="2" t="n">
+      <c r="N343" s="1" t="n">
         <v>45587</v>
       </c>
       <c r="O343" t="inlineStr">
@@ -34152,7 +34143,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N344" s="2" t="n">
+      <c r="N344" s="1" t="n">
         <v>45610</v>
       </c>
       <c r="O344" t="inlineStr">
@@ -34250,7 +34241,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N345" s="2" t="n">
+      <c r="N345" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="O345" t="inlineStr">
@@ -34348,7 +34339,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N346" s="2" t="n">
+      <c r="N346" s="1" t="n">
         <v>45604</v>
       </c>
       <c r="O346" t="inlineStr">
@@ -34446,7 +34437,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N347" s="2" t="n">
+      <c r="N347" s="1" t="n">
         <v>45573</v>
       </c>
       <c r="O347" t="inlineStr">
@@ -34546,7 +34537,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N348" s="2" t="n">
+      <c r="N348" s="1" t="n">
         <v>45615</v>
       </c>
       <c r="O348" t="inlineStr">
@@ -34644,7 +34635,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N349" s="2" t="n">
+      <c r="N349" s="1" t="n">
         <v>45635</v>
       </c>
       <c r="O349" t="inlineStr">
@@ -34742,7 +34733,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N350" s="2" t="n">
+      <c r="N350" s="1" t="n">
         <v>45635</v>
       </c>
       <c r="O350" t="inlineStr">
@@ -34840,7 +34831,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N351" s="2" t="n">
+      <c r="N351" s="1" t="n">
         <v>45616</v>
       </c>
       <c r="O351" t="inlineStr">
@@ -34938,7 +34929,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N352" s="2" t="n">
+      <c r="N352" s="1" t="n">
         <v>44704</v>
       </c>
       <c r="O352" t="inlineStr">
@@ -35036,7 +35027,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N353" s="2" t="n">
+      <c r="N353" s="1" t="n">
         <v>45623</v>
       </c>
       <c r="O353" t="inlineStr">
@@ -35134,7 +35125,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N354" s="2" t="n">
+      <c r="N354" s="1" t="n">
         <v>45623</v>
       </c>
       <c r="O354" t="inlineStr">
@@ -35232,7 +35223,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N355" s="2" t="n">
+      <c r="N355" s="1" t="n">
         <v>45603</v>
       </c>
       <c r="O355" t="inlineStr">
@@ -35330,7 +35321,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N356" s="2" t="n">
+      <c r="N356" s="1" t="n">
         <v>45603</v>
       </c>
       <c r="O356" t="inlineStr">
@@ -35428,7 +35419,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N357" s="2" t="n">
+      <c r="N357" s="1" t="n">
         <v>45659</v>
       </c>
       <c r="O357" t="inlineStr">
@@ -35526,7 +35517,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N358" s="2" t="n">
+      <c r="N358" s="1" t="n">
         <v>45635</v>
       </c>
       <c r="O358" t="inlineStr">
@@ -35626,7 +35617,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N359" s="2" t="n">
+      <c r="N359" s="1" t="n">
         <v>45572</v>
       </c>
       <c r="O359" t="inlineStr">
@@ -35724,7 +35715,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N360" s="2" t="n">
+      <c r="N360" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="O360" t="inlineStr">
@@ -35822,7 +35813,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N361" s="2" t="n">
+      <c r="N361" s="1" t="n">
         <v>45650</v>
       </c>
       <c r="O361" t="inlineStr">
@@ -35920,7 +35911,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N362" s="2" t="n">
+      <c r="N362" s="1" t="n">
         <v>45649</v>
       </c>
       <c r="O362" t="inlineStr">
@@ -36018,7 +36009,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N363" s="2" t="n">
+      <c r="N363" s="1" t="n">
         <v>45649</v>
       </c>
       <c r="O363" t="inlineStr">
@@ -36116,7 +36107,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N364" s="2" t="n">
+      <c r="N364" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="O364" t="inlineStr">
@@ -36214,7 +36205,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N365" s="2" t="n">
+      <c r="N365" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="O365" t="inlineStr">
@@ -36312,7 +36303,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N366" s="2" t="n">
+      <c r="N366" s="1" t="n">
         <v>45623</v>
       </c>
       <c r="O366" t="inlineStr">
@@ -36410,7 +36401,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N367" s="2" t="n">
+      <c r="N367" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="O367" t="inlineStr">
@@ -36508,7 +36499,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N368" s="2" t="n">
+      <c r="N368" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O368" t="inlineStr">
@@ -36606,7 +36597,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N369" s="2" t="n">
+      <c r="N369" s="1" t="n">
         <v>45601</v>
       </c>
       <c r="O369" t="inlineStr">
@@ -36704,7 +36695,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N370" s="2" t="n">
+      <c r="N370" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="O370" t="inlineStr">
@@ -36802,7 +36793,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N371" s="2" t="n">
+      <c r="N371" s="1" t="n">
         <v>45373</v>
       </c>
       <c r="O371" t="inlineStr">
@@ -36900,7 +36891,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N372" s="2" t="n">
+      <c r="N372" s="1" t="n">
         <v>45649</v>
       </c>
       <c r="O372" t="inlineStr">
@@ -36998,7 +36989,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N373" s="2" t="n">
+      <c r="N373" s="1" t="n">
         <v>45631</v>
       </c>
       <c r="O373" t="inlineStr">
@@ -37096,7 +37087,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N374" s="2" t="n">
+      <c r="N374" s="1" t="n">
         <v>45400</v>
       </c>
       <c r="O374" t="inlineStr">
@@ -37194,7 +37185,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N375" s="2" t="n">
+      <c r="N375" s="1" t="n">
         <v>45621</v>
       </c>
       <c r="O375" t="inlineStr">
@@ -37292,7 +37283,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N376" s="2" t="n">
+      <c r="N376" s="1" t="n">
         <v>45650</v>
       </c>
       <c r="O376" t="inlineStr">
@@ -37390,7 +37381,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N377" s="2" t="n">
+      <c r="N377" s="1" t="n">
         <v>45659</v>
       </c>
       <c r="O377" t="inlineStr">
@@ -37488,7 +37479,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N378" s="2" t="n">
+      <c r="N378" s="1" t="n">
         <v>44018</v>
       </c>
       <c r="O378" t="inlineStr">
@@ -37586,7 +37577,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N379" s="2" t="n">
+      <c r="N379" s="1" t="n">
         <v>41773</v>
       </c>
       <c r="O379" t="inlineStr">
@@ -37686,7 +37677,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N380" s="2" t="n">
+      <c r="N380" s="1" t="n">
         <v>42410</v>
       </c>
       <c r="O380" t="inlineStr">
@@ -37784,7 +37775,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N381" s="2" t="n">
+      <c r="N381" s="1" t="n">
         <v>45672</v>
       </c>
       <c r="O381" t="inlineStr">
@@ -37882,7 +37873,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N382" s="2" t="n">
+      <c r="N382" s="1" t="n">
         <v>45538</v>
       </c>
       <c r="O382" t="inlineStr">
@@ -37980,7 +37971,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N383" s="2" t="n">
+      <c r="N383" s="1" t="n">
         <v>45673</v>
       </c>
       <c r="O383" t="inlineStr">
@@ -38078,7 +38069,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N384" s="2" t="n">
+      <c r="N384" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="O384" t="inlineStr">
@@ -38176,7 +38167,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N385" s="2" t="n">
+      <c r="N385" s="1" t="n">
         <v>45495</v>
       </c>
       <c r="O385" t="inlineStr">
@@ -38274,7 +38265,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N386" s="2" t="n">
+      <c r="N386" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="O386" t="inlineStr">
@@ -38372,7 +38363,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N387" s="2" t="n">
+      <c r="N387" s="1" t="n">
         <v>45632</v>
       </c>
       <c r="O387" t="inlineStr">
@@ -38470,7 +38461,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N388" s="2" t="n">
+      <c r="N388" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O388" t="inlineStr">
@@ -38568,7 +38559,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N389" s="2" t="n">
+      <c r="N389" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="O389" t="inlineStr">
@@ -38666,7 +38657,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N390" s="2" t="n">
+      <c r="N390" s="1" t="n">
         <v>45671</v>
       </c>
       <c r="O390" t="inlineStr">
@@ -38764,7 +38755,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N391" s="2" t="n">
+      <c r="N391" s="1" t="n">
         <v>45671</v>
       </c>
       <c r="O391" t="inlineStr">
@@ -38862,7 +38853,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N392" s="2" t="n">
+      <c r="N392" s="1" t="n">
         <v>45673</v>
       </c>
       <c r="O392" t="inlineStr">
@@ -38960,7 +38951,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N393" s="2" t="n">
+      <c r="N393" s="1" t="n">
         <v>45645</v>
       </c>
       <c r="O393" t="inlineStr">
@@ -39058,7 +39049,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N394" s="2" t="n">
+      <c r="N394" s="1" t="n">
         <v>45650</v>
       </c>
       <c r="O394" t="inlineStr">
@@ -39156,7 +39147,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N395" s="2" t="n">
+      <c r="N395" s="1" t="n">
         <v>45673</v>
       </c>
       <c r="O395" t="inlineStr">
@@ -39254,7 +39245,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N396" s="2" t="n">
+      <c r="N396" s="1" t="n">
         <v>45672</v>
       </c>
       <c r="O396" t="inlineStr">
@@ -39352,7 +39343,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N397" s="2" t="n">
+      <c r="N397" s="1" t="n">
         <v>45623</v>
       </c>
       <c r="O397" t="inlineStr">
@@ -39450,7 +39441,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N398" s="2" t="n">
+      <c r="N398" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O398" t="inlineStr">
@@ -39548,7 +39539,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N399" s="2" t="n">
+      <c r="N399" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O399" t="inlineStr">
@@ -39646,7 +39637,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N400" s="2" t="n">
+      <c r="N400" s="1" t="n">
         <v>45665</v>
       </c>
       <c r="O400" t="inlineStr">
@@ -39744,7 +39735,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N401" s="2" t="n">
+      <c r="N401" s="1" t="n">
         <v>45673</v>
       </c>
       <c r="O401" t="inlineStr">
@@ -39842,7 +39833,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N402" s="2" t="n">
+      <c r="N402" s="1" t="n">
         <v>45686</v>
       </c>
       <c r="O402" t="inlineStr">
@@ -39940,7 +39931,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N403" s="2" t="n">
+      <c r="N403" s="1" t="n">
         <v>45686</v>
       </c>
       <c r="O403" t="inlineStr">
@@ -40040,7 +40031,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N404" s="2" t="n">
+      <c r="N404" s="1" t="n">
         <v>45392</v>
       </c>
       <c r="O404" t="inlineStr">
@@ -40138,7 +40129,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N405" s="2" t="n">
+      <c r="N405" s="1" t="n">
         <v>45650</v>
       </c>
       <c r="O405" t="inlineStr">
@@ -40236,7 +40227,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N406" s="2" t="n">
+      <c r="N406" s="1" t="n">
         <v>45650</v>
       </c>
       <c r="O406" t="inlineStr">
@@ -40334,7 +40325,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N407" s="2" t="n">
+      <c r="N407" s="1" t="n">
         <v>45645</v>
       </c>
       <c r="O407" t="inlineStr">
@@ -40432,7 +40423,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N408" s="2" t="n">
+      <c r="N408" s="1" t="n">
         <v>45673</v>
       </c>
       <c r="O408" t="inlineStr">
@@ -40530,7 +40521,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N409" s="2" t="n">
+      <c r="N409" s="1" t="n">
         <v>45667</v>
       </c>
       <c r="O409" t="inlineStr">
@@ -40628,7 +40619,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N410" s="2" t="n">
+      <c r="N410" s="1" t="n">
         <v>45657</v>
       </c>
       <c r="O410" t="inlineStr">
@@ -40726,7 +40717,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N411" s="2" t="n">
+      <c r="N411" s="1" t="n">
         <v>45673</v>
       </c>
       <c r="O411" t="inlineStr">
@@ -40824,7 +40815,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N412" s="2" t="n">
+      <c r="N412" s="1" t="n">
         <v>45672</v>
       </c>
       <c r="O412" t="inlineStr">
@@ -40922,7 +40913,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N413" s="2" t="n">
+      <c r="N413" s="1" t="n">
         <v>45659</v>
       </c>
       <c r="O413" t="inlineStr">
@@ -41020,7 +41011,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N414" s="2" t="n">
+      <c r="N414" s="1" t="n">
         <v>45692</v>
       </c>
       <c r="O414" t="inlineStr">
@@ -41118,7 +41109,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N415" s="2" t="n">
+      <c r="N415" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O415" t="inlineStr">
@@ -41216,7 +41207,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N416" s="2" t="n">
+      <c r="N416" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O416" t="inlineStr">
@@ -41314,7 +41305,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N417" s="2" t="n">
+      <c r="N417" s="1" t="n">
         <v>45660</v>
       </c>
       <c r="O417" t="inlineStr">
@@ -41412,7 +41403,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N418" s="2" t="n">
+      <c r="N418" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O418" t="inlineStr">
@@ -41510,7 +41501,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N419" s="2" t="n">
+      <c r="N419" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O419" t="inlineStr">
@@ -41608,7 +41599,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N420" s="2" t="n">
+      <c r="N420" s="1" t="n">
         <v>45707</v>
       </c>
       <c r="O420" t="inlineStr">
@@ -41706,7 +41697,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N421" s="2" t="n">
+      <c r="N421" s="1" t="n">
         <v>45706</v>
       </c>
       <c r="O421" t="inlineStr">
@@ -41804,7 +41795,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N422" s="2" t="n">
+      <c r="N422" s="1" t="n">
         <v>45706</v>
       </c>
       <c r="O422" t="inlineStr">
@@ -41902,7 +41893,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N423" s="2" t="n">
+      <c r="N423" s="1" t="n">
         <v>45705</v>
       </c>
       <c r="O423" t="inlineStr">
@@ -42000,7 +41991,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N424" s="2" t="n">
+      <c r="N424" s="1" t="n">
         <v>45706</v>
       </c>
       <c r="O424" t="inlineStr">
@@ -42098,7 +42089,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N425" s="2" t="n">
+      <c r="N425" s="1" t="n">
         <v>45727</v>
       </c>
       <c r="O425" t="inlineStr">
@@ -42196,7 +42187,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N426" s="2" t="n">
+      <c r="N426" s="1" t="n">
         <v>45721</v>
       </c>
       <c r="O426" t="inlineStr">
@@ -42294,7 +42285,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N427" s="2" t="n">
+      <c r="N427" s="1" t="n">
         <v>45706</v>
       </c>
       <c r="O427" t="inlineStr">
@@ -42392,7 +42383,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N428" s="2" t="n">
+      <c r="N428" s="1" t="n">
         <v>45712</v>
       </c>
       <c r="O428" t="inlineStr">
@@ -42490,7 +42481,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N429" s="2" t="n">
+      <c r="N429" s="1" t="n">
         <v>45693</v>
       </c>
       <c r="O429" t="inlineStr">
@@ -42588,7 +42579,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N430" s="2" t="n">
+      <c r="N430" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="O430" t="inlineStr">
@@ -42686,7 +42677,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N431" s="2" t="n">
+      <c r="N431" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="O431" t="inlineStr">
@@ -42784,7 +42775,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N432" s="2" t="n">
+      <c r="N432" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="O432" t="inlineStr">
@@ -42882,7 +42873,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N433" s="2" t="n">
+      <c r="N433" s="1" t="n">
         <v>45707</v>
       </c>
       <c r="O433" t="inlineStr">
@@ -42980,7 +42971,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N434" s="2" t="n">
+      <c r="N434" s="1" t="n">
         <v>45712</v>
       </c>
       <c r="O434" t="inlineStr">
@@ -43078,7 +43069,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N435" s="2" t="n">
+      <c r="N435" s="1" t="n">
         <v>45707</v>
       </c>
       <c r="O435" t="inlineStr">
@@ -43176,7 +43167,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N436" s="2" t="n">
+      <c r="N436" s="1" t="n">
         <v>45707</v>
       </c>
       <c r="O436" t="inlineStr">
@@ -43274,7 +43265,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N437" s="2" t="n">
+      <c r="N437" s="1" t="n">
         <v>45702</v>
       </c>
       <c r="O437" t="inlineStr">
@@ -43372,7 +43363,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N438" s="2" t="n">
+      <c r="N438" s="1" t="n">
         <v>45707</v>
       </c>
       <c r="O438" t="inlineStr">
@@ -43470,7 +43461,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N439" s="2" t="n">
+      <c r="N439" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="O439" t="inlineStr">
@@ -43568,7 +43559,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N440" s="2" t="n">
+      <c r="N440" s="1" t="n">
         <v>45714</v>
       </c>
       <c r="O440" t="inlineStr">
@@ -43666,7 +43657,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N441" s="2" t="n">
+      <c r="N441" s="1" t="n">
         <v>45712</v>
       </c>
       <c r="O441" t="inlineStr">
@@ -43764,7 +43755,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N442" s="2" t="n">
+      <c r="N442" s="1" t="n">
         <v>45712</v>
       </c>
       <c r="O442" t="inlineStr">
@@ -43862,7 +43853,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N443" s="2" t="n">
+      <c r="N443" s="1" t="n">
         <v>45698</v>
       </c>
       <c r="O443" t="inlineStr">
@@ -43960,7 +43951,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N444" s="2" t="n">
+      <c r="N444" s="1" t="n">
         <v>45698</v>
       </c>
       <c r="O444" t="inlineStr">
@@ -44058,7 +44049,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N445" s="2" t="n">
+      <c r="N445" s="1" t="n">
         <v>45719</v>
       </c>
       <c r="O445" t="inlineStr">
@@ -44156,7 +44147,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N446" s="2" t="n">
+      <c r="N446" s="1" t="n">
         <v>45716</v>
       </c>
       <c r="O446" t="inlineStr">
@@ -44254,7 +44245,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N447" s="2" t="n">
+      <c r="N447" s="1" t="n">
         <v>43812</v>
       </c>
       <c r="O447" t="inlineStr">
@@ -44352,7 +44343,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N448" s="2" t="n">
+      <c r="N448" s="1" t="n">
         <v>44405</v>
       </c>
       <c r="O448" t="inlineStr">
@@ -44450,7 +44441,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N449" s="2" t="n">
+      <c r="N449" s="1" t="n">
         <v>45733</v>
       </c>
       <c r="O449" t="inlineStr">
@@ -44548,7 +44539,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N450" s="2" t="n">
+      <c r="N450" s="1" t="n">
         <v>45733</v>
       </c>
       <c r="O450" t="inlineStr">
@@ -44646,7 +44637,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N451" s="2" t="n">
+      <c r="N451" s="1" t="n">
         <v>45733</v>
       </c>
       <c r="O451" t="inlineStr">
@@ -44744,7 +44735,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N452" s="2" t="n">
+      <c r="N452" s="1" t="n">
         <v>45477</v>
       </c>
       <c r="O452" t="inlineStr">
@@ -44844,7 +44835,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N453" s="2" t="n">
+      <c r="N453" s="1" t="n">
         <v>45348</v>
       </c>
       <c r="O453" t="inlineStr">
@@ -44942,7 +44933,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N454" s="2" t="n">
+      <c r="N454" s="1" t="n">
         <v>45734</v>
       </c>
       <c r="O454" t="inlineStr">
@@ -45040,7 +45031,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N455" s="2" t="n">
+      <c r="N455" s="1" t="n">
         <v>45734</v>
       </c>
       <c r="O455" t="inlineStr">
@@ -45138,7 +45129,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N456" s="2" t="n">
+      <c r="N456" s="1" t="n">
         <v>45733</v>
       </c>
       <c r="O456" t="inlineStr">
@@ -45236,7 +45227,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N457" s="2" t="n">
+      <c r="N457" s="1" t="n">
         <v>43628</v>
       </c>
       <c r="O457" t="inlineStr">
@@ -45334,7 +45325,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N458" s="2" t="n">
+      <c r="N458" s="1" t="n">
         <v>45734</v>
       </c>
       <c r="O458" t="inlineStr">
@@ -45432,7 +45423,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N459" s="2" t="n">
+      <c r="N459" s="1" t="n">
         <v>45734</v>
       </c>
       <c r="O459" t="inlineStr">
@@ -45530,7 +45521,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N460" s="2" t="n">
+      <c r="N460" s="1" t="n">
         <v>45734</v>
       </c>
       <c r="O460" t="inlineStr">
@@ -45628,7 +45619,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N461" s="2" t="n">
+      <c r="N461" s="1" t="n">
         <v>38296</v>
       </c>
       <c r="O461" t="inlineStr">
@@ -45726,7 +45717,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N462" s="2" t="n">
+      <c r="N462" s="1" t="n">
         <v>45730</v>
       </c>
       <c r="O462" t="inlineStr">
@@ -45824,7 +45815,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N463" s="2" t="n">
+      <c r="N463" s="1" t="n">
         <v>38853</v>
       </c>
       <c r="O463" t="inlineStr">
@@ -45922,7 +45913,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N464" s="2" t="n">
+      <c r="N464" s="1" t="n">
         <v>37952</v>
       </c>
       <c r="O464" t="inlineStr">
@@ -46020,7 +46011,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N465" s="2" t="n">
+      <c r="N465" s="1" t="n">
         <v>45734</v>
       </c>
       <c r="O465" t="inlineStr">
@@ -46118,7 +46109,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N466" s="2" t="n">
+      <c r="N466" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O466" t="inlineStr">
@@ -46216,7 +46207,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N467" s="2" t="n">
+      <c r="N467" s="1" t="n">
         <v>44753</v>
       </c>
       <c r="O467" t="inlineStr">
@@ -46314,7 +46305,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N468" s="2" t="n">
+      <c r="N468" s="1" t="n">
         <v>45734</v>
       </c>
       <c r="O468" t="inlineStr">
@@ -46412,7 +46403,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N469" s="2" t="n">
+      <c r="N469" s="1" t="n">
         <v>45734</v>
       </c>
       <c r="O469" t="inlineStr">
@@ -46510,7 +46501,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N470" s="2" t="n">
+      <c r="N470" s="1" t="n">
         <v>45734</v>
       </c>
       <c r="O470" t="inlineStr">
@@ -46608,7 +46599,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N471" s="2" t="n">
+      <c r="N471" s="1" t="n">
         <v>43483</v>
       </c>
       <c r="O471" t="inlineStr">
@@ -46706,7 +46697,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N472" s="2" t="n">
+      <c r="N472" s="1" t="n">
         <v>45719</v>
       </c>
       <c r="O472" t="inlineStr">
@@ -46804,7 +46795,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N473" s="2" t="n">
+      <c r="N473" s="1" t="n">
         <v>45719</v>
       </c>
       <c r="O473" t="inlineStr">
@@ -46902,7 +46893,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N474" s="2" t="n">
+      <c r="N474" s="1" t="n">
         <v>45719</v>
       </c>
       <c r="O474" t="inlineStr">
@@ -47000,7 +46991,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N475" s="2" t="n">
+      <c r="N475" s="1" t="n">
         <v>45712</v>
       </c>
       <c r="O475" t="inlineStr">
@@ -47098,7 +47089,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N476" s="2" t="n">
+      <c r="N476" s="1" t="n">
         <v>45744</v>
       </c>
       <c r="O476" t="inlineStr">
@@ -47196,7 +47187,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N477" s="2" t="n">
+      <c r="N477" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O477" t="inlineStr">
@@ -47294,7 +47285,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N478" s="2" t="n">
+      <c r="N478" s="1" t="n">
         <v>45772</v>
       </c>
       <c r="O478" t="inlineStr">
@@ -47392,7 +47383,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N479" s="2" t="n">
+      <c r="N479" s="1" t="n">
         <v>45782</v>
       </c>
       <c r="O479" t="inlineStr">
@@ -47492,7 +47483,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N480" s="2" t="n">
+      <c r="N480" s="1" t="n">
         <v>42492</v>
       </c>
       <c r="O480" t="inlineStr">
@@ -47590,7 +47581,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N481" s="2" t="n">
+      <c r="N481" s="1" t="n">
         <v>45674</v>
       </c>
       <c r="O481" t="inlineStr">
@@ -47688,7 +47679,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N482" s="2" t="n">
+      <c r="N482" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O482" t="inlineStr">
@@ -47786,7 +47777,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N483" s="2" t="n">
+      <c r="N483" s="1" t="n">
         <v>45650</v>
       </c>
       <c r="O483" t="inlineStr">
@@ -47884,7 +47875,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N484" s="2" t="n">
+      <c r="N484" s="1" t="n">
         <v>43483</v>
       </c>
       <c r="O484" t="inlineStr">
@@ -47982,7 +47973,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N485" s="2" t="n">
+      <c r="N485" s="1" t="n">
         <v>45749</v>
       </c>
       <c r="O485" t="inlineStr">
@@ -48080,7 +48071,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N486" s="2" t="n">
+      <c r="N486" s="1" t="n">
         <v>45790</v>
       </c>
       <c r="O486" t="inlineStr">
@@ -48178,7 +48169,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N487" s="2" t="n">
+      <c r="N487" s="1" t="n">
         <v>45189</v>
       </c>
       <c r="O487" t="inlineStr">
@@ -48276,7 +48267,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N488" s="2" t="n">
+      <c r="N488" s="1" t="n">
         <v>45449</v>
       </c>
       <c r="O488" t="inlineStr">
@@ -48374,7 +48365,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N489" s="2" t="n">
+      <c r="N489" s="1" t="n">
         <v>45800</v>
       </c>
       <c r="O489" t="inlineStr">
@@ -48472,7 +48463,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N490" s="2" t="n">
+      <c r="N490" s="1" t="n">
         <v>45791</v>
       </c>
       <c r="O490" t="inlineStr">
@@ -48570,7 +48561,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N491" s="2" t="n">
+      <c r="N491" s="1" t="n">
         <v>45791</v>
       </c>
       <c r="O491" t="inlineStr">
@@ -48668,7 +48659,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N492" s="2" t="n">
+      <c r="N492" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O492" t="inlineStr">
@@ -48766,7 +48757,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N493" s="2" t="n">
+      <c r="N493" s="1" t="n">
         <v>45643</v>
       </c>
       <c r="O493" t="inlineStr">
@@ -48864,7 +48855,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N494" s="2" t="n">
+      <c r="N494" s="1" t="n">
         <v>45554</v>
       </c>
       <c r="O494" t="inlineStr">
@@ -48962,7 +48953,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N495" s="2" t="n">
+      <c r="N495" s="1" t="n">
         <v>45734</v>
       </c>
       <c r="O495" t="inlineStr">
@@ -49060,7 +49051,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N496" s="2" t="n">
+      <c r="N496" s="1" t="n">
         <v>45924</v>
       </c>
       <c r="O496" t="inlineStr">
@@ -49158,7 +49149,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N497" s="2" t="n">
+      <c r="N497" s="1" t="n">
         <v>45931</v>
       </c>
       <c r="O497" t="inlineStr">
@@ -49256,7 +49247,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N498" s="2" t="n">
+      <c r="N498" s="1" t="n">
         <v>45960</v>
       </c>
       <c r="O498" t="inlineStr">
@@ -49354,7 +49345,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N499" s="2" t="n">
+      <c r="N499" s="1" t="n">
         <v>45953</v>
       </c>
       <c r="O499" t="inlineStr">
@@ -49452,7 +49443,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N500" s="2" t="n">
+      <c r="N500" s="1" t="n">
         <v>43882</v>
       </c>
       <c r="O500" t="inlineStr">
@@ -49550,7 +49541,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N501" s="2" t="n">
+      <c r="N501" s="1" t="n">
         <v>43882</v>
       </c>
       <c r="O501" t="inlineStr">
@@ -49648,7 +49639,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N502" s="2" t="n">
+      <c r="N502" s="1" t="n">
         <v>45149</v>
       </c>
       <c r="O502" t="inlineStr">
@@ -49746,7 +49737,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N503" s="2" t="n">
+      <c r="N503" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O503" t="inlineStr">
@@ -49844,7 +49835,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N504" s="2" t="n">
+      <c r="N504" s="1" t="n">
         <v>45945</v>
       </c>
       <c r="O504" t="inlineStr">
@@ -49942,7 +49933,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N505" s="2" t="n">
+      <c r="N505" s="1" t="n">
         <v>43882</v>
       </c>
       <c r="O505" t="inlineStr">
@@ -50040,7 +50031,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N506" s="2" t="n">
+      <c r="N506" s="1" t="n">
         <v>45883</v>
       </c>
       <c r="O506" t="inlineStr">
@@ -50138,7 +50129,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N507" s="2" t="n">
+      <c r="N507" s="1" t="n">
         <v>45281</v>
       </c>
       <c r="O507" t="inlineStr">
@@ -50238,7 +50229,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N508" s="2" t="n">
+      <c r="N508" s="1" t="n">
         <v>45972</v>
       </c>
       <c r="O508" t="inlineStr">
@@ -50334,7 +50325,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N509" s="2" t="n">
+      <c r="N509" s="1" t="n">
         <v>45874</v>
       </c>
       <c r="O509" t="inlineStr">
@@ -50434,7 +50425,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N510" s="2" t="n">
+      <c r="N510" s="1" t="n">
         <v>45782</v>
       </c>
       <c r="O510" t="inlineStr">
@@ -50534,7 +50525,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N511" s="2" t="n">
+      <c r="N511" s="1" t="n">
         <v>45782</v>
       </c>
       <c r="O511" t="inlineStr">
@@ -50632,7 +50623,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N512" s="2" t="n">
+      <c r="N512" s="1" t="n">
         <v>43755</v>
       </c>
       <c r="O512" t="inlineStr">
@@ -50730,7 +50721,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N513" s="2" t="n">
+      <c r="N513" s="1" t="n">
         <v>45687</v>
       </c>
       <c r="O513" t="inlineStr">
@@ -50828,7 +50819,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N514" s="2" t="n">
+      <c r="N514" s="1" t="n">
         <v>44775</v>
       </c>
       <c r="O514" t="inlineStr">
@@ -50928,7 +50919,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N515" s="2" t="n">
+      <c r="N515" s="1" t="n">
         <v>45951</v>
       </c>
       <c r="O515" t="inlineStr">
@@ -51026,7 +51017,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N516" s="2" t="n">
+      <c r="N516" s="1" t="n">
         <v>45000</v>
       </c>
       <c r="O516" t="inlineStr">
@@ -51126,7 +51117,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N517" s="2" t="n">
+      <c r="N517" s="1" t="n">
         <v>45953</v>
       </c>
       <c r="O517" t="inlineStr">
@@ -51226,7 +51217,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N518" s="2" t="n">
+      <c r="N518" s="1" t="n">
         <v>45953</v>
       </c>
       <c r="O518" t="inlineStr">
@@ -51324,7 +51315,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N519" s="2" t="n">
+      <c r="N519" s="1" t="n">
         <v>45951</v>
       </c>
       <c r="O519" t="inlineStr">
@@ -51424,7 +51415,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N520" s="2" t="n">
+      <c r="N520" s="1" t="n">
         <v>43776</v>
       </c>
       <c r="O520" t="inlineStr">
@@ -51524,7 +51515,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N521" s="2" t="n">
+      <c r="N521" s="1" t="n">
         <v>45866</v>
       </c>
       <c r="O521" t="inlineStr">
@@ -51624,7 +51615,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N522" s="2" t="n">
+      <c r="N522" s="1" t="n">
         <v>45945</v>
       </c>
       <c r="O522" t="inlineStr">
@@ -51722,7 +51713,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N523" s="2" t="n">
+      <c r="N523" s="1" t="n">
         <v>45951</v>
       </c>
       <c r="O523" t="inlineStr">
@@ -51822,7 +51813,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N524" s="2" t="n">
+      <c r="N524" s="1" t="n">
         <v>45868</v>
       </c>
       <c r="O524" t="inlineStr">
@@ -51922,7 +51913,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N525" s="2" t="n">
+      <c r="N525" s="1" t="n">
         <v>45868</v>
       </c>
       <c r="O525" t="inlineStr">
@@ -52020,7 +52011,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N526" s="2" t="n">
+      <c r="N526" s="1" t="n">
         <v>45993</v>
       </c>
       <c r="O526" t="inlineStr">
@@ -52118,7 +52109,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N527" s="2" t="n">
+      <c r="N527" s="1" t="n">
         <v>45973</v>
       </c>
       <c r="O527" t="inlineStr">
@@ -52208,7 +52199,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N528" s="2" t="n">
+      <c r="N528" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="O528" t="inlineStr">
@@ -52298,7 +52289,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N529" s="2" t="n">
+      <c r="N529" s="1" t="n">
         <v>45609</v>
       </c>
       <c r="O529" t="inlineStr">
@@ -52388,7 +52379,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N530" s="2" t="n">
+      <c r="N530" s="1" t="n">
         <v>45245</v>
       </c>
       <c r="O530" t="inlineStr">
@@ -52478,7 +52469,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N531" s="2" t="n">
+      <c r="N531" s="1" t="n">
         <v>45441</v>
       </c>
       <c r="O531" t="inlineStr">
@@ -52576,7 +52567,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N532" s="2" t="n">
+      <c r="N532" s="1" t="n">
         <v>45883</v>
       </c>
       <c r="O532" t="inlineStr">
@@ -52674,7 +52665,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N533" s="2" t="n">
+      <c r="N533" s="1" t="n">
         <v>44774</v>
       </c>
       <c r="O533" t="inlineStr">
@@ -52772,7 +52763,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N534" s="2" t="n">
+      <c r="N534" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O534" t="inlineStr">
@@ -52862,7 +52853,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N535" s="2" t="n">
+      <c r="N535" s="1" t="n">
         <v>44153</v>
       </c>
       <c r="O535" t="inlineStr">
@@ -52960,7 +52951,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N536" s="2" t="n">
+      <c r="N536" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="O536" t="inlineStr">
@@ -53058,7 +53049,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N537" s="2" t="n">
+      <c r="N537" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="O537" t="inlineStr">
@@ -53156,7 +53147,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N538" s="2" t="n">
+      <c r="N538" s="1" t="n">
         <v>45992</v>
       </c>
       <c r="O538" t="inlineStr">
@@ -53246,7 +53237,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N539" s="2" t="n">
+      <c r="N539" s="1" t="n">
         <v>46037</v>
       </c>
       <c r="O539" t="inlineStr">
@@ -53344,7 +53335,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N540" s="2" t="n">
+      <c r="N540" s="1" t="n">
         <v>45980</v>
       </c>
       <c r="O540" t="inlineStr">
@@ -53442,7 +53433,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N541" s="2" t="n">
+      <c r="N541" s="1" t="n">
         <v>45980</v>
       </c>
       <c r="O541" t="inlineStr">
@@ -53540,7 +53531,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N542" s="2" t="n">
+      <c r="N542" s="1" t="n">
         <v>44281</v>
       </c>
       <c r="O542" t="inlineStr">
@@ -53638,7 +53629,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N543" s="2" t="n">
+      <c r="N543" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O543" t="inlineStr">
@@ -53736,7 +53727,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N544" s="2" t="n">
+      <c r="N544" s="1" t="n">
         <v>46042</v>
       </c>
       <c r="O544" t="inlineStr">
@@ -53834,7 +53825,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N545" s="2" t="n">
+      <c r="N545" s="1" t="n">
         <v>46042</v>
       </c>
       <c r="O545" t="inlineStr">
@@ -53924,7 +53915,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N546" s="2" t="n">
+      <c r="N546" s="1" t="n">
         <v>46100</v>
       </c>
       <c r="O546" t="inlineStr">
@@ -54022,7 +54013,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N547" s="2" t="n">
+      <c r="N547" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O547" t="inlineStr">
@@ -54120,7 +54111,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N548" s="2" t="n">
+      <c r="N548" s="1" t="n">
         <v>46006</v>
       </c>
       <c r="O548" t="inlineStr">
@@ -54220,7 +54211,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N549" s="2" t="n">
+      <c r="N549" s="1" t="n">
         <v>45481</v>
       </c>
       <c r="O549" t="inlineStr">
@@ -54318,7 +54309,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N550" s="2" t="n">
+      <c r="N550" s="1" t="n">
         <v>44365</v>
       </c>
       <c r="O550" t="inlineStr">
@@ -54416,7 +54407,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N551" s="2" t="n">
+      <c r="N551" s="1" t="n">
         <v>45966</v>
       </c>
       <c r="O551" t="inlineStr">
@@ -54514,7 +54505,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N552" s="2" t="n">
+      <c r="N552" s="1" t="n">
         <v>45966</v>
       </c>
       <c r="O552" t="inlineStr">
@@ -54612,7 +54603,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N553" s="2" t="n">
+      <c r="N553" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="O553" t="inlineStr">
@@ -54702,7 +54693,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N554" s="2" t="n">
+      <c r="N554" s="1" t="n">
         <v>45112</v>
       </c>
       <c r="O554" t="inlineStr">
@@ -54792,7 +54783,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N555" s="2" t="n">
+      <c r="N555" s="1" t="n">
         <v>41873</v>
       </c>
       <c r="O555" t="inlineStr">
@@ -54882,7 +54873,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N556" s="2" t="n">
+      <c r="N556" s="1" t="n">
         <v>41873</v>
       </c>
       <c r="O556" t="inlineStr">
@@ -54980,7 +54971,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N557" s="2" t="n">
+      <c r="N557" s="1" t="n">
         <v>45994</v>
       </c>
       <c r="O557" t="inlineStr">
@@ -55078,7 +55069,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N558" s="2" t="n">
+      <c r="N558" s="1" t="n">
         <v>45869</v>
       </c>
       <c r="O558" t="inlineStr">
@@ -55176,7 +55167,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N559" s="2" t="n">
+      <c r="N559" s="1" t="n">
         <v>45916</v>
       </c>
       <c r="O559" t="inlineStr">
@@ -55266,7 +55257,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N560" s="2" t="n">
+      <c r="N560" s="1" t="n">
         <v>46052</v>
       </c>
       <c r="O560" t="inlineStr">
@@ -55364,7 +55355,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N561" s="2" t="n">
+      <c r="N561" s="1" t="n">
         <v>45936</v>
       </c>
       <c r="O561" t="inlineStr">
@@ -55462,7 +55453,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N562" s="2" t="n">
+      <c r="N562" s="1" t="n">
         <v>45988</v>
       </c>
       <c r="O562" t="inlineStr">
@@ -55560,7 +55551,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N563" s="2" t="n">
+      <c r="N563" s="1" t="n">
         <v>45945</v>
       </c>
       <c r="O563" t="inlineStr">
@@ -55650,7 +55641,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N564" s="2" t="n">
+      <c r="N564" s="1" t="n">
         <v>46083</v>
       </c>
       <c r="O564" t="inlineStr">
@@ -55740,7 +55731,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N565" s="2" t="n">
+      <c r="N565" s="1" t="n">
         <v>46083</v>
       </c>
       <c r="O565" t="inlineStr">
@@ -55830,7 +55821,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N566" s="2" t="n">
+      <c r="N566" s="1" t="n">
         <v>46083</v>
       </c>
       <c r="O566" t="inlineStr">
@@ -55928,7 +55919,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N567" s="2" t="n">
+      <c r="N567" s="1" t="n">
         <v>46008</v>
       </c>
       <c r="O567" t="inlineStr">
@@ -56018,7 +56009,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N568" s="2" t="n">
+      <c r="N568" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="O568" t="inlineStr">
@@ -56116,7 +56107,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N569" s="2" t="n">
+      <c r="N569" s="1" t="n">
         <v>45960</v>
       </c>
       <c r="O569" t="inlineStr">
@@ -56206,7 +56197,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N570" s="2" t="n">
+      <c r="N570" s="1" t="n">
         <v>46083</v>
       </c>
       <c r="O570" t="inlineStr">
@@ -56304,7 +56295,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N571" s="2" t="n">
+      <c r="N571" s="1" t="n">
         <v>45972</v>
       </c>
       <c r="O571" t="inlineStr">
@@ -56402,7 +56393,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N572" s="2" t="n">
+      <c r="N572" s="1" t="n">
         <v>45986</v>
       </c>
       <c r="O572" t="inlineStr">
@@ -56441,6 +56432,104 @@
         </is>
       </c>
       <c r="V572" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>9945</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN UNIVERSITARIA DE BOGOTA -UNIVERSITARIA DE BOGOTÁ</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F573" t="n">
+        <v>118314</v>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN INTELIGENCIA ARTIFICIAL Y CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H573" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I573" t="n">
+        <v>153</v>
+      </c>
+      <c r="J573" t="n">
+        <v>10</v>
+      </c>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L573" t="n">
+        <v>7500000</v>
+      </c>
+      <c r="M573" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N573" s="2" t="n">
+        <v>45868</v>
+      </c>
+      <c r="O573" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P573" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q573" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R573" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S573" t="inlineStr"/>
+      <c r="T573" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="U573" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V573" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V573"/>
+  <dimension ref="A1:V576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56438,10 +56438,8 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>9945</t>
-        </is>
+      <c r="A573" t="n">
+        <v>9945</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
@@ -56495,7 +56493,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N573" s="2" t="n">
+      <c r="N573" s="1" t="n">
         <v>45868</v>
       </c>
       <c r="O573" t="inlineStr">
@@ -56530,6 +56528,286 @@
         </is>
       </c>
       <c r="V573" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA VISIÓN DE LAS AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F574" t="n">
+        <v>118523</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Terapia Respiratoria</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I574" t="n">
+        <v>157</v>
+      </c>
+      <c r="J574" t="n">
+        <v>9</v>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr"/>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N574" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>Terapias</t>
+        </is>
+      </c>
+      <c r="S574" t="inlineStr"/>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V574" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>4111</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DEL CARIBE</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr"/>
+      <c r="E575" t="inlineStr"/>
+      <c r="F575" t="n">
+        <v>118524</v>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>Administración en Seguridad y Salud en el Trabajo</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I575" t="n">
+        <v>164</v>
+      </c>
+      <c r="J575" t="n">
+        <v>10</v>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr"/>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N575" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr"/>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V575" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>9116</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CLARETIANA - UNICLARETIANA</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Chocó</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Quibdó</t>
+        </is>
+      </c>
+      <c r="F576" t="n">
+        <v>118531</v>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>Antropología</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I576" t="n">
+        <v>135</v>
+      </c>
+      <c r="J576" t="n">
+        <v>8</v>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr"/>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N576" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>Sociología, Antropología y estudios culturales</t>
+        </is>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>Antropología y  artes liberales</t>
+        </is>
+      </c>
+      <c r="S576" t="inlineStr"/>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>2026-04-13</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V576" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -56534,10 +56531,8 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>2747</t>
-        </is>
+      <c r="A574" t="n">
+        <v>2747</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>
@@ -56589,7 +56584,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N574" s="2" t="n">
+      <c r="N574" s="1" t="n">
         <v>45972</v>
       </c>
       <c r="O574" t="inlineStr">
@@ -56630,10 +56625,8 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>4111</t>
-        </is>
+      <c r="A575" t="n">
+        <v>4111</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
@@ -56677,7 +56670,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N575" s="2" t="n">
+      <c r="N575" s="1" t="n">
         <v>46106</v>
       </c>
       <c r="O575" t="inlineStr">
@@ -56718,10 +56711,8 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>9116</t>
-        </is>
+      <c r="A576" t="n">
+        <v>9116</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
@@ -56773,7 +56764,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N576" s="2" t="n">
+      <c r="N576" s="1" t="n">
         <v>45980</v>
       </c>
       <c r="O576" t="inlineStr">

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V576"/>
+  <dimension ref="A1:V578"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56804,6 +56807,182 @@
         </is>
       </c>
     </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>1824</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD METROPOLITANA</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr"/>
+      <c r="E577" t="inlineStr"/>
+      <c r="F577" t="n">
+        <v>118536</v>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>ENFERMERIA</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I577" t="n">
+        <v>160</v>
+      </c>
+      <c r="J577" t="n">
+        <v>8</v>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr"/>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N577" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S577" t="inlineStr"/>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V577" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>2827</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL META - UNIMETA</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr"/>
+      <c r="E578" t="inlineStr"/>
+      <c r="F578" t="n">
+        <v>118537</v>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I578" t="n">
+        <v>171</v>
+      </c>
+      <c r="J578" t="n">
+        <v>10</v>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr"/>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N578" s="2" t="n">
+        <v>44957</v>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S578" t="inlineStr"/>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>2026-04-16</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V578" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -56808,10 +56805,8 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>1824</t>
-        </is>
+      <c r="A577" t="n">
+        <v>1824</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
@@ -56855,7 +56850,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N577" s="2" t="n">
+      <c r="N577" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="O577" t="inlineStr">
@@ -56896,10 +56891,8 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>2827</t>
-        </is>
+      <c r="A578" t="n">
+        <v>2827</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
@@ -56943,7 +56936,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N578" s="2" t="n">
+      <c r="N578" s="1" t="n">
         <v>44957</v>
       </c>
       <c r="O578" t="inlineStr">

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V578"/>
+  <dimension ref="A1:V579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56976,6 +56979,102 @@
         </is>
       </c>
     </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2725</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>POLITECNICO GRANCOLOMBIANO</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F579" t="n">
+        <v>118540</v>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>PROFESIONAL EN CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I579" t="n">
+        <v>140</v>
+      </c>
+      <c r="J579" t="n">
+        <v>8</v>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr"/>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N579" s="2" t="n">
+        <v>45980</v>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>Estadística</t>
+        </is>
+      </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>Matemáticas, estadística y afines</t>
+        </is>
+      </c>
+      <c r="S579" t="inlineStr"/>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="V579" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V579"/>
+  <dimension ref="A1:V585"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56980,10 +56980,8 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
+      <c r="A579" t="n">
+        <v>2725</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
@@ -57035,7 +57033,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N579" s="2" t="n">
+      <c r="N579" s="1" t="n">
         <v>45980</v>
       </c>
       <c r="O579" t="inlineStr">
@@ -57070,6 +57068,566 @@
         </is>
       </c>
       <c r="V579" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA GUAJIRA</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr"/>
+      <c r="E580" t="inlineStr"/>
+      <c r="F580" t="n">
+        <v>118551</v>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Ingeniería en energías</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I580" t="n">
+        <v>155</v>
+      </c>
+      <c r="J580" t="n">
+        <v>9</v>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr"/>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N580" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>Electricidad y energía</t>
+        </is>
+      </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S580" t="inlineStr"/>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V580" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA GUAJIRA</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr"/>
+      <c r="E581" t="inlineStr"/>
+      <c r="F581" t="n">
+        <v>118550</v>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Licenciatura en Educación Artística</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I581" t="n">
+        <v>152</v>
+      </c>
+      <c r="J581" t="n">
+        <v>9</v>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr"/>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N581" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R581" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S581" t="inlineStr"/>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V581" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>1703</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INCCA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F582" t="n">
+        <v>118545</v>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Administracion de Empresas</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I582" t="n">
+        <v>141</v>
+      </c>
+      <c r="J582" t="n">
+        <v>9</v>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr"/>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N582" s="2" t="n">
+        <v>46015</v>
+      </c>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S582" t="inlineStr"/>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V582" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2702</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DE CIENCIAS DE LA SALUD</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F583" t="n">
+        <v>118541</v>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>Tecnología en Atención Prehospitalaria</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I583" t="n">
+        <v>118</v>
+      </c>
+      <c r="J583" t="n">
+        <v>6</v>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr"/>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N583" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q583" t="inlineStr">
+        <is>
+          <t>Salud no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R583" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S583" t="inlineStr"/>
+      <c r="T583" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V583" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>9131</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA CERVANTES SAN AGUSTÍN - UNICERVANTES</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F584" t="n">
+        <v>118548</v>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA EDUCATIVA</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I584" t="n">
+        <v>24</v>
+      </c>
+      <c r="J584" t="n">
+        <v>2</v>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr"/>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N584" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q584" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S584" t="inlineStr"/>
+      <c r="T584" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="U584" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V584" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>9131</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA CERVANTES SAN AGUSTÍN - UNICERVANTES</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Florencia</t>
+        </is>
+      </c>
+      <c r="F585" t="n">
+        <v>118546</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>Finanzas y Negocios Internacionales</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I585" t="n">
+        <v>134</v>
+      </c>
+      <c r="J585" t="n">
+        <v>8</v>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr"/>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N585" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q585" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R585" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S585" t="inlineStr"/>
+      <c r="T585" t="inlineStr">
+        <is>
+          <t>2026-04-20</t>
+        </is>
+      </c>
+      <c r="U585" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V585" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V585"/>
+  <dimension ref="A1:V586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57074,10 +57074,8 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A580" t="n">
+        <v>1218</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
@@ -57121,7 +57119,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N580" s="2" t="n">
+      <c r="N580" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="O580" t="inlineStr">
@@ -57162,10 +57160,8 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A581" t="n">
+        <v>1218</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
@@ -57209,7 +57205,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N581" s="2" t="n">
+      <c r="N581" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="O581" t="inlineStr">
@@ -57250,10 +57246,8 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>1703</t>
-        </is>
+      <c r="A582" t="n">
+        <v>1703</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
@@ -57305,7 +57299,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N582" s="2" t="n">
+      <c r="N582" s="1" t="n">
         <v>46015</v>
       </c>
       <c r="O582" t="inlineStr">
@@ -57346,10 +57340,8 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
+      <c r="A583" t="n">
+        <v>2702</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
@@ -57401,7 +57393,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N583" s="2" t="n">
+      <c r="N583" s="1" t="n">
         <v>46006</v>
       </c>
       <c r="O583" t="inlineStr">
@@ -57442,10 +57434,8 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t>9131</t>
-        </is>
+      <c r="A584" t="n">
+        <v>9131</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
@@ -57497,7 +57487,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N584" s="2" t="n">
+      <c r="N584" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="O584" t="inlineStr">
@@ -57538,10 +57528,8 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>9131</t>
-        </is>
+      <c r="A585" t="n">
+        <v>9131</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
@@ -57593,7 +57581,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N585" s="2" t="n">
+      <c r="N585" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="O585" t="inlineStr">
@@ -57628,6 +57616,102 @@
         </is>
       </c>
       <c r="V585" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA - ITM</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F586" t="n">
+        <v>118556</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>Diseño para la Comunicación Interactiva</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I586" t="n">
+        <v>130</v>
+      </c>
+      <c r="J586" t="n">
+        <v>8</v>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr"/>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N586" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q586" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R586" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S586" t="inlineStr"/>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>2026-04-21</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V586" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V586"/>
+  <dimension ref="A1:V587"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57622,10 +57622,8 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
+      <c r="A586" t="n">
+        <v>3302</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
@@ -57677,7 +57675,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N586" s="2" t="n">
+      <c r="N586" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O586" t="inlineStr">
@@ -57712,6 +57710,94 @@
         </is>
       </c>
       <c r="V586" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>1709</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD CENTRAL</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr"/>
+      <c r="E587" t="inlineStr"/>
+      <c r="F587" t="n">
+        <v>115818</v>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>INGENIERIA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I587" t="n">
+        <v>135</v>
+      </c>
+      <c r="J587" t="n">
+        <v>8</v>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr"/>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N587" s="2" t="n">
+        <v>44636</v>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q587" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R587" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S587" t="inlineStr"/>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V587" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V573"/>
+  <dimension ref="A1:V574"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56438,10 +56435,8 @@
       </c>
     </row>
     <row r="573">
-      <c r="A573" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
+      <c r="A573" t="n">
+        <v>2847</v>
       </c>
       <c r="B573" t="inlineStr">
         <is>
@@ -56493,7 +56488,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N573" s="2" t="n">
+      <c r="N573" s="1" t="n">
         <v>45987</v>
       </c>
       <c r="O573" t="inlineStr">
@@ -56528,6 +56523,92 @@
         </is>
       </c>
       <c r="V573" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>1104</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr"/>
+      <c r="E574" t="inlineStr"/>
+      <c r="F574" t="n">
+        <v>118575</v>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>Farmacia</t>
+        </is>
+      </c>
+      <c r="H574" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I574" t="n">
+        <v>185</v>
+      </c>
+      <c r="J574" t="n">
+        <v>10</v>
+      </c>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L574" t="inlineStr"/>
+      <c r="M574" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N574" t="inlineStr"/>
+      <c r="O574" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P574" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q574" t="inlineStr">
+        <is>
+          <t>Farmacia</t>
+        </is>
+      </c>
+      <c r="R574" t="inlineStr">
+        <is>
+          <t>Optometría, otros programas de ciencias de la salud</t>
+        </is>
+      </c>
+      <c r="S574" t="inlineStr"/>
+      <c r="T574" t="inlineStr">
+        <is>
+          <t>2026-04-25</t>
+        </is>
+      </c>
+      <c r="U574" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V574" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -56529,10 +56529,8 @@
       </c>
     </row>
     <row r="574">
-      <c r="A574" t="inlineStr">
-        <is>
-          <t>1104</t>
-        </is>
+      <c r="A574" t="n">
+        <v>1104</v>
       </c>
       <c r="B574" t="inlineStr">
         <is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V574"/>
+  <dimension ref="A1:V575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56612,6 +56615,102 @@
         </is>
       </c>
     </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>3710</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA ANTONIO DE AREVALO - UNITECNAR</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F575" t="n">
+        <v>118577</v>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="H575" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I575" t="n">
+        <v>149</v>
+      </c>
+      <c r="J575" t="n">
+        <v>9</v>
+      </c>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L575" t="inlineStr"/>
+      <c r="M575" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N575" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="O575" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P575" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q575" t="inlineStr">
+        <is>
+          <t>Formación para docentes con asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R575" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S575" t="inlineStr"/>
+      <c r="T575" t="inlineStr">
+        <is>
+          <t>2026-04-29</t>
+        </is>
+      </c>
+      <c r="U575" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V575" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V575"/>
+  <dimension ref="A1:V576"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56616,10 +56616,8 @@
       </c>
     </row>
     <row r="575">
-      <c r="A575" t="inlineStr">
-        <is>
-          <t>3710</t>
-        </is>
+      <c r="A575" t="n">
+        <v>3710</v>
       </c>
       <c r="B575" t="inlineStr">
         <is>
@@ -56671,7 +56669,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N575" s="2" t="n">
+      <c r="N575" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="O575" t="inlineStr">
@@ -56706,6 +56704,102 @@
         </is>
       </c>
       <c r="V575" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>2713</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA LOS LIBERTADORES</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F576" t="n">
+        <v>118581</v>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>Cultura Física, Deporte y Recreación</t>
+        </is>
+      </c>
+      <c r="H576" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I576" t="n">
+        <v>144</v>
+      </c>
+      <c r="J576" t="n">
+        <v>8</v>
+      </c>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L576" t="inlineStr"/>
+      <c r="M576" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N576" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="O576" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P576" t="inlineStr">
+        <is>
+          <t>Bienestar</t>
+        </is>
+      </c>
+      <c r="Q576" t="inlineStr">
+        <is>
+          <t>Bienestar no clasificado en otra parte</t>
+        </is>
+      </c>
+      <c r="R576" t="inlineStr">
+        <is>
+          <t>Deportes, educación física y recreación</t>
+        </is>
+      </c>
+      <c r="S576" t="inlineStr"/>
+      <c r="T576" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="U576" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V576" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V576"/>
+  <dimension ref="A1:V579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56710,10 +56710,8 @@
       </c>
     </row>
     <row r="576">
-      <c r="A576" t="inlineStr">
-        <is>
-          <t>2713</t>
-        </is>
+      <c r="A576" t="n">
+        <v>2713</v>
       </c>
       <c r="B576" t="inlineStr">
         <is>
@@ -56765,7 +56763,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N576" s="2" t="n">
+      <c r="N576" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="O576" t="inlineStr">
@@ -56800,6 +56798,286 @@
         </is>
       </c>
       <c r="V576" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>1111</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD TECNOLOGICA DE PEREIRA - UTP</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>Risaralda</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>Mistrató</t>
+        </is>
+      </c>
+      <c r="F577" t="n">
+        <v>117690</v>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN EDUCACIÓN BÁSICA PRIMARIA</t>
+        </is>
+      </c>
+      <c r="H577" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I577" t="n">
+        <v>153</v>
+      </c>
+      <c r="J577" t="n">
+        <v>8</v>
+      </c>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L577" t="inlineStr"/>
+      <c r="M577" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N577" s="2" t="n">
+        <v>44165</v>
+      </c>
+      <c r="O577" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P577" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q577" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R577" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S577" t="inlineStr"/>
+      <c r="T577" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="U577" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V577" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CALDAS</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F578" t="n">
+        <v>118588</v>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>Geografía</t>
+        </is>
+      </c>
+      <c r="H578" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I578" t="n">
+        <v>137</v>
+      </c>
+      <c r="J578" t="n">
+        <v>8</v>
+      </c>
+      <c r="K578" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L578" t="inlineStr"/>
+      <c r="M578" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N578" s="2" t="n">
+        <v>46006</v>
+      </c>
+      <c r="O578" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P578" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q578" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R578" t="inlineStr">
+        <is>
+          <t>Geografía, historia</t>
+        </is>
+      </c>
+      <c r="S578" t="inlineStr"/>
+      <c r="T578" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="U578" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V578" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>2728</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DEL AREA ANDINA</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr"/>
+      <c r="E579" t="inlineStr"/>
+      <c r="F579" t="n">
+        <v>118583</v>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>Terapia Respiratoria</t>
+        </is>
+      </c>
+      <c r="H579" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I579" t="n">
+        <v>160</v>
+      </c>
+      <c r="J579" t="n">
+        <v>8</v>
+      </c>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L579" t="inlineStr"/>
+      <c r="M579" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N579" s="2" t="n">
+        <v>46027</v>
+      </c>
+      <c r="O579" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P579" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q579" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R579" t="inlineStr">
+        <is>
+          <t>Terapias</t>
+        </is>
+      </c>
+      <c r="S579" t="inlineStr"/>
+      <c r="T579" t="inlineStr">
+        <is>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="U579" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V579" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -56804,10 +56801,8 @@
       </c>
     </row>
     <row r="577">
-      <c r="A577" t="inlineStr">
-        <is>
-          <t>1111</t>
-        </is>
+      <c r="A577" t="n">
+        <v>1111</v>
       </c>
       <c r="B577" t="inlineStr">
         <is>
@@ -56859,7 +56854,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N577" s="2" t="n">
+      <c r="N577" s="1" t="n">
         <v>44165</v>
       </c>
       <c r="O577" t="inlineStr">
@@ -56900,10 +56895,8 @@
       </c>
     </row>
     <row r="578">
-      <c r="A578" t="inlineStr">
-        <is>
-          <t>1112</t>
-        </is>
+      <c r="A578" t="n">
+        <v>1112</v>
       </c>
       <c r="B578" t="inlineStr">
         <is>
@@ -56955,7 +56948,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N578" s="2" t="n">
+      <c r="N578" s="1" t="n">
         <v>46006</v>
       </c>
       <c r="O578" t="inlineStr">
@@ -56996,10 +56989,8 @@
       </c>
     </row>
     <row r="579">
-      <c r="A579" t="inlineStr">
-        <is>
-          <t>2728</t>
-        </is>
+      <c r="A579" t="n">
+        <v>2728</v>
       </c>
       <c r="B579" t="inlineStr">
         <is>
@@ -57043,7 +57034,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N579" s="2" t="n">
+      <c r="N579" s="1" t="n">
         <v>46027</v>
       </c>
       <c r="O579" t="inlineStr">

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -16,9 +16,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +51,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V579"/>
+  <dimension ref="A1:V593"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57074,6 +57077,1344 @@
         </is>
       </c>
     </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F580" t="n">
+        <v>118621</v>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>CIENCIA POLÍTICA</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I580" t="n">
+        <v>125</v>
+      </c>
+      <c r="J580" t="n">
+        <v>8</v>
+      </c>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L580" t="inlineStr"/>
+      <c r="M580" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N580" t="inlineStr"/>
+      <c r="O580" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q580" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R580" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S580" t="inlineStr"/>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V580" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>1103</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F581" t="n">
+        <v>118622</v>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN FILOLOGÍA E IDIOMAS - INGLÉS</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I581" t="n">
+        <v>149</v>
+      </c>
+      <c r="J581" t="n">
+        <v>8</v>
+      </c>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L581" t="inlineStr"/>
+      <c r="M581" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N581" t="inlineStr"/>
+      <c r="O581" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>Idiomas</t>
+        </is>
+      </c>
+      <c r="Q581" t="inlineStr">
+        <is>
+          <t>Literatura y lingüística</t>
+        </is>
+      </c>
+      <c r="R581" t="inlineStr">
+        <is>
+          <t>Lenguas modernas, literatura, linguística y afines</t>
+        </is>
+      </c>
+      <c r="S581" t="inlineStr"/>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>Instituto de Idiomas</t>
+        </is>
+      </c>
+      <c r="V581" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>1126</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>Archipiélago de San Andrés, Providencia y Santa Catalina</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>San Andrés</t>
+        </is>
+      </c>
+      <c r="F582" t="n">
+        <v>118623</v>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>OCEANOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I582" t="n">
+        <v>155</v>
+      </c>
+      <c r="J582" t="n">
+        <v>10</v>
+      </c>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L582" t="inlineStr"/>
+      <c r="M582" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N582" t="inlineStr"/>
+      <c r="O582" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>Ciencias físicas</t>
+        </is>
+      </c>
+      <c r="Q582" t="inlineStr">
+        <is>
+          <t>Ciencias físicas no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R582" t="inlineStr">
+        <is>
+          <t>Geología, otros programas de ciencias naturales</t>
+        </is>
+      </c>
+      <c r="S582" t="inlineStr"/>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="V582" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F583" t="n">
+        <v>118615</v>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN EDUCACIÓN INFANTIL</t>
+        </is>
+      </c>
+      <c r="H583" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I583" t="n">
+        <v>144</v>
+      </c>
+      <c r="J583" t="n">
+        <v>8</v>
+      </c>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L583" t="inlineStr"/>
+      <c r="M583" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N583" s="2" t="n">
+        <v>45160</v>
+      </c>
+      <c r="O583" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P583" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q583" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R583" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S583" t="inlineStr"/>
+      <c r="T583" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U583" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V583" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>2830</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA IBEROAMERICANA</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F584" t="n">
+        <v>118602</v>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN EDUCACIÓN ESPECIAL</t>
+        </is>
+      </c>
+      <c r="H584" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I584" t="n">
+        <v>144</v>
+      </c>
+      <c r="J584" t="n">
+        <v>8</v>
+      </c>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L584" t="inlineStr"/>
+      <c r="M584" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N584" s="2" t="n">
+        <v>46003</v>
+      </c>
+      <c r="O584" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P584" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q584" t="inlineStr">
+        <is>
+          <t>Formación para docentes sin asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R584" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S584" t="inlineStr"/>
+      <c r="T584" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U584" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V584" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F585" t="n">
+        <v>118611</v>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>ECONOMÍA</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I585" t="n">
+        <v>136</v>
+      </c>
+      <c r="J585" t="n">
+        <v>8</v>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr"/>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N585" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P585" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q585" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="R585" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S585" t="inlineStr"/>
+      <c r="T585" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U585" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V585" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F586" t="n">
+        <v>118612</v>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I586" t="n">
+        <v>145</v>
+      </c>
+      <c r="J586" t="n">
+        <v>8</v>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr"/>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N586" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P586" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q586" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R586" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S586" t="inlineStr"/>
+      <c r="T586" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U586" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V586" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>2850</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA ANTONIO JOSE DE SUCRE - CORPOSUCRE</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>Sucre</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>Sincelejo</t>
+        </is>
+      </c>
+      <c r="F587" t="n">
+        <v>118618</v>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN MATEMÁTICAS</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I587" t="n">
+        <v>149</v>
+      </c>
+      <c r="J587" t="n">
+        <v>9</v>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr"/>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N587" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P587" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q587" t="inlineStr">
+        <is>
+          <t>Formación para docentes con asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R587" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S587" t="inlineStr"/>
+      <c r="T587" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U587" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V587" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>UNIDADES TECNOLOGICAS DE SANTANDER</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F588" t="n">
+        <v>118607</v>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS TURÍSTICAS Y HOTELERAS</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I588" t="n">
+        <v>174</v>
+      </c>
+      <c r="J588" t="n">
+        <v>10</v>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr"/>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N588" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P588" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q588" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R588" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S588" t="inlineStr"/>
+      <c r="T588" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U588" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V588" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F589" t="n">
+        <v>118608</v>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I589" t="n">
+        <v>136</v>
+      </c>
+      <c r="J589" t="n">
+        <v>8</v>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr"/>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N589" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P589" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q589" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R589" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S589" t="inlineStr"/>
+      <c r="T589" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U589" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V589" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>3817</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AUTONOMA DE NARIÑO -AUNAR-</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F590" t="n">
+        <v>118619</v>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>DISEÑO VISUAL</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I590" t="n">
+        <v>136</v>
+      </c>
+      <c r="J590" t="n">
+        <v>8</v>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr"/>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N590" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P590" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q590" t="inlineStr">
+        <is>
+          <t>Bellas artes</t>
+        </is>
+      </c>
+      <c r="R590" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S590" t="inlineStr"/>
+      <c r="T590" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U590" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V590" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA TALLER CINCO CENTRO DE DISEÑO</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F591" t="n">
+        <v>118603</v>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I591" t="n">
+        <v>136</v>
+      </c>
+      <c r="J591" t="n">
+        <v>8</v>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr"/>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N591" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P591" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q591" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R591" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S591" t="inlineStr"/>
+      <c r="T591" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U591" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V591" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA TALLER CINCO CENTRO DE DISEÑO</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F592" t="n">
+        <v>118604</v>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I592" t="n">
+        <v>136</v>
+      </c>
+      <c r="J592" t="n">
+        <v>8</v>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr"/>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N592" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P592" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q592" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R592" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S592" t="inlineStr"/>
+      <c r="T592" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U592" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V592" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE ASTURIAS</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F593" t="n">
+        <v>118617</v>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>LENGUAS MODERNAS</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I593" t="n">
+        <v>144</v>
+      </c>
+      <c r="J593" t="n">
+        <v>8</v>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr"/>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N593" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P593" t="inlineStr">
+        <is>
+          <t>Idiomas</t>
+        </is>
+      </c>
+      <c r="Q593" t="inlineStr">
+        <is>
+          <t>Adquisición del lenguaje</t>
+        </is>
+      </c>
+      <c r="R593" t="inlineStr">
+        <is>
+          <t>Lenguas modernas, literatura, linguística y afines</t>
+        </is>
+      </c>
+      <c r="S593" t="inlineStr"/>
+      <c r="T593" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="U593" t="inlineStr">
+        <is>
+          <t>Instituto de Idiomas</t>
+        </is>
+      </c>
+      <c r="V593" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V593"/>
+  <dimension ref="A1:V609"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57078,10 +57078,8 @@
       </c>
     </row>
     <row r="580">
-      <c r="A580" t="inlineStr">
-        <is>
-          <t>1103</t>
-        </is>
+      <c r="A580" t="n">
+        <v>1103</v>
       </c>
       <c r="B580" t="inlineStr">
         <is>
@@ -57172,10 +57170,8 @@
       </c>
     </row>
     <row r="581">
-      <c r="A581" t="inlineStr">
-        <is>
-          <t>1103</t>
-        </is>
+      <c r="A581" t="n">
+        <v>1103</v>
       </c>
       <c r="B581" t="inlineStr">
         <is>
@@ -57266,10 +57262,8 @@
       </c>
     </row>
     <row r="582">
-      <c r="A582" t="inlineStr">
-        <is>
-          <t>1126</t>
-        </is>
+      <c r="A582" t="n">
+        <v>1126</v>
       </c>
       <c r="B582" t="inlineStr">
         <is>
@@ -57360,10 +57354,8 @@
       </c>
     </row>
     <row r="583">
-      <c r="A583" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A583" t="n">
+        <v>2829</v>
       </c>
       <c r="B583" t="inlineStr">
         <is>
@@ -57415,7 +57407,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N583" s="2" t="n">
+      <c r="N583" s="1" t="n">
         <v>45160</v>
       </c>
       <c r="O583" t="inlineStr">
@@ -57456,10 +57448,8 @@
       </c>
     </row>
     <row r="584">
-      <c r="A584" t="inlineStr">
-        <is>
-          <t>2830</t>
-        </is>
+      <c r="A584" t="n">
+        <v>2830</v>
       </c>
       <c r="B584" t="inlineStr">
         <is>
@@ -57511,7 +57501,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N584" s="2" t="n">
+      <c r="N584" s="1" t="n">
         <v>46003</v>
       </c>
       <c r="O584" t="inlineStr">
@@ -57552,10 +57542,8 @@
       </c>
     </row>
     <row r="585">
-      <c r="A585" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A585" t="n">
+        <v>2832</v>
       </c>
       <c r="B585" t="inlineStr">
         <is>
@@ -57607,7 +57595,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N585" s="2" t="n">
+      <c r="N585" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O585" t="inlineStr">
@@ -57648,10 +57636,8 @@
       </c>
     </row>
     <row r="586">
-      <c r="A586" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A586" t="n">
+        <v>2832</v>
       </c>
       <c r="B586" t="inlineStr">
         <is>
@@ -57703,7 +57689,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N586" s="2" t="n">
+      <c r="N586" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O586" t="inlineStr">
@@ -57744,10 +57730,8 @@
       </c>
     </row>
     <row r="587">
-      <c r="A587" t="inlineStr">
-        <is>
-          <t>2850</t>
-        </is>
+      <c r="A587" t="n">
+        <v>2850</v>
       </c>
       <c r="B587" t="inlineStr">
         <is>
@@ -57799,7 +57783,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N587" s="2" t="n">
+      <c r="N587" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O587" t="inlineStr">
@@ -57840,10 +57824,8 @@
       </c>
     </row>
     <row r="588">
-      <c r="A588" t="inlineStr">
-        <is>
-          <t>3201</t>
-        </is>
+      <c r="A588" t="n">
+        <v>3201</v>
       </c>
       <c r="B588" t="inlineStr">
         <is>
@@ -57895,7 +57877,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N588" s="2" t="n">
+      <c r="N588" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O588" t="inlineStr">
@@ -57936,10 +57918,8 @@
       </c>
     </row>
     <row r="589">
-      <c r="A589" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
+      <c r="A589" t="n">
+        <v>3204</v>
       </c>
       <c r="B589" t="inlineStr">
         <is>
@@ -57991,7 +57971,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N589" s="2" t="n">
+      <c r="N589" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O589" t="inlineStr">
@@ -58032,10 +58012,8 @@
       </c>
     </row>
     <row r="590">
-      <c r="A590" t="inlineStr">
-        <is>
-          <t>3817</t>
-        </is>
+      <c r="A590" t="n">
+        <v>3817</v>
       </c>
       <c r="B590" t="inlineStr">
         <is>
@@ -58087,7 +58065,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N590" s="2" t="n">
+      <c r="N590" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O590" t="inlineStr">
@@ -58128,10 +58106,8 @@
       </c>
     </row>
     <row r="591">
-      <c r="A591" t="inlineStr">
-        <is>
-          <t>4835</t>
-        </is>
+      <c r="A591" t="n">
+        <v>4835</v>
       </c>
       <c r="B591" t="inlineStr">
         <is>
@@ -58183,7 +58159,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N591" s="2" t="n">
+      <c r="N591" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="O591" t="inlineStr">
@@ -58224,10 +58200,8 @@
       </c>
     </row>
     <row r="592">
-      <c r="A592" t="inlineStr">
-        <is>
-          <t>4835</t>
-        </is>
+      <c r="A592" t="n">
+        <v>4835</v>
       </c>
       <c r="B592" t="inlineStr">
         <is>
@@ -58279,7 +58253,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N592" s="2" t="n">
+      <c r="N592" s="1" t="n">
         <v>46022</v>
       </c>
       <c r="O592" t="inlineStr">
@@ -58320,10 +58294,8 @@
       </c>
     </row>
     <row r="593">
-      <c r="A593" t="inlineStr">
-        <is>
-          <t>9913</t>
-        </is>
+      <c r="A593" t="n">
+        <v>9913</v>
       </c>
       <c r="B593" t="inlineStr">
         <is>
@@ -58375,7 +58347,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N593" s="2" t="n">
+      <c r="N593" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O593" t="inlineStr">
@@ -58410,6 +58382,1542 @@
         </is>
       </c>
       <c r="V593" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA GUAJIRA</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="F594" t="n">
+        <v>118676</v>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>INGENIERÍA AGROINDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I594" t="n">
+        <v>175</v>
+      </c>
+      <c r="J594" t="n">
+        <v>9</v>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr"/>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N594" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P594" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q594" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R594" t="inlineStr">
+        <is>
+          <t>Ingeniería agroindustrial, alimentos y afines</t>
+        </is>
+      </c>
+      <c r="S594" t="inlineStr"/>
+      <c r="T594" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U594" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V594" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA GUAJIRA</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="F595" t="n">
+        <v>118675</v>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN CIENCIAS SOCIALES</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I595" t="n">
+        <v>131</v>
+      </c>
+      <c r="J595" t="n">
+        <v>8</v>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr"/>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N595" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P595" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q595" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R595" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S595" t="inlineStr"/>
+      <c r="T595" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U595" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V595" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>1218</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LA GUAJIRA</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>Fonseca</t>
+        </is>
+      </c>
+      <c r="F596" t="n">
+        <v>118677</v>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN ESPAÑOL Y HUMANIDADES</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I596" t="n">
+        <v>142</v>
+      </c>
+      <c r="J596" t="n">
+        <v>8</v>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr"/>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N596" s="2" t="n">
+        <v>46135</v>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P596" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q596" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R596" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S596" t="inlineStr"/>
+      <c r="T596" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U596" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V596" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>1828</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ICESI</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F597" t="n">
+        <v>118680</v>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>DISEÑO E INNOVACIÓN</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I597" t="n">
+        <v>129</v>
+      </c>
+      <c r="J597" t="n">
+        <v>8</v>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr"/>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N597" s="2" t="n">
+        <v>44778</v>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P597" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q597" t="inlineStr">
+        <is>
+          <t>Diseño industrial, de moda e interiores</t>
+        </is>
+      </c>
+      <c r="R597" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S597" t="inlineStr"/>
+      <c r="T597" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U597" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+      <c r="V597" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2710</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA MONSERRATE -UNIMONSERRATE</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F598" t="n">
+        <v>118646</v>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>LENGUAS Y CULTURA</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I598" t="n">
+        <v>144</v>
+      </c>
+      <c r="J598" t="n">
+        <v>8</v>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr"/>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N598" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P598" t="inlineStr">
+        <is>
+          <t>Idiomas</t>
+        </is>
+      </c>
+      <c r="Q598" t="inlineStr">
+        <is>
+          <t>Adquisición del lenguaje</t>
+        </is>
+      </c>
+      <c r="R598" t="inlineStr">
+        <is>
+          <t>Lenguas modernas, literatura, linguística y afines</t>
+        </is>
+      </c>
+      <c r="S598" t="inlineStr"/>
+      <c r="T598" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U598" t="inlineStr">
+        <is>
+          <t>Instituto de Idiomas</t>
+        </is>
+      </c>
+      <c r="V598" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2825</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA RAFAEL NUÑEZ</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F599" t="n">
+        <v>118632</v>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I599" t="n">
+        <v>160</v>
+      </c>
+      <c r="J599" t="n">
+        <v>8</v>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr"/>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N599" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P599" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q599" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R599" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S599" t="inlineStr"/>
+      <c r="T599" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U599" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V599" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2833</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA REMINGTON</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F600" t="n">
+        <v>118660</v>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>DISEÑO DE ESPACIOS Y ENTORNOS VIRTUALES</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I600" t="n">
+        <v>144</v>
+      </c>
+      <c r="J600" t="n">
+        <v>8</v>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr"/>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>Bimestral</t>
+        </is>
+      </c>
+      <c r="N600" s="2" t="n">
+        <v>46024</v>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P600" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q600" t="inlineStr">
+        <is>
+          <t>Diseño industrial, de moda e interiores</t>
+        </is>
+      </c>
+      <c r="R600" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S600" t="inlineStr"/>
+      <c r="T600" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U600" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+      <c r="V600" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2834</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>UNIVERSITARIA AGUSTINIANA- UNIAGUSTINIANA</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F601" t="n">
+        <v>118637</v>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>TEOLOGIA</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I601" t="n">
+        <v>136</v>
+      </c>
+      <c r="J601" t="n">
+        <v>8</v>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr"/>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N601" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P601" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="Q601" t="inlineStr">
+        <is>
+          <t>Religión y Teología</t>
+        </is>
+      </c>
+      <c r="R601" t="inlineStr">
+        <is>
+          <t>Filosofía, teología y afines</t>
+        </is>
+      </c>
+      <c r="S601" t="inlineStr"/>
+      <c r="T601" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U601" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V601" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>3117</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DE BARRANQUILLA - IUB</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F602" t="n">
+        <v>118655</v>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I602" t="n">
+        <v>165</v>
+      </c>
+      <c r="J602" t="n">
+        <v>13</v>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr"/>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N602" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="O602" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P602" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q602" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R602" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S602" t="inlineStr"/>
+      <c r="T602" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U602" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V602" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA ANTONIO JOSE CAMACHO</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F603" t="n">
+        <v>118681</v>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>MERCADEO Y PUBLICIDAD</t>
+        </is>
+      </c>
+      <c r="H603" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I603" t="n">
+        <v>139</v>
+      </c>
+      <c r="J603" t="n">
+        <v>8</v>
+      </c>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L603" t="inlineStr"/>
+      <c r="M603" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N603" s="2" t="n">
+        <v>46133</v>
+      </c>
+      <c r="O603" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P603" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q603" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R603" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S603" t="inlineStr"/>
+      <c r="T603" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U603" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V603" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>4108</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr">
+        <is>
+          <t>ESCUELA TECNOLOGICA INSTITUTO TECNICO CENTRAL</t>
+        </is>
+      </c>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F604" t="n">
+        <v>118658</v>
+      </c>
+      <c r="G604" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN ENERGÍAS RENOVABLES</t>
+        </is>
+      </c>
+      <c r="H604" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I604" t="n">
+        <v>168</v>
+      </c>
+      <c r="J604" t="n">
+        <v>10</v>
+      </c>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L604" t="inlineStr"/>
+      <c r="M604" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N604" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O604" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P604" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q604" t="inlineStr">
+        <is>
+          <t>Electricidad y energía</t>
+        </is>
+      </c>
+      <c r="R604" t="inlineStr">
+        <is>
+          <t>Ingeniería eléctrica y afines</t>
+        </is>
+      </c>
+      <c r="S604" t="inlineStr"/>
+      <c r="T604" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U604" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V604" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>4726</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA SAN MATEO - SAN MATEO EDUCACION SUPERIOR</t>
+        </is>
+      </c>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F605" t="n">
+        <v>118654</v>
+      </c>
+      <c r="G605" t="inlineStr">
+        <is>
+          <t>CONTADURIA PUBLICA</t>
+        </is>
+      </c>
+      <c r="H605" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I605" t="n">
+        <v>140</v>
+      </c>
+      <c r="J605" t="n">
+        <v>8</v>
+      </c>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L605" t="inlineStr"/>
+      <c r="M605" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N605" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O605" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P605" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q605" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R605" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S605" t="inlineStr"/>
+      <c r="T605" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U605" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V605" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ECCI</t>
+        </is>
+      </c>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F606" t="n">
+        <v>118635</v>
+      </c>
+      <c r="G606" t="inlineStr">
+        <is>
+          <t>DISEÑO DIGITAL</t>
+        </is>
+      </c>
+      <c r="H606" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I606" t="n">
+        <v>145</v>
+      </c>
+      <c r="J606" t="n">
+        <v>9</v>
+      </c>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L606" t="inlineStr"/>
+      <c r="M606" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N606" s="2" t="n">
+        <v>45965</v>
+      </c>
+      <c r="O606" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P606" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q606" t="inlineStr">
+        <is>
+          <t>Bellas artes</t>
+        </is>
+      </c>
+      <c r="R606" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S606" t="inlineStr"/>
+      <c r="T606" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U606" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V606" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ECCI</t>
+        </is>
+      </c>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F607" t="n">
+        <v>118636</v>
+      </c>
+      <c r="G607" t="inlineStr">
+        <is>
+          <t>DISEÑO GRÁFICO</t>
+        </is>
+      </c>
+      <c r="H607" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I607" t="n">
+        <v>138</v>
+      </c>
+      <c r="J607" t="n">
+        <v>8</v>
+      </c>
+      <c r="K607" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L607" t="inlineStr"/>
+      <c r="M607" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N607" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O607" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P607" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q607" t="inlineStr">
+        <is>
+          <t>Bellas artes</t>
+        </is>
+      </c>
+      <c r="R607" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S607" t="inlineStr"/>
+      <c r="T607" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U607" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V607" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE ASTURIAS</t>
+        </is>
+      </c>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F608" t="n">
+        <v>118663</v>
+      </c>
+      <c r="G608" t="inlineStr">
+        <is>
+          <t>COMUNICACIÓN Y DISEÑO PUBLICITARIO</t>
+        </is>
+      </c>
+      <c r="H608" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I608" t="n">
+        <v>153</v>
+      </c>
+      <c r="J608" t="n">
+        <v>10</v>
+      </c>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L608" t="inlineStr"/>
+      <c r="M608" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N608" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O608" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P608" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q608" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R608" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S608" t="inlineStr"/>
+      <c r="T608" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U608" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V608" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>9939</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA CATÓLICA DEL CARIBE</t>
+        </is>
+      </c>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F609" t="n">
+        <v>118640</v>
+      </c>
+      <c r="G609" t="inlineStr">
+        <is>
+          <t>TEOLOGÍA</t>
+        </is>
+      </c>
+      <c r="H609" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I609" t="n">
+        <v>128</v>
+      </c>
+      <c r="J609" t="n">
+        <v>8</v>
+      </c>
+      <c r="K609" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L609" t="inlineStr"/>
+      <c r="M609" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N609" s="2" t="n">
+        <v>46037</v>
+      </c>
+      <c r="O609" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P609" t="inlineStr">
+        <is>
+          <t>Humanidades (Excepto idiomas)</t>
+        </is>
+      </c>
+      <c r="Q609" t="inlineStr">
+        <is>
+          <t>Religión y Teología</t>
+        </is>
+      </c>
+      <c r="R609" t="inlineStr">
+        <is>
+          <t>Filosofía, teología y afines</t>
+        </is>
+      </c>
+      <c r="S609" t="inlineStr"/>
+      <c r="T609" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="U609" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V609" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V609"/>
+  <dimension ref="A1:V628"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58388,10 +58388,8 @@
       </c>
     </row>
     <row r="594">
-      <c r="A594" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A594" t="n">
+        <v>1218</v>
       </c>
       <c r="B594" t="inlineStr">
         <is>
@@ -58443,7 +58441,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N594" s="2" t="n">
+      <c r="N594" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O594" t="inlineStr">
@@ -58484,10 +58482,8 @@
       </c>
     </row>
     <row r="595">
-      <c r="A595" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A595" t="n">
+        <v>1218</v>
       </c>
       <c r="B595" t="inlineStr">
         <is>
@@ -58539,7 +58535,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N595" s="2" t="n">
+      <c r="N595" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="O595" t="inlineStr">
@@ -58580,10 +58576,8 @@
       </c>
     </row>
     <row r="596">
-      <c r="A596" t="inlineStr">
-        <is>
-          <t>1218</t>
-        </is>
+      <c r="A596" t="n">
+        <v>1218</v>
       </c>
       <c r="B596" t="inlineStr">
         <is>
@@ -58635,7 +58629,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N596" s="2" t="n">
+      <c r="N596" s="1" t="n">
         <v>46135</v>
       </c>
       <c r="O596" t="inlineStr">
@@ -58676,10 +58670,8 @@
       </c>
     </row>
     <row r="597">
-      <c r="A597" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A597" t="n">
+        <v>1828</v>
       </c>
       <c r="B597" t="inlineStr">
         <is>
@@ -58731,7 +58723,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N597" s="2" t="n">
+      <c r="N597" s="1" t="n">
         <v>44778</v>
       </c>
       <c r="O597" t="inlineStr">
@@ -58772,10 +58764,8 @@
       </c>
     </row>
     <row r="598">
-      <c r="A598" t="inlineStr">
-        <is>
-          <t>2710</t>
-        </is>
+      <c r="A598" t="n">
+        <v>2710</v>
       </c>
       <c r="B598" t="inlineStr">
         <is>
@@ -58827,7 +58817,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N598" s="2" t="n">
+      <c r="N598" s="1" t="n">
         <v>46037</v>
       </c>
       <c r="O598" t="inlineStr">
@@ -58868,10 +58858,8 @@
       </c>
     </row>
     <row r="599">
-      <c r="A599" t="inlineStr">
-        <is>
-          <t>2825</t>
-        </is>
+      <c r="A599" t="n">
+        <v>2825</v>
       </c>
       <c r="B599" t="inlineStr">
         <is>
@@ -58923,7 +58911,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N599" s="2" t="n">
+      <c r="N599" s="1" t="n">
         <v>45988</v>
       </c>
       <c r="O599" t="inlineStr">
@@ -58964,10 +58952,8 @@
       </c>
     </row>
     <row r="600">
-      <c r="A600" t="inlineStr">
-        <is>
-          <t>2833</t>
-        </is>
+      <c r="A600" t="n">
+        <v>2833</v>
       </c>
       <c r="B600" t="inlineStr">
         <is>
@@ -59019,7 +59005,7 @@
           <t>Bimestral</t>
         </is>
       </c>
-      <c r="N600" s="2" t="n">
+      <c r="N600" s="1" t="n">
         <v>46024</v>
       </c>
       <c r="O600" t="inlineStr">
@@ -59060,10 +59046,8 @@
       </c>
     </row>
     <row r="601">
-      <c r="A601" t="inlineStr">
-        <is>
-          <t>2834</t>
-        </is>
+      <c r="A601" t="n">
+        <v>2834</v>
       </c>
       <c r="B601" t="inlineStr">
         <is>
@@ -59115,7 +59099,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N601" s="2" t="n">
+      <c r="N601" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O601" t="inlineStr">
@@ -59156,10 +59140,8 @@
       </c>
     </row>
     <row r="602">
-      <c r="A602" t="inlineStr">
-        <is>
-          <t>3117</t>
-        </is>
+      <c r="A602" t="n">
+        <v>3117</v>
       </c>
       <c r="B602" t="inlineStr">
         <is>
@@ -59211,7 +59193,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N602" s="2" t="n">
+      <c r="N602" s="1" t="n">
         <v>46149</v>
       </c>
       <c r="O602" t="inlineStr">
@@ -59252,10 +59234,8 @@
       </c>
     </row>
     <row r="603">
-      <c r="A603" t="inlineStr">
-        <is>
-          <t>3301</t>
-        </is>
+      <c r="A603" t="n">
+        <v>3301</v>
       </c>
       <c r="B603" t="inlineStr">
         <is>
@@ -59307,7 +59287,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N603" s="2" t="n">
+      <c r="N603" s="1" t="n">
         <v>46133</v>
       </c>
       <c r="O603" t="inlineStr">
@@ -59348,10 +59328,8 @@
       </c>
     </row>
     <row r="604">
-      <c r="A604" t="inlineStr">
-        <is>
-          <t>4108</t>
-        </is>
+      <c r="A604" t="n">
+        <v>4108</v>
       </c>
       <c r="B604" t="inlineStr">
         <is>
@@ -59403,7 +59381,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N604" s="2" t="n">
+      <c r="N604" s="1" t="n">
         <v>46118</v>
       </c>
       <c r="O604" t="inlineStr">
@@ -59444,10 +59422,8 @@
       </c>
     </row>
     <row r="605">
-      <c r="A605" t="inlineStr">
-        <is>
-          <t>4726</t>
-        </is>
+      <c r="A605" t="n">
+        <v>4726</v>
       </c>
       <c r="B605" t="inlineStr">
         <is>
@@ -59499,7 +59475,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N605" s="2" t="n">
+      <c r="N605" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O605" t="inlineStr">
@@ -59540,10 +59516,8 @@
       </c>
     </row>
     <row r="606">
-      <c r="A606" t="inlineStr">
-        <is>
-          <t>5802</t>
-        </is>
+      <c r="A606" t="n">
+        <v>5802</v>
       </c>
       <c r="B606" t="inlineStr">
         <is>
@@ -59595,7 +59569,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N606" s="2" t="n">
+      <c r="N606" s="1" t="n">
         <v>45965</v>
       </c>
       <c r="O606" t="inlineStr">
@@ -59636,10 +59610,8 @@
       </c>
     </row>
     <row r="607">
-      <c r="A607" t="inlineStr">
-        <is>
-          <t>5802</t>
-        </is>
+      <c r="A607" t="n">
+        <v>5802</v>
       </c>
       <c r="B607" t="inlineStr">
         <is>
@@ -59691,7 +59663,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N607" s="2" t="n">
+      <c r="N607" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O607" t="inlineStr">
@@ -59732,10 +59704,8 @@
       </c>
     </row>
     <row r="608">
-      <c r="A608" t="inlineStr">
-        <is>
-          <t>9913</t>
-        </is>
+      <c r="A608" t="n">
+        <v>9913</v>
       </c>
       <c r="B608" t="inlineStr">
         <is>
@@ -59787,7 +59757,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N608" s="2" t="n">
+      <c r="N608" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O608" t="inlineStr">
@@ -59828,10 +59798,8 @@
       </c>
     </row>
     <row r="609">
-      <c r="A609" t="inlineStr">
-        <is>
-          <t>9939</t>
-        </is>
+      <c r="A609" t="n">
+        <v>9939</v>
       </c>
       <c r="B609" t="inlineStr">
         <is>
@@ -59883,7 +59851,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N609" s="2" t="n">
+      <c r="N609" s="1" t="n">
         <v>46037</v>
       </c>
       <c r="O609" t="inlineStr">
@@ -59918,6 +59886,1830 @@
         </is>
       </c>
       <c r="V609" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INDUSTRIAL DE SANTANDER</t>
+        </is>
+      </c>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr">
+        <is>
+          <t>Socorro</t>
+        </is>
+      </c>
+      <c r="F610" t="n">
+        <v>118698</v>
+      </c>
+      <c r="G610" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS TURÍSTICAS Y HOTELERAS</t>
+        </is>
+      </c>
+      <c r="H610" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I610" t="n">
+        <v>128</v>
+      </c>
+      <c r="J610" t="n">
+        <v>8</v>
+      </c>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L610" t="inlineStr"/>
+      <c r="M610" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N610" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O610" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P610" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q610" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R610" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S610" t="inlineStr"/>
+      <c r="T610" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U610" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V610" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F611" t="n">
+        <v>118687</v>
+      </c>
+      <c r="G611" t="inlineStr">
+        <is>
+          <t>DISEÑO</t>
+        </is>
+      </c>
+      <c r="H611" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I611" t="n">
+        <v>125</v>
+      </c>
+      <c r="J611" t="n">
+        <v>8</v>
+      </c>
+      <c r="K611" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L611" t="inlineStr"/>
+      <c r="M611" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N611" s="2" t="n">
+        <v>46030</v>
+      </c>
+      <c r="O611" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P611" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q611" t="inlineStr">
+        <is>
+          <t>Artes no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R611" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S611" t="inlineStr"/>
+      <c r="T611" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U611" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V611" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>1829</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="F612" t="n">
+        <v>118741</v>
+      </c>
+      <c r="G612" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN LENGUAS EXTRANJERAS CON ÉNFASIS EN INGLÉS</t>
+        </is>
+      </c>
+      <c r="H612" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I612" t="n">
+        <v>148</v>
+      </c>
+      <c r="J612" t="n">
+        <v>10</v>
+      </c>
+      <c r="K612" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L612" t="inlineStr"/>
+      <c r="M612" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N612" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="O612" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P612" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q612" t="inlineStr">
+        <is>
+          <t>Formación para docentes con asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R612" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S612" t="inlineStr"/>
+      <c r="T612" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U612" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V612" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>1829</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr">
+        <is>
+          <t>Palmira</t>
+        </is>
+      </c>
+      <c r="F613" t="n">
+        <v>118740</v>
+      </c>
+      <c r="G613" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN LENGUAS EXTRANJERAS CON ÉNFASIS EN INGLÉS</t>
+        </is>
+      </c>
+      <c r="H613" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I613" t="n">
+        <v>148</v>
+      </c>
+      <c r="J613" t="n">
+        <v>10</v>
+      </c>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L613" t="inlineStr"/>
+      <c r="M613" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N613" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="O613" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P613" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q613" t="inlineStr">
+        <is>
+          <t>Formación para docentes con asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R613" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S613" t="inlineStr"/>
+      <c r="T613" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U613" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V613" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2712</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA KONRAD LORENZ</t>
+        </is>
+      </c>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F614" t="n">
+        <v>118732</v>
+      </c>
+      <c r="G614" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN EN SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H614" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I614" t="n">
+        <v>144</v>
+      </c>
+      <c r="J614" t="n">
+        <v>9</v>
+      </c>
+      <c r="K614" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="L614" t="inlineStr"/>
+      <c r="M614" t="inlineStr">
+        <is>
+          <t>Cuatrimestral</t>
+        </is>
+      </c>
+      <c r="N614" s="2" t="n">
+        <v>45972</v>
+      </c>
+      <c r="O614" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="P614" t="inlineStr">
+        <is>
+          <t>Servicios de higiene y salud ocupacional</t>
+        </is>
+      </c>
+      <c r="Q614" t="inlineStr">
+        <is>
+          <t>Salud y protección laboral</t>
+        </is>
+      </c>
+      <c r="R614" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S614" t="inlineStr"/>
+      <c r="T614" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U614" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V614" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CATOLICA LUMEN GENTIUM - UNICATÓLICA - CALI</t>
+        </is>
+      </c>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F615" t="n">
+        <v>118737</v>
+      </c>
+      <c r="G615" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H615" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I615" t="n">
+        <v>138</v>
+      </c>
+      <c r="J615" t="n">
+        <v>8</v>
+      </c>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L615" t="inlineStr"/>
+      <c r="M615" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N615" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="O615" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P615" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q615" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R615" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S615" t="inlineStr"/>
+      <c r="T615" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U615" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V615" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>2731</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CATOLICA LUMEN GENTIUM - UNICATÓLICA - CALI</t>
+        </is>
+      </c>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F616" t="n">
+        <v>118749</v>
+      </c>
+      <c r="G616" t="inlineStr">
+        <is>
+          <t>CONTADURÍA PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H616" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I616" t="n">
+        <v>138</v>
+      </c>
+      <c r="J616" t="n">
+        <v>8</v>
+      </c>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L616" t="inlineStr"/>
+      <c r="M616" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N616" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="O616" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P616" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q616" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R616" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S616" t="inlineStr"/>
+      <c r="T616" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U616" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V616" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EIA</t>
+        </is>
+      </c>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F617" t="n">
+        <v>118722</v>
+      </c>
+      <c r="G617" t="inlineStr">
+        <is>
+          <t>INTELIGENCIA DE NEGOCIOS Y ANALÍTICA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H617" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I617" t="n">
+        <v>139</v>
+      </c>
+      <c r="J617" t="n">
+        <v>8</v>
+      </c>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L617" t="inlineStr"/>
+      <c r="M617" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N617" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O617" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P617" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q617" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R617" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S617" t="inlineStr"/>
+      <c r="T617" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U617" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V617" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F618" t="n">
+        <v>118699</v>
+      </c>
+      <c r="G618" t="inlineStr">
+        <is>
+          <t>CONTADURIA PUBLICA</t>
+        </is>
+      </c>
+      <c r="H618" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I618" t="n">
+        <v>143</v>
+      </c>
+      <c r="J618" t="n">
+        <v>9</v>
+      </c>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L618" t="inlineStr"/>
+      <c r="M618" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N618" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O618" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P618" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q618" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R618" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S618" t="inlineStr"/>
+      <c r="T618" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U618" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V618" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F619" t="n">
+        <v>118691</v>
+      </c>
+      <c r="G619" t="inlineStr">
+        <is>
+          <t>PROFESIONAL EN GASTRONOMÍA</t>
+        </is>
+      </c>
+      <c r="H619" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I619" t="n">
+        <v>136</v>
+      </c>
+      <c r="J619" t="n">
+        <v>8</v>
+      </c>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L619" t="inlineStr"/>
+      <c r="M619" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N619" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O619" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="P619" t="inlineStr">
+        <is>
+          <t>Servicios personales</t>
+        </is>
+      </c>
+      <c r="Q619" t="inlineStr">
+        <is>
+          <t>Hotelería, restaurantes y servicios de banquetes</t>
+        </is>
+      </c>
+      <c r="R619" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S619" t="inlineStr"/>
+      <c r="T619" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U619" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V619" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F620" t="n">
+        <v>118692</v>
+      </c>
+      <c r="G620" t="inlineStr">
+        <is>
+          <t>PROFESIONAL EN GASTRONOMÍA</t>
+        </is>
+      </c>
+      <c r="H620" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I620" t="n">
+        <v>136</v>
+      </c>
+      <c r="J620" t="n">
+        <v>8</v>
+      </c>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L620" t="inlineStr"/>
+      <c r="M620" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N620" s="2" t="n">
+        <v>46029</v>
+      </c>
+      <c r="O620" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="P620" t="inlineStr">
+        <is>
+          <t>Servicios personales</t>
+        </is>
+      </c>
+      <c r="Q620" t="inlineStr">
+        <is>
+          <t>Hotelería, restaurantes y servicios de banquetes</t>
+        </is>
+      </c>
+      <c r="R620" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S620" t="inlineStr"/>
+      <c r="T620" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U620" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V620" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>2829</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA MINUTO DE DIOS -UNIMINUTO-</t>
+        </is>
+      </c>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr">
+        <is>
+          <t>Fusagasugá</t>
+        </is>
+      </c>
+      <c r="F621" t="n">
+        <v>118753</v>
+      </c>
+      <c r="G621" t="inlineStr">
+        <is>
+          <t>TRABAJO SOCIAL</t>
+        </is>
+      </c>
+      <c r="H621" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I621" t="n">
+        <v>144</v>
+      </c>
+      <c r="J621" t="n">
+        <v>8</v>
+      </c>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L621" t="inlineStr"/>
+      <c r="M621" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N621" s="2" t="n">
+        <v>44131</v>
+      </c>
+      <c r="O621" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P621" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q621" t="inlineStr">
+        <is>
+          <t>Trabajo social</t>
+        </is>
+      </c>
+      <c r="R621" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S621" t="inlineStr"/>
+      <c r="T621" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U621" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V621" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="F622" t="n">
+        <v>118762</v>
+      </c>
+      <c r="G622" t="inlineStr">
+        <is>
+          <t>ENFERMERÍA</t>
+        </is>
+      </c>
+      <c r="H622" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I622" t="n">
+        <v>164</v>
+      </c>
+      <c r="J622" t="n">
+        <v>8</v>
+      </c>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L622" t="inlineStr"/>
+      <c r="M622" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N622" s="2" t="n">
+        <v>46013</v>
+      </c>
+      <c r="O622" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P622" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q622" t="inlineStr">
+        <is>
+          <t>Enfermería y partería</t>
+        </is>
+      </c>
+      <c r="R622" t="inlineStr">
+        <is>
+          <t>Enfermería</t>
+        </is>
+      </c>
+      <c r="S622" t="inlineStr"/>
+      <c r="T622" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U622" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V622" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>3103</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA MAYOR DE CARTAGENA</t>
+        </is>
+      </c>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F623" t="n">
+        <v>118711</v>
+      </c>
+      <c r="G623" t="inlineStr">
+        <is>
+          <t>TRABAJO SOCIAL</t>
+        </is>
+      </c>
+      <c r="H623" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I623" t="n">
+        <v>138</v>
+      </c>
+      <c r="J623" t="n">
+        <v>9</v>
+      </c>
+      <c r="K623" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L623" t="inlineStr"/>
+      <c r="M623" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N623" s="2" t="n">
+        <v>46009</v>
+      </c>
+      <c r="O623" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P623" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q623" t="inlineStr">
+        <is>
+          <t>Trabajo social</t>
+        </is>
+      </c>
+      <c r="R623" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S623" t="inlineStr"/>
+      <c r="T623" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U623" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V623" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>3204</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr">
+        <is>
+          <t>TECNOLOGICO DE ANTIOQUIA</t>
+        </is>
+      </c>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr">
+        <is>
+          <t>Anorí</t>
+        </is>
+      </c>
+      <c r="F624" t="n">
+        <v>118751</v>
+      </c>
+      <c r="G624" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H624" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I624" t="n">
+        <v>148</v>
+      </c>
+      <c r="J624" t="n">
+        <v>9</v>
+      </c>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L624" t="inlineStr"/>
+      <c r="M624" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N624" s="2" t="n">
+        <v>45650</v>
+      </c>
+      <c r="O624" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P624" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q624" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R624" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S624" t="inlineStr"/>
+      <c r="T624" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U624" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V624" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>4817</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr">
+        <is>
+          <t>CORPORACION DE EDUCACIÓN SUPERIOR DEL LITORAL</t>
+        </is>
+      </c>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F625" t="n">
+        <v>118760</v>
+      </c>
+      <c r="G625" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H625" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I625" t="n">
+        <v>136</v>
+      </c>
+      <c r="J625" t="n">
+        <v>8</v>
+      </c>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L625" t="inlineStr"/>
+      <c r="M625" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N625" s="2" t="n">
+        <v>46021</v>
+      </c>
+      <c r="O625" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P625" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q625" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R625" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S625" t="inlineStr"/>
+      <c r="T625" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U625" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V625" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>5801</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr">
+        <is>
+          <t>CORPORACION ESCUELA TECNOLOGICA DEL ORIENTE</t>
+        </is>
+      </c>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F626" t="n">
+        <v>118755</v>
+      </c>
+      <c r="G626" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN INTELIGENCIA DE NEGOCIOS Y ANALÍTICA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H626" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I626" t="n">
+        <v>24</v>
+      </c>
+      <c r="J626" t="n">
+        <v>2</v>
+      </c>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L626" t="inlineStr"/>
+      <c r="M626" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N626" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O626" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="Q626" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="R626" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S626" t="inlineStr"/>
+      <c r="T626" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U626" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="V626" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>5801</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr">
+        <is>
+          <t>CORPORACION ESCUELA TECNOLOGICA DEL ORIENTE</t>
+        </is>
+      </c>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F627" t="n">
+        <v>118713</v>
+      </c>
+      <c r="G627" t="inlineStr">
+        <is>
+          <t>SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H627" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I627" t="n">
+        <v>155</v>
+      </c>
+      <c r="J627" t="n">
+        <v>9</v>
+      </c>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L627" t="inlineStr"/>
+      <c r="M627" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N627" s="2" t="n">
+        <v>45951</v>
+      </c>
+      <c r="O627" t="inlineStr">
+        <is>
+          <t>Servicios</t>
+        </is>
+      </c>
+      <c r="P627" t="inlineStr">
+        <is>
+          <t>Servicios de higiene y salud ocupacional</t>
+        </is>
+      </c>
+      <c r="Q627" t="inlineStr">
+        <is>
+          <t>Salud y protección laboral</t>
+        </is>
+      </c>
+      <c r="R627" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S627" t="inlineStr"/>
+      <c r="T627" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U627" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V627" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>9943</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr">
+        <is>
+          <t>Villavicencio</t>
+        </is>
+      </c>
+      <c r="F628" t="n">
+        <v>118710</v>
+      </c>
+      <c r="G628" t="inlineStr">
+        <is>
+          <t>PROFESIONAL EN LENGUAS EXTRANJERAS</t>
+        </is>
+      </c>
+      <c r="H628" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I628" t="n">
+        <v>132</v>
+      </c>
+      <c r="J628" t="n">
+        <v>8</v>
+      </c>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L628" t="inlineStr"/>
+      <c r="M628" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N628" s="2" t="n">
+        <v>46007</v>
+      </c>
+      <c r="O628" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P628" t="inlineStr">
+        <is>
+          <t>Idiomas</t>
+        </is>
+      </c>
+      <c r="Q628" t="inlineStr">
+        <is>
+          <t>Adquisición del lenguaje</t>
+        </is>
+      </c>
+      <c r="R628" t="inlineStr">
+        <is>
+          <t>Lenguas modernas, literatura, linguística y afines</t>
+        </is>
+      </c>
+      <c r="S628" t="inlineStr"/>
+      <c r="T628" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="U628" t="inlineStr">
+        <is>
+          <t>Instituto de Idiomas</t>
+        </is>
+      </c>
+      <c r="V628" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V628"/>
+  <dimension ref="A1:V643"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59892,10 +59892,8 @@
       </c>
     </row>
     <row r="610">
-      <c r="A610" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
+      <c r="A610" t="n">
+        <v>1204</v>
       </c>
       <c r="B610" t="inlineStr">
         <is>
@@ -59947,7 +59945,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N610" s="2" t="n">
+      <c r="N610" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O610" t="inlineStr">
@@ -59988,10 +59986,8 @@
       </c>
     </row>
     <row r="611">
-      <c r="A611" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A611" t="n">
+        <v>1823</v>
       </c>
       <c r="B611" t="inlineStr">
         <is>
@@ -60043,7 +60039,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N611" s="2" t="n">
+      <c r="N611" s="1" t="n">
         <v>46030</v>
       </c>
       <c r="O611" t="inlineStr">
@@ -60084,10 +60080,8 @@
       </c>
     </row>
     <row r="612">
-      <c r="A612" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
+      <c r="A612" t="n">
+        <v>1829</v>
       </c>
       <c r="B612" t="inlineStr">
         <is>
@@ -60139,7 +60133,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N612" s="2" t="n">
+      <c r="N612" s="1" t="n">
         <v>46083</v>
       </c>
       <c r="O612" t="inlineStr">
@@ -60180,10 +60174,8 @@
       </c>
     </row>
     <row r="613">
-      <c r="A613" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
+      <c r="A613" t="n">
+        <v>1829</v>
       </c>
       <c r="B613" t="inlineStr">
         <is>
@@ -60235,7 +60227,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N613" s="2" t="n">
+      <c r="N613" s="1" t="n">
         <v>46083</v>
       </c>
       <c r="O613" t="inlineStr">
@@ -60276,10 +60268,8 @@
       </c>
     </row>
     <row r="614">
-      <c r="A614" t="inlineStr">
-        <is>
-          <t>2712</t>
-        </is>
+      <c r="A614" t="n">
+        <v>2712</v>
       </c>
       <c r="B614" t="inlineStr">
         <is>
@@ -60331,7 +60321,7 @@
           <t>Cuatrimestral</t>
         </is>
       </c>
-      <c r="N614" s="2" t="n">
+      <c r="N614" s="1" t="n">
         <v>45972</v>
       </c>
       <c r="O614" t="inlineStr">
@@ -60372,10 +60362,8 @@
       </c>
     </row>
     <row r="615">
-      <c r="A615" t="inlineStr">
-        <is>
-          <t>2731</t>
-        </is>
+      <c r="A615" t="n">
+        <v>2731</v>
       </c>
       <c r="B615" t="inlineStr">
         <is>
@@ -60427,7 +60415,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N615" s="2" t="n">
+      <c r="N615" s="1" t="n">
         <v>46080</v>
       </c>
       <c r="O615" t="inlineStr">
@@ -60468,10 +60456,8 @@
       </c>
     </row>
     <row r="616">
-      <c r="A616" t="inlineStr">
-        <is>
-          <t>2731</t>
-        </is>
+      <c r="A616" t="n">
+        <v>2731</v>
       </c>
       <c r="B616" t="inlineStr">
         <is>
@@ -60523,7 +60509,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N616" s="2" t="n">
+      <c r="N616" s="1" t="n">
         <v>46097</v>
       </c>
       <c r="O616" t="inlineStr">
@@ -60564,10 +60550,8 @@
       </c>
     </row>
     <row r="617">
-      <c r="A617" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
+      <c r="A617" t="n">
+        <v>2813</v>
       </c>
       <c r="B617" t="inlineStr">
         <is>
@@ -60619,7 +60603,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N617" s="2" t="n">
+      <c r="N617" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O617" t="inlineStr">
@@ -60660,10 +60644,8 @@
       </c>
     </row>
     <row r="618">
-      <c r="A618" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A618" t="n">
+        <v>2829</v>
       </c>
       <c r="B618" t="inlineStr">
         <is>
@@ -60715,7 +60697,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N618" s="2" t="n">
+      <c r="N618" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O618" t="inlineStr">
@@ -60756,10 +60738,8 @@
       </c>
     </row>
     <row r="619">
-      <c r="A619" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A619" t="n">
+        <v>2829</v>
       </c>
       <c r="B619" t="inlineStr">
         <is>
@@ -60811,7 +60791,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N619" s="2" t="n">
+      <c r="N619" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O619" t="inlineStr">
@@ -60852,10 +60832,8 @@
       </c>
     </row>
     <row r="620">
-      <c r="A620" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A620" t="n">
+        <v>2829</v>
       </c>
       <c r="B620" t="inlineStr">
         <is>
@@ -60907,7 +60885,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N620" s="2" t="n">
+      <c r="N620" s="1" t="n">
         <v>46029</v>
       </c>
       <c r="O620" t="inlineStr">
@@ -60948,10 +60926,8 @@
       </c>
     </row>
     <row r="621">
-      <c r="A621" t="inlineStr">
-        <is>
-          <t>2829</t>
-        </is>
+      <c r="A621" t="n">
+        <v>2829</v>
       </c>
       <c r="B621" t="inlineStr">
         <is>
@@ -61003,7 +60979,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N621" s="2" t="n">
+      <c r="N621" s="1" t="n">
         <v>44131</v>
       </c>
       <c r="O621" t="inlineStr">
@@ -61044,10 +61020,8 @@
       </c>
     </row>
     <row r="622">
-      <c r="A622" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A622" t="n">
+        <v>2832</v>
       </c>
       <c r="B622" t="inlineStr">
         <is>
@@ -61099,7 +61073,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N622" s="2" t="n">
+      <c r="N622" s="1" t="n">
         <v>46013</v>
       </c>
       <c r="O622" t="inlineStr">
@@ -61140,10 +61114,8 @@
       </c>
     </row>
     <row r="623">
-      <c r="A623" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
+      <c r="A623" t="n">
+        <v>3103</v>
       </c>
       <c r="B623" t="inlineStr">
         <is>
@@ -61195,7 +61167,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N623" s="2" t="n">
+      <c r="N623" s="1" t="n">
         <v>46009</v>
       </c>
       <c r="O623" t="inlineStr">
@@ -61236,10 +61208,8 @@
       </c>
     </row>
     <row r="624">
-      <c r="A624" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
+      <c r="A624" t="n">
+        <v>3204</v>
       </c>
       <c r="B624" t="inlineStr">
         <is>
@@ -61291,7 +61261,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N624" s="2" t="n">
+      <c r="N624" s="1" t="n">
         <v>45650</v>
       </c>
       <c r="O624" t="inlineStr">
@@ -61332,10 +61302,8 @@
       </c>
     </row>
     <row r="625">
-      <c r="A625" t="inlineStr">
-        <is>
-          <t>4817</t>
-        </is>
+      <c r="A625" t="n">
+        <v>4817</v>
       </c>
       <c r="B625" t="inlineStr">
         <is>
@@ -61387,7 +61355,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N625" s="2" t="n">
+      <c r="N625" s="1" t="n">
         <v>46021</v>
       </c>
       <c r="O625" t="inlineStr">
@@ -61428,10 +61396,8 @@
       </c>
     </row>
     <row r="626">
-      <c r="A626" t="inlineStr">
-        <is>
-          <t>5801</t>
-        </is>
+      <c r="A626" t="n">
+        <v>5801</v>
       </c>
       <c r="B626" t="inlineStr">
         <is>
@@ -61483,7 +61449,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N626" s="2" t="n">
+      <c r="N626" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O626" t="inlineStr">
@@ -61524,10 +61490,8 @@
       </c>
     </row>
     <row r="627">
-      <c r="A627" t="inlineStr">
-        <is>
-          <t>5801</t>
-        </is>
+      <c r="A627" t="n">
+        <v>5801</v>
       </c>
       <c r="B627" t="inlineStr">
         <is>
@@ -61579,7 +61543,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N627" s="2" t="n">
+      <c r="N627" s="1" t="n">
         <v>45951</v>
       </c>
       <c r="O627" t="inlineStr">
@@ -61620,10 +61584,8 @@
       </c>
     </row>
     <row r="628">
-      <c r="A628" t="inlineStr">
-        <is>
-          <t>9943</t>
-        </is>
+      <c r="A628" t="n">
+        <v>9943</v>
       </c>
       <c r="B628" t="inlineStr">
         <is>
@@ -61675,7 +61637,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N628" s="2" t="n">
+      <c r="N628" s="1" t="n">
         <v>46007</v>
       </c>
       <c r="O628" t="inlineStr">
@@ -61710,6 +61672,1448 @@
         </is>
       </c>
       <c r="V628" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>1729</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD EL BOSQUE</t>
+        </is>
+      </c>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F629" t="n">
+        <v>118809</v>
+      </c>
+      <c r="G629" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN INTELIGENCIA DE NEGOCIOS</t>
+        </is>
+      </c>
+      <c r="H629" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I629" t="n">
+        <v>144</v>
+      </c>
+      <c r="J629" t="n">
+        <v>9</v>
+      </c>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L629" t="n">
+        <v>7990000</v>
+      </c>
+      <c r="M629" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N629" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O629" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P629" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q629" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R629" t="inlineStr">
+        <is>
+          <t>Otras ingenierías</t>
+        </is>
+      </c>
+      <c r="S629" t="inlineStr"/>
+      <c r="T629" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U629" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V629" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>2209</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr">
+        <is>
+          <t>POLITECNICO COLOMBIANO JAIME ISAZA CADAVID</t>
+        </is>
+      </c>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F630" t="n">
+        <v>118717</v>
+      </c>
+      <c r="G630" t="inlineStr">
+        <is>
+          <t>DISEÑO AUDIOVISUAL</t>
+        </is>
+      </c>
+      <c r="H630" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I630" t="n">
+        <v>130</v>
+      </c>
+      <c r="J630" t="n">
+        <v>8</v>
+      </c>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L630" t="inlineStr"/>
+      <c r="M630" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N630" s="2" t="n">
+        <v>46002</v>
+      </c>
+      <c r="O630" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P630" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q630" t="inlineStr">
+        <is>
+          <t>Diseño industrial, de moda e interiores</t>
+        </is>
+      </c>
+      <c r="R630" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S630" t="inlineStr"/>
+      <c r="T630" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U630" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+      <c r="V630" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>2828</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL HUILA-CORHUILA-</t>
+        </is>
+      </c>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F631" t="n">
+        <v>118807</v>
+      </c>
+      <c r="G631" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H631" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I631" t="n">
+        <v>149</v>
+      </c>
+      <c r="J631" t="n">
+        <v>9</v>
+      </c>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L631" t="inlineStr"/>
+      <c r="M631" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N631" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O631" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P631" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q631" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R631" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S631" t="inlineStr"/>
+      <c r="T631" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U631" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V631" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>2828</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL HUILA-CORHUILA-</t>
+        </is>
+      </c>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F632" t="n">
+        <v>118808</v>
+      </c>
+      <c r="G632" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H632" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I632" t="n">
+        <v>149</v>
+      </c>
+      <c r="J632" t="n">
+        <v>9</v>
+      </c>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L632" t="inlineStr"/>
+      <c r="M632" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N632" s="2" t="n">
+        <v>46111</v>
+      </c>
+      <c r="O632" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P632" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q632" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R632" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S632" t="inlineStr"/>
+      <c r="T632" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U632" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V632" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>2847</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE INVESTIGACION Y DESARROLLO - UDI</t>
+        </is>
+      </c>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F633" t="n">
+        <v>118771</v>
+      </c>
+      <c r="G633" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN LITERATURA Y LENGUA CASTELLANA</t>
+        </is>
+      </c>
+      <c r="H633" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I633" t="n">
+        <v>140</v>
+      </c>
+      <c r="J633" t="n">
+        <v>8</v>
+      </c>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L633" t="inlineStr"/>
+      <c r="M633" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N633" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="O633" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P633" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q633" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R633" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S633" t="inlineStr"/>
+      <c r="T633" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U633" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V633" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>2847</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE INVESTIGACION Y DESARROLLO - UDI</t>
+        </is>
+      </c>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F634" t="n">
+        <v>118772</v>
+      </c>
+      <c r="G634" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN LITERATURA Y LENGUA CASTELLANA</t>
+        </is>
+      </c>
+      <c r="H634" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I634" t="n">
+        <v>140</v>
+      </c>
+      <c r="J634" t="n">
+        <v>8</v>
+      </c>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L634" t="inlineStr"/>
+      <c r="M634" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N634" s="2" t="n">
+        <v>45993</v>
+      </c>
+      <c r="O634" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P634" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q634" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R634" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S634" t="inlineStr"/>
+      <c r="T634" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U634" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V634" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>4817</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr">
+        <is>
+          <t>CORPORACION DE EDUCACIÓN SUPERIOR DEL LITORAL</t>
+        </is>
+      </c>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F635" t="n">
+        <v>118769</v>
+      </c>
+      <c r="G635" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN EN SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H635" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I635" t="n">
+        <v>136</v>
+      </c>
+      <c r="J635" t="n">
+        <v>8</v>
+      </c>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L635" t="inlineStr"/>
+      <c r="M635" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N635" s="2" t="n">
+        <v>45988</v>
+      </c>
+      <c r="O635" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P635" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q635" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R635" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S635" t="inlineStr"/>
+      <c r="T635" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U635" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V635" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>9904</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA COLOMBO GERMANA</t>
+        </is>
+      </c>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F636" t="n">
+        <v>118634</v>
+      </c>
+      <c r="G636" t="inlineStr">
+        <is>
+          <t>DISEÑO GRÁFICO Y MULTIMEDIA</t>
+        </is>
+      </c>
+      <c r="H636" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I636" t="n">
+        <v>144</v>
+      </c>
+      <c r="J636" t="n">
+        <v>8</v>
+      </c>
+      <c r="K636" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L636" t="inlineStr"/>
+      <c r="M636" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N636" s="2" t="n">
+        <v>46008</v>
+      </c>
+      <c r="O636" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P636" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q636" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R636" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S636" t="inlineStr"/>
+      <c r="T636" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U636" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V636" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>9913</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DE ASTURIAS</t>
+        </is>
+      </c>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F637" t="n">
+        <v>118777</v>
+      </c>
+      <c r="G637" t="inlineStr">
+        <is>
+          <t>TRABAJO SOCIAL</t>
+        </is>
+      </c>
+      <c r="H637" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I637" t="n">
+        <v>136</v>
+      </c>
+      <c r="J637" t="n">
+        <v>8</v>
+      </c>
+      <c r="K637" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L637" t="inlineStr"/>
+      <c r="M637" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N637" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="O637" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P637" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q637" t="inlineStr">
+        <is>
+          <t>Trabajo social</t>
+        </is>
+      </c>
+      <c r="R637" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S637" t="inlineStr"/>
+      <c r="T637" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U637" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V637" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>9940</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE SANTA MARTA</t>
+        </is>
+      </c>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F638" t="n">
+        <v>118791</v>
+      </c>
+      <c r="G638" t="inlineStr">
+        <is>
+          <t>ARQUITECTURA</t>
+        </is>
+      </c>
+      <c r="H638" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I638" t="n">
+        <v>167</v>
+      </c>
+      <c r="J638" t="n">
+        <v>10</v>
+      </c>
+      <c r="K638" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L638" t="inlineStr"/>
+      <c r="M638" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N638" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="O638" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P638" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q638" t="inlineStr">
+        <is>
+          <t>Arquitectura y urbanismo</t>
+        </is>
+      </c>
+      <c r="R638" t="inlineStr">
+        <is>
+          <t>Arquitectura y afines</t>
+        </is>
+      </c>
+      <c r="S638" t="inlineStr"/>
+      <c r="T638" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U638" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+      <c r="V638" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>9940</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE SANTA MARTA</t>
+        </is>
+      </c>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F639" t="n">
+        <v>118794</v>
+      </c>
+      <c r="G639" t="inlineStr">
+        <is>
+          <t>DISEÑO DE MODAS</t>
+        </is>
+      </c>
+      <c r="H639" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I639" t="n">
+        <v>162</v>
+      </c>
+      <c r="J639" t="n">
+        <v>10</v>
+      </c>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L639" t="inlineStr"/>
+      <c r="M639" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N639" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="O639" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P639" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q639" t="inlineStr">
+        <is>
+          <t>Diseño industrial, de moda e interiores</t>
+        </is>
+      </c>
+      <c r="R639" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S639" t="inlineStr"/>
+      <c r="T639" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U639" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+      <c r="V639" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>9940</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE SANTA MARTA</t>
+        </is>
+      </c>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F640" t="n">
+        <v>118796</v>
+      </c>
+      <c r="G640" t="inlineStr">
+        <is>
+          <t>INGENIERÍA AGRÍCOLA</t>
+        </is>
+      </c>
+      <c r="H640" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I640" t="n">
+        <v>165</v>
+      </c>
+      <c r="J640" t="n">
+        <v>10</v>
+      </c>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L640" t="inlineStr"/>
+      <c r="M640" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N640" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="O640" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P640" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="Q640" t="inlineStr">
+        <is>
+          <t>Producción agrícola y ganadera</t>
+        </is>
+      </c>
+      <c r="R640" t="inlineStr">
+        <is>
+          <t>Ingeniería agrícola, forestal y afines</t>
+        </is>
+      </c>
+      <c r="S640" t="inlineStr"/>
+      <c r="T640" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U640" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V640" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>9940</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE SANTA MARTA</t>
+        </is>
+      </c>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F641" t="n">
+        <v>118793</v>
+      </c>
+      <c r="G641" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE DATOS E INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H641" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I641" t="n">
+        <v>165</v>
+      </c>
+      <c r="J641" t="n">
+        <v>10</v>
+      </c>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L641" t="inlineStr"/>
+      <c r="M641" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N641" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="O641" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P641" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q641" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R641" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S641" t="inlineStr"/>
+      <c r="T641" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U641" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V641" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>9940</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE SANTA MARTA</t>
+        </is>
+      </c>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F642" t="n">
+        <v>118798</v>
+      </c>
+      <c r="G642" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DEL AGUA Y DESARROLLO SOSTENIBLE</t>
+        </is>
+      </c>
+      <c r="H642" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I642" t="n">
+        <v>170</v>
+      </c>
+      <c r="J642" t="n">
+        <v>10</v>
+      </c>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L642" t="inlineStr"/>
+      <c r="M642" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N642" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="O642" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P642" t="inlineStr">
+        <is>
+          <t>Arquitectura y construcción</t>
+        </is>
+      </c>
+      <c r="Q642" t="inlineStr">
+        <is>
+          <t>Construcción e ingeniería civil</t>
+        </is>
+      </c>
+      <c r="R642" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S642" t="inlineStr"/>
+      <c r="T642" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U642" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V642" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>9940</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE SANTA MARTA</t>
+        </is>
+      </c>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F643" t="n">
+        <v>118789</v>
+      </c>
+      <c r="G643" t="inlineStr">
+        <is>
+          <t>INGENIERÍA TOPOGRÁFICA Y GEOMÁTICA</t>
+        </is>
+      </c>
+      <c r="H643" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I643" t="n">
+        <v>165</v>
+      </c>
+      <c r="J643" t="n">
+        <v>10</v>
+      </c>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L643" t="inlineStr"/>
+      <c r="M643" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N643" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="O643" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P643" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="Q643" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Programas y certificaciones interdisciplinarios relativos a ingeniería, industria y construcción </t>
+        </is>
+      </c>
+      <c r="R643" t="inlineStr">
+        <is>
+          <t>Ingeniería civil y afines</t>
+        </is>
+      </c>
+      <c r="S643" t="inlineStr"/>
+      <c r="T643" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="U643" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="V643" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V643"/>
+  <dimension ref="A1:V653"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61678,10 +61678,8 @@
       </c>
     </row>
     <row r="629">
-      <c r="A629" t="inlineStr">
-        <is>
-          <t>1729</t>
-        </is>
+      <c r="A629" t="n">
+        <v>1729</v>
       </c>
       <c r="B629" t="inlineStr">
         <is>
@@ -61735,7 +61733,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N629" s="2" t="n">
+      <c r="N629" s="1" t="n">
         <v>46121</v>
       </c>
       <c r="O629" t="inlineStr">
@@ -61776,10 +61774,8 @@
       </c>
     </row>
     <row r="630">
-      <c r="A630" t="inlineStr">
-        <is>
-          <t>2209</t>
-        </is>
+      <c r="A630" t="n">
+        <v>2209</v>
       </c>
       <c r="B630" t="inlineStr">
         <is>
@@ -61831,7 +61827,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N630" s="2" t="n">
+      <c r="N630" s="1" t="n">
         <v>46002</v>
       </c>
       <c r="O630" t="inlineStr">
@@ -61872,10 +61868,8 @@
       </c>
     </row>
     <row r="631">
-      <c r="A631" t="inlineStr">
-        <is>
-          <t>2828</t>
-        </is>
+      <c r="A631" t="n">
+        <v>2828</v>
       </c>
       <c r="B631" t="inlineStr">
         <is>
@@ -61927,7 +61921,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N631" s="2" t="n">
+      <c r="N631" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="O631" t="inlineStr">
@@ -61968,10 +61962,8 @@
       </c>
     </row>
     <row r="632">
-      <c r="A632" t="inlineStr">
-        <is>
-          <t>2828</t>
-        </is>
+      <c r="A632" t="n">
+        <v>2828</v>
       </c>
       <c r="B632" t="inlineStr">
         <is>
@@ -62023,7 +62015,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N632" s="2" t="n">
+      <c r="N632" s="1" t="n">
         <v>46111</v>
       </c>
       <c r="O632" t="inlineStr">
@@ -62064,10 +62056,8 @@
       </c>
     </row>
     <row r="633">
-      <c r="A633" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
+      <c r="A633" t="n">
+        <v>2847</v>
       </c>
       <c r="B633" t="inlineStr">
         <is>
@@ -62119,7 +62109,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N633" s="2" t="n">
+      <c r="N633" s="1" t="n">
         <v>45993</v>
       </c>
       <c r="O633" t="inlineStr">
@@ -62160,10 +62150,8 @@
       </c>
     </row>
     <row r="634">
-      <c r="A634" t="inlineStr">
-        <is>
-          <t>2847</t>
-        </is>
+      <c r="A634" t="n">
+        <v>2847</v>
       </c>
       <c r="B634" t="inlineStr">
         <is>
@@ -62215,7 +62203,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N634" s="2" t="n">
+      <c r="N634" s="1" t="n">
         <v>45993</v>
       </c>
       <c r="O634" t="inlineStr">
@@ -62256,10 +62244,8 @@
       </c>
     </row>
     <row r="635">
-      <c r="A635" t="inlineStr">
-        <is>
-          <t>4817</t>
-        </is>
+      <c r="A635" t="n">
+        <v>4817</v>
       </c>
       <c r="B635" t="inlineStr">
         <is>
@@ -62311,7 +62297,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N635" s="2" t="n">
+      <c r="N635" s="1" t="n">
         <v>45988</v>
       </c>
       <c r="O635" t="inlineStr">
@@ -62352,10 +62338,8 @@
       </c>
     </row>
     <row r="636">
-      <c r="A636" t="inlineStr">
-        <is>
-          <t>9904</t>
-        </is>
+      <c r="A636" t="n">
+        <v>9904</v>
       </c>
       <c r="B636" t="inlineStr">
         <is>
@@ -62407,7 +62391,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N636" s="2" t="n">
+      <c r="N636" s="1" t="n">
         <v>46008</v>
       </c>
       <c r="O636" t="inlineStr">
@@ -62448,10 +62432,8 @@
       </c>
     </row>
     <row r="637">
-      <c r="A637" t="inlineStr">
-        <is>
-          <t>9913</t>
-        </is>
+      <c r="A637" t="n">
+        <v>9913</v>
       </c>
       <c r="B637" t="inlineStr">
         <is>
@@ -62503,7 +62485,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N637" s="2" t="n">
+      <c r="N637" s="1" t="n">
         <v>46050</v>
       </c>
       <c r="O637" t="inlineStr">
@@ -62544,10 +62526,8 @@
       </c>
     </row>
     <row r="638">
-      <c r="A638" t="inlineStr">
-        <is>
-          <t>9940</t>
-        </is>
+      <c r="A638" t="n">
+        <v>9940</v>
       </c>
       <c r="B638" t="inlineStr">
         <is>
@@ -62599,7 +62579,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N638" s="2" t="n">
+      <c r="N638" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="O638" t="inlineStr">
@@ -62640,10 +62620,8 @@
       </c>
     </row>
     <row r="639">
-      <c r="A639" t="inlineStr">
-        <is>
-          <t>9940</t>
-        </is>
+      <c r="A639" t="n">
+        <v>9940</v>
       </c>
       <c r="B639" t="inlineStr">
         <is>
@@ -62695,7 +62673,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N639" s="2" t="n">
+      <c r="N639" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="O639" t="inlineStr">
@@ -62736,10 +62714,8 @@
       </c>
     </row>
     <row r="640">
-      <c r="A640" t="inlineStr">
-        <is>
-          <t>9940</t>
-        </is>
+      <c r="A640" t="n">
+        <v>9940</v>
       </c>
       <c r="B640" t="inlineStr">
         <is>
@@ -62791,7 +62767,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N640" s="2" t="n">
+      <c r="N640" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="O640" t="inlineStr">
@@ -62832,10 +62808,8 @@
       </c>
     </row>
     <row r="641">
-      <c r="A641" t="inlineStr">
-        <is>
-          <t>9940</t>
-        </is>
+      <c r="A641" t="n">
+        <v>9940</v>
       </c>
       <c r="B641" t="inlineStr">
         <is>
@@ -62887,7 +62861,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N641" s="2" t="n">
+      <c r="N641" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="O641" t="inlineStr">
@@ -62928,10 +62902,8 @@
       </c>
     </row>
     <row r="642">
-      <c r="A642" t="inlineStr">
-        <is>
-          <t>9940</t>
-        </is>
+      <c r="A642" t="n">
+        <v>9940</v>
       </c>
       <c r="B642" t="inlineStr">
         <is>
@@ -62983,7 +62955,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N642" s="2" t="n">
+      <c r="N642" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="O642" t="inlineStr">
@@ -63024,10 +62996,8 @@
       </c>
     </row>
     <row r="643">
-      <c r="A643" t="inlineStr">
-        <is>
-          <t>9940</t>
-        </is>
+      <c r="A643" t="n">
+        <v>9940</v>
       </c>
       <c r="B643" t="inlineStr">
         <is>
@@ -63079,7 +63049,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N643" s="2" t="n">
+      <c r="N643" s="1" t="n">
         <v>46101</v>
       </c>
       <c r="O643" t="inlineStr">
@@ -63114,6 +63084,966 @@
         </is>
       </c>
       <c r="V643" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>1113</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CORDOBA</t>
+        </is>
+      </c>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="F644" t="n">
+        <v>118828</v>
+      </c>
+      <c r="G644" t="inlineStr">
+        <is>
+          <t>MEDICINA</t>
+        </is>
+      </c>
+      <c r="H644" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I644" t="n">
+        <v>265</v>
+      </c>
+      <c r="J644" t="n">
+        <v>12</v>
+      </c>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L644" t="inlineStr"/>
+      <c r="M644" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N644" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="O644" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P644" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q644" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="R644" t="inlineStr">
+        <is>
+          <t>Medicina</t>
+        </is>
+      </c>
+      <c r="S644" t="inlineStr"/>
+      <c r="T644" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U644" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V644" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>1805</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTIAGO DE CALI</t>
+        </is>
+      </c>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F645" t="n">
+        <v>118830</v>
+      </c>
+      <c r="G645" t="inlineStr">
+        <is>
+          <t>CIENCIA POLÍTICA</t>
+        </is>
+      </c>
+      <c r="H645" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I645" t="n">
+        <v>122</v>
+      </c>
+      <c r="J645" t="n">
+        <v>9</v>
+      </c>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L645" t="inlineStr"/>
+      <c r="M645" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N645" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="O645" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P645" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q645" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R645" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S645" t="inlineStr"/>
+      <c r="T645" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U645" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V645" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>1806</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD LIBRE</t>
+        </is>
+      </c>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F646" t="n">
+        <v>118829</v>
+      </c>
+      <c r="G646" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN LOGÍSTICA</t>
+        </is>
+      </c>
+      <c r="H646" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I646" t="n">
+        <v>144</v>
+      </c>
+      <c r="J646" t="n">
+        <v>8</v>
+      </c>
+      <c r="K646" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L646" t="inlineStr"/>
+      <c r="M646" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N646" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="O646" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P646" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q646" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R646" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S646" t="inlineStr"/>
+      <c r="T646" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U646" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V646" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr">
+        <is>
+          <t>Cartago</t>
+        </is>
+      </c>
+      <c r="F647" t="n">
+        <v>118841</v>
+      </c>
+      <c r="G647" t="inlineStr">
+        <is>
+          <t>FISIOTERAPIA</t>
+        </is>
+      </c>
+      <c r="H647" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I647" t="n">
+        <v>158</v>
+      </c>
+      <c r="J647" t="n">
+        <v>8</v>
+      </c>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L647" t="inlineStr"/>
+      <c r="M647" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N647" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="O647" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P647" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q647" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R647" t="inlineStr">
+        <is>
+          <t>Terapias</t>
+        </is>
+      </c>
+      <c r="S647" t="inlineStr"/>
+      <c r="T647" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U647" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V647" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F648" t="n">
+        <v>118840</v>
+      </c>
+      <c r="G648" t="inlineStr">
+        <is>
+          <t>MERCADEO</t>
+        </is>
+      </c>
+      <c r="H648" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I648" t="n">
+        <v>139</v>
+      </c>
+      <c r="J648" t="n">
+        <v>8</v>
+      </c>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L648" t="inlineStr"/>
+      <c r="M648" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N648" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="O648" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P648" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q648" t="inlineStr">
+        <is>
+          <t>Mercadotecnia y publicidad</t>
+        </is>
+      </c>
+      <c r="R648" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S648" t="inlineStr"/>
+      <c r="T648" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U648" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V648" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>2721</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA MARIA CANO</t>
+        </is>
+      </c>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F649" t="n">
+        <v>118767</v>
+      </c>
+      <c r="G649" t="inlineStr">
+        <is>
+          <t>ACTIVIDAD FÍSICA Y DEPORTE</t>
+        </is>
+      </c>
+      <c r="H649" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I649" t="n">
+        <v>155</v>
+      </c>
+      <c r="J649" t="n">
+        <v>9</v>
+      </c>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L649" t="inlineStr"/>
+      <c r="M649" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N649" s="2" t="n">
+        <v>46045</v>
+      </c>
+      <c r="O649" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P649" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q649" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R649" t="inlineStr">
+        <is>
+          <t>Optometría, otros programas de ciencias de la salud</t>
+        </is>
+      </c>
+      <c r="S649" t="inlineStr"/>
+      <c r="T649" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U649" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V649" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>2725</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr">
+        <is>
+          <t>POLITECNICO GRANCOLOMBIANO</t>
+        </is>
+      </c>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F650" t="n">
+        <v>118837</v>
+      </c>
+      <c r="G650" t="inlineStr">
+        <is>
+          <t>FINANZAS</t>
+        </is>
+      </c>
+      <c r="H650" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I650" t="n">
+        <v>137</v>
+      </c>
+      <c r="J650" t="n">
+        <v>8</v>
+      </c>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L650" t="inlineStr"/>
+      <c r="M650" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N650" s="2" t="n">
+        <v>46050</v>
+      </c>
+      <c r="O650" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P650" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q650" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R650" t="inlineStr">
+        <is>
+          <t>Economía</t>
+        </is>
+      </c>
+      <c r="S650" t="inlineStr"/>
+      <c r="T650" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U650" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V650" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>4813</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIFICADA NACIONAL DE EDUCACION SUPERIOR-CUN-</t>
+        </is>
+      </c>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F651" t="n">
+        <v>118850</v>
+      </c>
+      <c r="G651" t="inlineStr">
+        <is>
+          <t>CONTADURÍA PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H651" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I651" t="n">
+        <v>153</v>
+      </c>
+      <c r="J651" t="n">
+        <v>9</v>
+      </c>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L651" t="inlineStr"/>
+      <c r="M651" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N651" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O651" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P651" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q651" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R651" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S651" t="inlineStr"/>
+      <c r="T651" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U651" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V651" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>5801</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr">
+        <is>
+          <t>CORPORACION ESCUELA TECNOLOGICA DEL ORIENTE</t>
+        </is>
+      </c>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F652" t="n">
+        <v>118858</v>
+      </c>
+      <c r="G652" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE PROYECTOS</t>
+        </is>
+      </c>
+      <c r="H652" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I652" t="n">
+        <v>24</v>
+      </c>
+      <c r="J652" t="n">
+        <v>2</v>
+      </c>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L652" t="inlineStr"/>
+      <c r="M652" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N652" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O652" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P652" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q652" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R652" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S652" t="inlineStr"/>
+      <c r="T652" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U652" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V652" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>9939</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA CATÓLICA DEL CARIBE</t>
+        </is>
+      </c>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F653" t="n">
+        <v>118857</v>
+      </c>
+      <c r="G653" t="inlineStr">
+        <is>
+          <t>CONTADURÍA PÚBLICA</t>
+        </is>
+      </c>
+      <c r="H653" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I653" t="n">
+        <v>135</v>
+      </c>
+      <c r="J653" t="n">
+        <v>9</v>
+      </c>
+      <c r="K653" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L653" t="inlineStr"/>
+      <c r="M653" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N653" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O653" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P653" t="inlineStr">
+        <is>
+          <t>Matemáticas y estadística</t>
+        </is>
+      </c>
+      <c r="Q653" t="inlineStr">
+        <is>
+          <t>Matemáticas</t>
+        </is>
+      </c>
+      <c r="R653" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S653" t="inlineStr"/>
+      <c r="T653" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="U653" t="inlineStr">
+        <is>
+          <t>Ciencias Básicas</t>
+        </is>
+      </c>
+      <c r="V653" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V653"/>
+  <dimension ref="A1:V669"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63090,10 +63090,8 @@
       </c>
     </row>
     <row r="644">
-      <c r="A644" t="inlineStr">
-        <is>
-          <t>1113</t>
-        </is>
+      <c r="A644" t="n">
+        <v>1113</v>
       </c>
       <c r="B644" t="inlineStr">
         <is>
@@ -63145,7 +63143,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N644" s="2" t="n">
+      <c r="N644" s="1" t="n">
         <v>46148</v>
       </c>
       <c r="O644" t="inlineStr">
@@ -63186,10 +63184,8 @@
       </c>
     </row>
     <row r="645">
-      <c r="A645" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A645" t="n">
+        <v>1805</v>
       </c>
       <c r="B645" t="inlineStr">
         <is>
@@ -63241,7 +63237,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N645" s="2" t="n">
+      <c r="N645" s="1" t="n">
         <v>46139</v>
       </c>
       <c r="O645" t="inlineStr">
@@ -63282,10 +63278,8 @@
       </c>
     </row>
     <row r="646">
-      <c r="A646" t="inlineStr">
-        <is>
-          <t>1806</t>
-        </is>
+      <c r="A646" t="n">
+        <v>1806</v>
       </c>
       <c r="B646" t="inlineStr">
         <is>
@@ -63337,7 +63331,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N646" s="2" t="n">
+      <c r="N646" s="1" t="n">
         <v>46146</v>
       </c>
       <c r="O646" t="inlineStr">
@@ -63378,10 +63372,8 @@
       </c>
     </row>
     <row r="647">
-      <c r="A647" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A647" t="n">
+        <v>1818</v>
       </c>
       <c r="B647" t="inlineStr">
         <is>
@@ -63433,7 +63425,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N647" s="2" t="n">
+      <c r="N647" s="1" t="n">
         <v>46100</v>
       </c>
       <c r="O647" t="inlineStr">
@@ -63474,10 +63466,8 @@
       </c>
     </row>
     <row r="648">
-      <c r="A648" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A648" t="n">
+        <v>1818</v>
       </c>
       <c r="B648" t="inlineStr">
         <is>
@@ -63529,7 +63519,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N648" s="2" t="n">
+      <c r="N648" s="1" t="n">
         <v>46100</v>
       </c>
       <c r="O648" t="inlineStr">
@@ -63570,10 +63560,8 @@
       </c>
     </row>
     <row r="649">
-      <c r="A649" t="inlineStr">
-        <is>
-          <t>2721</t>
-        </is>
+      <c r="A649" t="n">
+        <v>2721</v>
       </c>
       <c r="B649" t="inlineStr">
         <is>
@@ -63625,7 +63613,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N649" s="2" t="n">
+      <c r="N649" s="1" t="n">
         <v>46045</v>
       </c>
       <c r="O649" t="inlineStr">
@@ -63666,10 +63654,8 @@
       </c>
     </row>
     <row r="650">
-      <c r="A650" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
+      <c r="A650" t="n">
+        <v>2725</v>
       </c>
       <c r="B650" t="inlineStr">
         <is>
@@ -63721,7 +63707,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N650" s="2" t="n">
+      <c r="N650" s="1" t="n">
         <v>46050</v>
       </c>
       <c r="O650" t="inlineStr">
@@ -63762,10 +63748,8 @@
       </c>
     </row>
     <row r="651">
-      <c r="A651" t="inlineStr">
-        <is>
-          <t>4813</t>
-        </is>
+      <c r="A651" t="n">
+        <v>4813</v>
       </c>
       <c r="B651" t="inlineStr">
         <is>
@@ -63817,7 +63801,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N651" s="2" t="n">
+      <c r="N651" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O651" t="inlineStr">
@@ -63858,10 +63842,8 @@
       </c>
     </row>
     <row r="652">
-      <c r="A652" t="inlineStr">
-        <is>
-          <t>5801</t>
-        </is>
+      <c r="A652" t="n">
+        <v>5801</v>
       </c>
       <c r="B652" t="inlineStr">
         <is>
@@ -63913,7 +63895,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N652" s="2" t="n">
+      <c r="N652" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O652" t="inlineStr">
@@ -63954,10 +63936,8 @@
       </c>
     </row>
     <row r="653">
-      <c r="A653" t="inlineStr">
-        <is>
-          <t>9939</t>
-        </is>
+      <c r="A653" t="n">
+        <v>9939</v>
       </c>
       <c r="B653" t="inlineStr">
         <is>
@@ -64009,7 +63989,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N653" s="2" t="n">
+      <c r="N653" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O653" t="inlineStr">
@@ -64044,6 +64024,1542 @@
         </is>
       </c>
       <c r="V653" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F654" t="n">
+        <v>118927</v>
+      </c>
+      <c r="G654" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H654" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I654" t="n">
+        <v>135</v>
+      </c>
+      <c r="J654" t="n">
+        <v>8</v>
+      </c>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L654" t="inlineStr"/>
+      <c r="M654" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N654" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="O654" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P654" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q654" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R654" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S654" t="inlineStr"/>
+      <c r="T654" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U654" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V654" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr">
+        <is>
+          <t>Villavicencio</t>
+        </is>
+      </c>
+      <c r="F655" t="n">
+        <v>118914</v>
+      </c>
+      <c r="G655" t="inlineStr">
+        <is>
+          <t>INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H655" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I655" t="n">
+        <v>136</v>
+      </c>
+      <c r="J655" t="n">
+        <v>8</v>
+      </c>
+      <c r="K655" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L655" t="inlineStr"/>
+      <c r="M655" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N655" s="2" t="n">
+        <v>45643</v>
+      </c>
+      <c r="O655" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P655" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q655" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R655" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S655" t="inlineStr"/>
+      <c r="T655" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U655" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V655" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F656" t="n">
+        <v>118901</v>
+      </c>
+      <c r="G656" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN EDUCACION INFANTIL</t>
+        </is>
+      </c>
+      <c r="H656" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I656" t="n">
+        <v>144</v>
+      </c>
+      <c r="J656" t="n">
+        <v>9</v>
+      </c>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L656" t="inlineStr"/>
+      <c r="M656" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N656" s="2" t="n">
+        <v>44153</v>
+      </c>
+      <c r="O656" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P656" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q656" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R656" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S656" t="inlineStr"/>
+      <c r="T656" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U656" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V656" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>1735</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD MANUELA BELTRAN-UMB-</t>
+        </is>
+      </c>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F657" t="n">
+        <v>118912</v>
+      </c>
+      <c r="G657" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H657" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I657" t="n">
+        <v>156</v>
+      </c>
+      <c r="J657" t="n">
+        <v>8</v>
+      </c>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L657" t="inlineStr"/>
+      <c r="M657" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N657" s="2" t="n">
+        <v>44153</v>
+      </c>
+      <c r="O657" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P657" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q657" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R657" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S657" t="inlineStr"/>
+      <c r="T657" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U657" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V657" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>1804</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DEL CARIBE- UNIAUTONOMA</t>
+        </is>
+      </c>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F658" t="n">
+        <v>118935</v>
+      </c>
+      <c r="G658" t="inlineStr">
+        <is>
+          <t>NEGOCIOS DIGITALES</t>
+        </is>
+      </c>
+      <c r="H658" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I658" t="n">
+        <v>144</v>
+      </c>
+      <c r="J658" t="n">
+        <v>8</v>
+      </c>
+      <c r="K658" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L658" t="inlineStr"/>
+      <c r="M658" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N658" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="O658" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P658" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q658" t="inlineStr">
+        <is>
+          <t>Gestión financiera, administración bancaria y seguros</t>
+        </is>
+      </c>
+      <c r="R658" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S658" t="inlineStr"/>
+      <c r="T658" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U658" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V658" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>1813</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS ANDES</t>
+        </is>
+      </c>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F659" t="n">
+        <v>118944</v>
+      </c>
+      <c r="G659" t="inlineStr">
+        <is>
+          <t>CAMBIO AMBIENTAL GLOBAL</t>
+        </is>
+      </c>
+      <c r="H659" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I659" t="n">
+        <v>132</v>
+      </c>
+      <c r="J659" t="n">
+        <v>8</v>
+      </c>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L659" t="inlineStr"/>
+      <c r="M659" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N659" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O659" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P659" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q659" t="inlineStr">
+        <is>
+          <t>Sociología, Antropología y estudios culturales</t>
+        </is>
+      </c>
+      <c r="R659" t="inlineStr">
+        <is>
+          <t>Geografía, historia</t>
+        </is>
+      </c>
+      <c r="S659" t="inlineStr"/>
+      <c r="T659" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U659" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V659" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F660" t="n">
+        <v>118923</v>
+      </c>
+      <c r="G660" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN LENGUAS EXTRANJERAS CON ÉNFASIS EN INGLÉS Y ESPAÑOL</t>
+        </is>
+      </c>
+      <c r="H660" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I660" t="n">
+        <v>144</v>
+      </c>
+      <c r="J660" t="n">
+        <v>8</v>
+      </c>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L660" t="inlineStr"/>
+      <c r="M660" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N660" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="O660" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P660" t="inlineStr">
+        <is>
+          <t>Idiomas</t>
+        </is>
+      </c>
+      <c r="Q660" t="inlineStr">
+        <is>
+          <t>Adquisición del lenguaje</t>
+        </is>
+      </c>
+      <c r="R660" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S660" t="inlineStr"/>
+      <c r="T660" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U660" t="inlineStr">
+        <is>
+          <t>Instituto de Idiomas</t>
+        </is>
+      </c>
+      <c r="V660" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>1823</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE BUCARAMANGA-UNAB-</t>
+        </is>
+      </c>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F661" t="n">
+        <v>118933</v>
+      </c>
+      <c r="G661" t="inlineStr">
+        <is>
+          <t>QUÍMICA FARMACÉUTICA</t>
+        </is>
+      </c>
+      <c r="H661" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I661" t="n">
+        <v>151</v>
+      </c>
+      <c r="J661" t="n">
+        <v>9</v>
+      </c>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L661" t="inlineStr"/>
+      <c r="M661" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N661" s="2" t="n">
+        <v>46121</v>
+      </c>
+      <c r="O661" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P661" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q661" t="inlineStr">
+        <is>
+          <t>Farmacia</t>
+        </is>
+      </c>
+      <c r="R661" t="inlineStr">
+        <is>
+          <t>Química y afines</t>
+        </is>
+      </c>
+      <c r="S661" t="inlineStr"/>
+      <c r="T661" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U661" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V661" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>2106</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr">
+        <is>
+          <t>DIRECCION DE EDUCACION POLICIAL</t>
+        </is>
+      </c>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F662" t="n">
+        <v>118897</v>
+      </c>
+      <c r="G662" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN TECNOLOGÍAS DE LA INFORMACIÓN Y COMUNICACIONES</t>
+        </is>
+      </c>
+      <c r="H662" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I662" t="n">
+        <v>128</v>
+      </c>
+      <c r="J662" t="n">
+        <v>9</v>
+      </c>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L662" t="inlineStr"/>
+      <c r="M662" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N662" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="O662" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P662" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q662" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a tecnologías de la información y la comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="R662" t="inlineStr">
+        <is>
+          <t>Ingeniería electrónica, telecomunicaciones y afines</t>
+        </is>
+      </c>
+      <c r="S662" t="inlineStr"/>
+      <c r="T662" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U662" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V662" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA EMPRESARIAL DE LA CAMARA DE COMERCIO DE BOGOTA- UNIEMPRESARIAL</t>
+        </is>
+      </c>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F663" t="n">
+        <v>118922</v>
+      </c>
+      <c r="G663" t="inlineStr">
+        <is>
+          <t>NEGOCIOS TURÍSTICOS Y HOTELEROS</t>
+        </is>
+      </c>
+      <c r="H663" t="inlineStr">
+        <is>
+          <t>Híbrida (Dual-Virtual)</t>
+        </is>
+      </c>
+      <c r="I663" t="n">
+        <v>155</v>
+      </c>
+      <c r="J663" t="n">
+        <v>7</v>
+      </c>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L663" t="inlineStr"/>
+      <c r="M663" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N663" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="O663" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P663" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q663" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R663" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S663" t="inlineStr"/>
+      <c r="T663" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U663" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V663" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA EMPRESARIAL DE LA CAMARA DE COMERCIO DE BOGOTA- UNIEMPRESARIAL</t>
+        </is>
+      </c>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F664" t="n">
+        <v>118921</v>
+      </c>
+      <c r="G664" t="inlineStr">
+        <is>
+          <t>NEGOCIOS TURÍSTICOS Y HOTELEROS</t>
+        </is>
+      </c>
+      <c r="H664" t="inlineStr">
+        <is>
+          <t>Dual</t>
+        </is>
+      </c>
+      <c r="I664" t="n">
+        <v>155</v>
+      </c>
+      <c r="J664" t="n">
+        <v>7</v>
+      </c>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L664" t="inlineStr"/>
+      <c r="M664" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N664" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="O664" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P664" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q664" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R664" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S664" t="inlineStr"/>
+      <c r="T664" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U664" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V664" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>2832</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SANTANDER - UDES</t>
+        </is>
+      </c>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="F665" t="n">
+        <v>118938</v>
+      </c>
+      <c r="G665" t="inlineStr">
+        <is>
+          <t>INGENIERÍA AGRONÓMICA</t>
+        </is>
+      </c>
+      <c r="H665" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I665" t="n">
+        <v>143</v>
+      </c>
+      <c r="J665" t="n">
+        <v>9</v>
+      </c>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L665" t="inlineStr"/>
+      <c r="M665" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N665" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="O665" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P665" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="Q665" t="inlineStr">
+        <is>
+          <t>Producción agrícola y ganadera</t>
+        </is>
+      </c>
+      <c r="R665" t="inlineStr">
+        <is>
+          <t>Agronomía</t>
+        </is>
+      </c>
+      <c r="S665" t="inlineStr"/>
+      <c r="T665" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U665" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V665" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>5802</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD ECCI</t>
+        </is>
+      </c>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F666" t="n">
+        <v>118859</v>
+      </c>
+      <c r="G666" t="inlineStr">
+        <is>
+          <t>NUTRICIÓN Y DIETÉTICA</t>
+        </is>
+      </c>
+      <c r="H666" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I666" t="n">
+        <v>154</v>
+      </c>
+      <c r="J666" t="n">
+        <v>8</v>
+      </c>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L666" t="inlineStr"/>
+      <c r="M666" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N666" s="2" t="n">
+        <v>46052</v>
+      </c>
+      <c r="O666" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P666" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q666" t="inlineStr">
+        <is>
+          <t>Salud no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R666" t="inlineStr">
+        <is>
+          <t>Nutrición y dietética</t>
+        </is>
+      </c>
+      <c r="S666" t="inlineStr"/>
+      <c r="T666" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U666" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V666" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F667" t="n">
+        <v>118906</v>
+      </c>
+      <c r="G667" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H667" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I667" t="n">
+        <v>171</v>
+      </c>
+      <c r="J667" t="n">
+        <v>10</v>
+      </c>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L667" t="inlineStr"/>
+      <c r="M667" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N667" s="2" t="n">
+        <v>44641</v>
+      </c>
+      <c r="O667" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P667" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q667" t="inlineStr">
+        <is>
+          <t>Ingeniería y procesos químicos</t>
+        </is>
+      </c>
+      <c r="R667" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S667" t="inlineStr"/>
+      <c r="T667" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U667" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V667" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>9131</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA CERVANTES SAN AGUSTÍN - UNICERVANTES</t>
+        </is>
+      </c>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F668" t="n">
+        <v>118928</v>
+      </c>
+      <c r="G668" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN SISTEMAS DE SOFTWARE E INTELIGENCIA ARTIFICIAL</t>
+        </is>
+      </c>
+      <c r="H668" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I668" t="n">
+        <v>134</v>
+      </c>
+      <c r="J668" t="n">
+        <v>8</v>
+      </c>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L668" t="inlineStr"/>
+      <c r="M668" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N668" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="O668" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P668" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q668" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R668" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S668" t="inlineStr"/>
+      <c r="T668" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U668" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V668" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>9940</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE SANTA MARTA</t>
+        </is>
+      </c>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F669" t="n">
+        <v>118959</v>
+      </c>
+      <c r="G669" t="inlineStr">
+        <is>
+          <t>INGENIERÍA ELÉCTRICA</t>
+        </is>
+      </c>
+      <c r="H669" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I669" t="n">
+        <v>166</v>
+      </c>
+      <c r="J669" t="n">
+        <v>10</v>
+      </c>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L669" t="inlineStr"/>
+      <c r="M669" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N669" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O669" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P669" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q669" t="inlineStr">
+        <is>
+          <t>Electricidad y energía</t>
+        </is>
+      </c>
+      <c r="R669" t="inlineStr">
+        <is>
+          <t>Ingeniería eléctrica y afines</t>
+        </is>
+      </c>
+      <c r="S669" t="inlineStr"/>
+      <c r="T669" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="U669" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V669" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V674"/>
+  <dimension ref="A1:V686"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65534,10 +65534,8 @@
       </c>
     </row>
     <row r="670">
-      <c r="A670" t="inlineStr">
-        <is>
-          <t>1125</t>
-        </is>
+      <c r="A670" t="n">
+        <v>1125</v>
       </c>
       <c r="B670" t="inlineStr">
         <is>
@@ -65628,10 +65626,8 @@
       </c>
     </row>
     <row r="671">
-      <c r="A671" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A671" t="n">
+        <v>1711</v>
       </c>
       <c r="B671" t="inlineStr">
         <is>
@@ -65683,7 +65679,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N671" s="2" t="n">
+      <c r="N671" s="1" t="n">
         <v>46153</v>
       </c>
       <c r="O671" t="inlineStr">
@@ -65724,10 +65720,8 @@
       </c>
     </row>
     <row r="672">
-      <c r="A672" t="inlineStr">
-        <is>
-          <t>4721</t>
-        </is>
+      <c r="A672" t="n">
+        <v>4721</v>
       </c>
       <c r="B672" t="inlineStr">
         <is>
@@ -65779,7 +65773,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N672" s="2" t="n">
+      <c r="N672" s="1" t="n">
         <v>46182</v>
       </c>
       <c r="O672" t="inlineStr">
@@ -65820,10 +65814,8 @@
       </c>
     </row>
     <row r="673">
-      <c r="A673" t="inlineStr">
-        <is>
-          <t>9945</t>
-        </is>
+      <c r="A673" t="n">
+        <v>9945</v>
       </c>
       <c r="B673" t="inlineStr">
         <is>
@@ -65875,7 +65867,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N673" s="2" t="n">
+      <c r="N673" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O673" t="inlineStr">
@@ -65916,10 +65908,8 @@
       </c>
     </row>
     <row r="674">
-      <c r="A674" t="inlineStr">
-        <is>
-          <t>9945</t>
-        </is>
+      <c r="A674" t="n">
+        <v>9945</v>
       </c>
       <c r="B674" t="inlineStr">
         <is>
@@ -65971,7 +65961,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N674" s="2" t="n">
+      <c r="N674" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O674" t="inlineStr">
@@ -66006,6 +65996,1156 @@
         </is>
       </c>
       <c r="V674" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>1122</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL PACIFICO</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>Buenaventura</t>
+        </is>
+      </c>
+      <c r="F675" t="n">
+        <v>119012</v>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE NEGOCIOS INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I675" t="n">
+        <v>136</v>
+      </c>
+      <c r="J675" t="n">
+        <v>8</v>
+      </c>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L675" t="inlineStr"/>
+      <c r="M675" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N675" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="O675" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P675" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q675" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R675" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S675" t="inlineStr"/>
+      <c r="T675" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U675" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V675" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>1204</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD INDUSTRIAL DE SANTANDER</t>
+        </is>
+      </c>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="F676" t="n">
+        <v>119003</v>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>INGENIERÍA AGRONÓMICA</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I676" t="n">
+        <v>128</v>
+      </c>
+      <c r="J676" t="n">
+        <v>8</v>
+      </c>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L676" t="inlineStr"/>
+      <c r="M676" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N676" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="O676" t="inlineStr">
+        <is>
+          <t>Agropecuario, Silvicultura, Pesca y Veterinaria</t>
+        </is>
+      </c>
+      <c r="P676" t="inlineStr">
+        <is>
+          <t>Agropecuario</t>
+        </is>
+      </c>
+      <c r="Q676" t="inlineStr">
+        <is>
+          <t>Producción agrícola y ganadera</t>
+        </is>
+      </c>
+      <c r="R676" t="inlineStr">
+        <is>
+          <t>Ingeniería agronómica, pecuaria y afines</t>
+        </is>
+      </c>
+      <c r="S676" t="inlineStr"/>
+      <c r="T676" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U676" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V676" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F677" t="n">
+        <v>118996</v>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN LENGUAS EXTRANJERAS CON ÉNFASIS EN INGLÉS Y FRANCÉS</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I677" t="n">
+        <v>126</v>
+      </c>
+      <c r="J677" t="n">
+        <v>8</v>
+      </c>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L677" t="inlineStr"/>
+      <c r="M677" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N677" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O677" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P677" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q677" t="inlineStr">
+        <is>
+          <t>Formación para docentes con asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R677" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S677" t="inlineStr"/>
+      <c r="T677" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U677" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V677" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>1710</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD PONTIFICIA BOLIVARIANA</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F678" t="n">
+        <v>118997</v>
+      </c>
+      <c r="G678" t="inlineStr">
+        <is>
+          <t>LICENCIATURA EN LENGUAS EXTRANJERAS CON ÉNFASIS EN INGLÉS Y FRANCÉS</t>
+        </is>
+      </c>
+      <c r="H678" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I678" t="n">
+        <v>126</v>
+      </c>
+      <c r="J678" t="n">
+        <v>8</v>
+      </c>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L678" t="inlineStr"/>
+      <c r="M678" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N678" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O678" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P678" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q678" t="inlineStr">
+        <is>
+          <t>Formación para docentes con asignatura de especialización</t>
+        </is>
+      </c>
+      <c r="R678" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S678" t="inlineStr"/>
+      <c r="T678" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U678" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
+        </is>
+      </c>
+      <c r="V678" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F679" t="n">
+        <v>118989</v>
+      </c>
+      <c r="G679" t="inlineStr">
+        <is>
+          <t>LENGUAS Y CULTURA</t>
+        </is>
+      </c>
+      <c r="H679" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I679" t="n">
+        <v>138</v>
+      </c>
+      <c r="J679" t="n">
+        <v>8</v>
+      </c>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L679" t="inlineStr"/>
+      <c r="M679" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N679" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O679" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P679" t="inlineStr">
+        <is>
+          <t>Idiomas</t>
+        </is>
+      </c>
+      <c r="Q679" t="inlineStr">
+        <is>
+          <t>Adquisición del lenguaje</t>
+        </is>
+      </c>
+      <c r="R679" t="inlineStr">
+        <is>
+          <t>Lenguas modernas, literatura, linguística y afines</t>
+        </is>
+      </c>
+      <c r="S679" t="inlineStr"/>
+      <c r="T679" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U679" t="inlineStr">
+        <is>
+          <t>Instituto de Idiomas</t>
+        </is>
+      </c>
+      <c r="V679" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>1716</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F680" t="n">
+        <v>118988</v>
+      </c>
+      <c r="G680" t="inlineStr">
+        <is>
+          <t>LENGUAS Y CULTURA</t>
+        </is>
+      </c>
+      <c r="H680" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I680" t="n">
+        <v>138</v>
+      </c>
+      <c r="J680" t="n">
+        <v>8</v>
+      </c>
+      <c r="K680" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L680" t="inlineStr"/>
+      <c r="M680" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N680" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O680" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P680" t="inlineStr">
+        <is>
+          <t>Idiomas</t>
+        </is>
+      </c>
+      <c r="Q680" t="inlineStr">
+        <is>
+          <t>Adquisición del lenguaje</t>
+        </is>
+      </c>
+      <c r="R680" t="inlineStr">
+        <is>
+          <t>Lenguas modernas, literatura, linguística y afines</t>
+        </is>
+      </c>
+      <c r="S680" t="inlineStr"/>
+      <c r="T680" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U680" t="inlineStr">
+        <is>
+          <t>Instituto de Idiomas</t>
+        </is>
+      </c>
+      <c r="V680" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>1724</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE SAN BUENAVENTURA</t>
+        </is>
+      </c>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr">
+        <is>
+          <t>Cartagena de Indias</t>
+        </is>
+      </c>
+      <c r="F681" t="n">
+        <v>111794</v>
+      </c>
+      <c r="G681" t="inlineStr">
+        <is>
+          <t>BACTERIOLOGÍA Y LABORATORIO CLÍNICO</t>
+        </is>
+      </c>
+      <c r="H681" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I681" t="n">
+        <v>176</v>
+      </c>
+      <c r="J681" t="n">
+        <v>10</v>
+      </c>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L681" t="inlineStr"/>
+      <c r="M681" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N681" s="2" t="n">
+        <v>46199</v>
+      </c>
+      <c r="O681" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P681" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q681" t="inlineStr">
+        <is>
+          <t>Tecnología de diagnóstico y tratamiento médico</t>
+        </is>
+      </c>
+      <c r="R681" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S681" t="inlineStr"/>
+      <c r="T681" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U681" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+      <c r="V681" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr">
+        <is>
+          <t>Morales</t>
+        </is>
+      </c>
+      <c r="F682" t="n">
+        <v>117992</v>
+      </c>
+      <c r="G682" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H682" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I682" t="n">
+        <v>144</v>
+      </c>
+      <c r="J682" t="n">
+        <v>8</v>
+      </c>
+      <c r="K682" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L682" t="inlineStr"/>
+      <c r="M682" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N682" s="2" t="n">
+        <v>45860</v>
+      </c>
+      <c r="O682" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P682" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q682" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R682" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S682" t="inlineStr"/>
+      <c r="T682" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U682" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V682" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>1818</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD COOPERATIVA DE COLOMBIA</t>
+        </is>
+      </c>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>Miranda</t>
+        </is>
+      </c>
+      <c r="F683" t="n">
+        <v>117743</v>
+      </c>
+      <c r="G683" t="inlineStr">
+        <is>
+          <t>INGENIERIA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H683" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I683" t="n">
+        <v>156</v>
+      </c>
+      <c r="J683" t="n">
+        <v>10</v>
+      </c>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L683" t="inlineStr"/>
+      <c r="M683" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N683" t="inlineStr"/>
+      <c r="O683" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P683" t="inlineStr">
+        <is>
+          <t>Industria y procesamiento</t>
+        </is>
+      </c>
+      <c r="Q683" t="inlineStr">
+        <is>
+          <t>Industria y procesamiento no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R683" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S683" t="inlineStr"/>
+      <c r="T683" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U683" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V683" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F684" t="n">
+        <v>118985</v>
+      </c>
+      <c r="G684" t="inlineStr">
+        <is>
+          <t>TRABAJO SOCIAL</t>
+        </is>
+      </c>
+      <c r="H684" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I684" t="n">
+        <v>144</v>
+      </c>
+      <c r="J684" t="n">
+        <v>8</v>
+      </c>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L684" t="inlineStr"/>
+      <c r="M684" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N684" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="O684" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P684" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q684" t="inlineStr">
+        <is>
+          <t>Trabajo social</t>
+        </is>
+      </c>
+      <c r="R684" t="inlineStr">
+        <is>
+          <t>Sociología, trabajo social y afines</t>
+        </is>
+      </c>
+      <c r="S684" t="inlineStr"/>
+      <c r="T684" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U684" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V684" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F685" t="n">
+        <v>119006</v>
+      </c>
+      <c r="G685" t="inlineStr">
+        <is>
+          <t>TURISMO SOSTENIBLE E INNOVADOR</t>
+        </is>
+      </c>
+      <c r="H685" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I685" t="n">
+        <v>144</v>
+      </c>
+      <c r="J685" t="n">
+        <v>8</v>
+      </c>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L685" t="inlineStr"/>
+      <c r="M685" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N685" s="2" t="n">
+        <v>46198</v>
+      </c>
+      <c r="O685" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P685" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q685" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R685" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S685" t="inlineStr"/>
+      <c r="T685" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U685" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V685" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>4835</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA TALLER CINCO CENTRO DE DISEÑO</t>
+        </is>
+      </c>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F686" t="n">
+        <v>119010</v>
+      </c>
+      <c r="G686" t="inlineStr">
+        <is>
+          <t>CREACIÓN AUDIOVISUAL Y MULTIMEDIA</t>
+        </is>
+      </c>
+      <c r="H686" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I686" t="n">
+        <v>136</v>
+      </c>
+      <c r="J686" t="n">
+        <v>8</v>
+      </c>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L686" t="inlineStr"/>
+      <c r="M686" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N686" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="O686" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P686" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q686" t="inlineStr">
+        <is>
+          <t>Técnicas audiovisuales y producción para medios de comunicación</t>
+        </is>
+      </c>
+      <c r="R686" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S686" t="inlineStr"/>
+      <c r="T686" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="U686" t="inlineStr">
+        <is>
+          <t>Música</t>
+        </is>
+      </c>
+      <c r="V686" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V686"/>
+  <dimension ref="A1:V689"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66002,10 +66002,8 @@
       </c>
     </row>
     <row r="675">
-      <c r="A675" t="inlineStr">
-        <is>
-          <t>1122</t>
-        </is>
+      <c r="A675" t="n">
+        <v>1122</v>
       </c>
       <c r="B675" t="inlineStr">
         <is>
@@ -66057,7 +66055,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N675" s="2" t="n">
+      <c r="N675" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="O675" t="inlineStr">
@@ -66098,10 +66096,8 @@
       </c>
     </row>
     <row r="676">
-      <c r="A676" t="inlineStr">
-        <is>
-          <t>1204</t>
-        </is>
+      <c r="A676" t="n">
+        <v>1204</v>
       </c>
       <c r="B676" t="inlineStr">
         <is>
@@ -66153,7 +66149,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N676" s="2" t="n">
+      <c r="N676" s="1" t="n">
         <v>46122</v>
       </c>
       <c r="O676" t="inlineStr">
@@ -66194,10 +66190,8 @@
       </c>
     </row>
     <row r="677">
-      <c r="A677" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A677" t="n">
+        <v>1710</v>
       </c>
       <c r="B677" t="inlineStr">
         <is>
@@ -66249,7 +66243,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N677" s="2" t="n">
+      <c r="N677" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O677" t="inlineStr">
@@ -66290,10 +66284,8 @@
       </c>
     </row>
     <row r="678">
-      <c r="A678" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A678" t="n">
+        <v>1710</v>
       </c>
       <c r="B678" t="inlineStr">
         <is>
@@ -66345,7 +66337,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N678" s="2" t="n">
+      <c r="N678" s="1" t="n">
         <v>46093</v>
       </c>
       <c r="O678" t="inlineStr">
@@ -66386,10 +66378,8 @@
       </c>
     </row>
     <row r="679">
-      <c r="A679" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A679" t="n">
+        <v>1716</v>
       </c>
       <c r="B679" t="inlineStr">
         <is>
@@ -66441,7 +66431,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N679" s="2" t="n">
+      <c r="N679" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O679" t="inlineStr">
@@ -66482,10 +66472,8 @@
       </c>
     </row>
     <row r="680">
-      <c r="A680" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A680" t="n">
+        <v>1716</v>
       </c>
       <c r="B680" t="inlineStr">
         <is>
@@ -66537,7 +66525,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N680" s="2" t="n">
+      <c r="N680" s="1" t="n">
         <v>46162</v>
       </c>
       <c r="O680" t="inlineStr">
@@ -66578,10 +66566,8 @@
       </c>
     </row>
     <row r="681">
-      <c r="A681" t="inlineStr">
-        <is>
-          <t>1724</t>
-        </is>
+      <c r="A681" t="n">
+        <v>1724</v>
       </c>
       <c r="B681" t="inlineStr">
         <is>
@@ -66633,7 +66619,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N681" s="2" t="n">
+      <c r="N681" s="1" t="n">
         <v>46199</v>
       </c>
       <c r="O681" t="inlineStr">
@@ -66674,10 +66660,8 @@
       </c>
     </row>
     <row r="682">
-      <c r="A682" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A682" t="n">
+        <v>1818</v>
       </c>
       <c r="B682" t="inlineStr">
         <is>
@@ -66729,7 +66713,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N682" s="2" t="n">
+      <c r="N682" s="1" t="n">
         <v>45860</v>
       </c>
       <c r="O682" t="inlineStr">
@@ -66770,10 +66754,8 @@
       </c>
     </row>
     <row r="683">
-      <c r="A683" t="inlineStr">
-        <is>
-          <t>1818</t>
-        </is>
+      <c r="A683" t="n">
+        <v>1818</v>
       </c>
       <c r="B683" t="inlineStr">
         <is>
@@ -66864,10 +66846,8 @@
       </c>
     </row>
     <row r="684">
-      <c r="A684" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A684" t="n">
+        <v>2102</v>
       </c>
       <c r="B684" t="inlineStr">
         <is>
@@ -66919,7 +66899,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N684" s="2" t="n">
+      <c r="N684" s="1" t="n">
         <v>46108</v>
       </c>
       <c r="O684" t="inlineStr">
@@ -66960,10 +66940,8 @@
       </c>
     </row>
     <row r="685">
-      <c r="A685" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A685" t="n">
+        <v>2102</v>
       </c>
       <c r="B685" t="inlineStr">
         <is>
@@ -67015,7 +66993,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N685" s="2" t="n">
+      <c r="N685" s="1" t="n">
         <v>46198</v>
       </c>
       <c r="O685" t="inlineStr">
@@ -67056,10 +67034,8 @@
       </c>
     </row>
     <row r="686">
-      <c r="A686" t="inlineStr">
-        <is>
-          <t>4835</t>
-        </is>
+      <c r="A686" t="n">
+        <v>4835</v>
       </c>
       <c r="B686" t="inlineStr">
         <is>
@@ -67111,7 +67087,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N686" s="2" t="n">
+      <c r="N686" s="1" t="n">
         <v>46094</v>
       </c>
       <c r="O686" t="inlineStr">
@@ -67146,6 +67122,294 @@
         </is>
       </c>
       <c r="V686" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2302</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA DE ENVIGADO</t>
+        </is>
+      </c>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr">
+        <is>
+          <t>Envigado</t>
+        </is>
+      </c>
+      <c r="F687" t="n">
+        <v>119020</v>
+      </c>
+      <c r="G687" t="inlineStr">
+        <is>
+          <t>DERECHO</t>
+        </is>
+      </c>
+      <c r="H687" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I687" t="n">
+        <v>170</v>
+      </c>
+      <c r="J687" t="n">
+        <v>10</v>
+      </c>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L687" t="inlineStr"/>
+      <c r="M687" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N687" s="2" t="n">
+        <v>45364</v>
+      </c>
+      <c r="O687" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P687" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q687" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R687" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S687" t="inlineStr"/>
+      <c r="T687" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="U687" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V687" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2815</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA ADVENTISTA - UNAC</t>
+        </is>
+      </c>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F688" t="n">
+        <v>119025</v>
+      </c>
+      <c r="G688" t="inlineStr">
+        <is>
+          <t>CONTADURIA PUBLICA</t>
+        </is>
+      </c>
+      <c r="H688" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I688" t="n">
+        <v>153</v>
+      </c>
+      <c r="J688" t="n">
+        <v>9</v>
+      </c>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L688" t="inlineStr"/>
+      <c r="M688" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N688" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O688" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P688" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q688" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R688" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S688" t="inlineStr"/>
+      <c r="T688" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="U688" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V688" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>3302</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr">
+        <is>
+          <t>INSTITUCION UNIVERSITARIA - ITM</t>
+        </is>
+      </c>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F689" t="n">
+        <v>119023</v>
+      </c>
+      <c r="G689" t="inlineStr">
+        <is>
+          <t>DISEÑO</t>
+        </is>
+      </c>
+      <c r="H689" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I689" t="n">
+        <v>130</v>
+      </c>
+      <c r="J689" t="n">
+        <v>8</v>
+      </c>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L689" t="inlineStr"/>
+      <c r="M689" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N689" s="2" t="n">
+        <v>44392</v>
+      </c>
+      <c r="O689" t="inlineStr">
+        <is>
+          <t>Arte y Humanidades</t>
+        </is>
+      </c>
+      <c r="P689" t="inlineStr">
+        <is>
+          <t>Artes</t>
+        </is>
+      </c>
+      <c r="Q689" t="inlineStr">
+        <is>
+          <t>Diseño industrial, de moda e interiores</t>
+        </is>
+      </c>
+      <c r="R689" t="inlineStr">
+        <is>
+          <t>Diseño</t>
+        </is>
+      </c>
+      <c r="S689" t="inlineStr"/>
+      <c r="T689" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="U689" t="inlineStr">
+        <is>
+          <t>Escuela de Arquitectura, Urbanismo y Diseño</t>
+        </is>
+      </c>
+      <c r="V689" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>

--- a/data/novedades/Nuevos_pregrado.xlsx
+++ b/data/novedades/Nuevos_pregrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V689"/>
+  <dimension ref="A1:V707"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -67128,10 +67128,8 @@
       </c>
     </row>
     <row r="687">
-      <c r="A687" t="inlineStr">
-        <is>
-          <t>2302</t>
-        </is>
+      <c r="A687" t="n">
+        <v>2302</v>
       </c>
       <c r="B687" t="inlineStr">
         <is>
@@ -67183,7 +67181,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N687" s="2" t="n">
+      <c r="N687" s="1" t="n">
         <v>45364</v>
       </c>
       <c r="O687" t="inlineStr">
@@ -67224,10 +67222,8 @@
       </c>
     </row>
     <row r="688">
-      <c r="A688" t="inlineStr">
-        <is>
-          <t>2815</t>
-        </is>
+      <c r="A688" t="n">
+        <v>2815</v>
       </c>
       <c r="B688" t="inlineStr">
         <is>
@@ -67279,7 +67275,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N688" s="2" t="n">
+      <c r="N688" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O688" t="inlineStr">
@@ -67320,10 +67316,8 @@
       </c>
     </row>
     <row r="689">
-      <c r="A689" t="inlineStr">
-        <is>
-          <t>3302</t>
-        </is>
+      <c r="A689" t="n">
+        <v>3302</v>
       </c>
       <c r="B689" t="inlineStr">
         <is>
@@ -67375,7 +67369,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N689" s="2" t="n">
+      <c r="N689" s="1" t="n">
         <v>44392</v>
       </c>
       <c r="O689" t="inlineStr">
@@ -67410,6 +67404,1734 @@
         </is>
       </c>
       <c r="V689" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>1112</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE CALDAS</t>
+        </is>
+      </c>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr">
+        <is>
+          <t>La Dorada</t>
+        </is>
+      </c>
+      <c r="F690" t="n">
+        <v>119015</v>
+      </c>
+      <c r="G690" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN AGROINDUSTRIA Y TECNOLOGÍAS INTELIGENTES</t>
+        </is>
+      </c>
+      <c r="H690" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I690" t="n">
+        <v>144</v>
+      </c>
+      <c r="J690" t="n">
+        <v>8</v>
+      </c>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L690" t="inlineStr"/>
+      <c r="M690" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N690" s="2" t="n">
+        <v>46122</v>
+      </c>
+      <c r="O690" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P690" t="inlineStr">
+        <is>
+          <t>Industria y procesamiento</t>
+        </is>
+      </c>
+      <c r="Q690" t="inlineStr">
+        <is>
+          <t>Procesamiento de alimentos</t>
+        </is>
+      </c>
+      <c r="R690" t="inlineStr">
+        <is>
+          <t>Ingeniería agroindustrial, alimentos y afines</t>
+        </is>
+      </c>
+      <c r="S690" t="inlineStr"/>
+      <c r="T690" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U690" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V690" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SURCOLOMBIANA</t>
+        </is>
+      </c>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr">
+        <is>
+          <t>Pitalito</t>
+        </is>
+      </c>
+      <c r="F691" t="n">
+        <v>119051</v>
+      </c>
+      <c r="G691" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DEL CAFÉ</t>
+        </is>
+      </c>
+      <c r="H691" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I691" t="n">
+        <v>157</v>
+      </c>
+      <c r="J691" t="n">
+        <v>10</v>
+      </c>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L691" t="inlineStr"/>
+      <c r="M691" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N691" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O691" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P691" t="inlineStr">
+        <is>
+          <t>Industria y procesamiento</t>
+        </is>
+      </c>
+      <c r="Q691" t="inlineStr">
+        <is>
+          <t>Procesamiento de alimentos</t>
+        </is>
+      </c>
+      <c r="R691" t="inlineStr">
+        <is>
+          <t>Ingeniería agroindustrial, alimentos y afines</t>
+        </is>
+      </c>
+      <c r="S691" t="inlineStr"/>
+      <c r="T691" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U691" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V691" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL MAGDALENA - UNIMAGDALENA</t>
+        </is>
+      </c>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>Magdalena</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr">
+        <is>
+          <t>Santa Marta</t>
+        </is>
+      </c>
+      <c r="F692" t="n">
+        <v>119041</v>
+      </c>
+      <c r="G692" t="inlineStr">
+        <is>
+          <t>GENÉTICA</t>
+        </is>
+      </c>
+      <c r="H692" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I692" t="n">
+        <v>145</v>
+      </c>
+      <c r="J692" t="n">
+        <v>9</v>
+      </c>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L692" t="inlineStr"/>
+      <c r="M692" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N692" s="2" t="n">
+        <v>46197</v>
+      </c>
+      <c r="O692" t="inlineStr">
+        <is>
+          <t>Ciencias Naturales, Matemáticas y Estadística</t>
+        </is>
+      </c>
+      <c r="P692" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines</t>
+        </is>
+      </c>
+      <c r="Q692" t="inlineStr">
+        <is>
+          <t>Ciencias biológicas y afines no clasificados en otra parte</t>
+        </is>
+      </c>
+      <c r="R692" t="inlineStr">
+        <is>
+          <t>Biología, microbiología y afines</t>
+        </is>
+      </c>
+      <c r="S692" t="inlineStr"/>
+      <c r="T692" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U692" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="V692" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr">
+        <is>
+          <t>Manizales</t>
+        </is>
+      </c>
+      <c r="F693" t="n">
+        <v>119031</v>
+      </c>
+      <c r="G693" t="inlineStr">
+        <is>
+          <t>COMUNICACIÓN SOCIAL</t>
+        </is>
+      </c>
+      <c r="H693" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I693" t="n">
+        <v>126</v>
+      </c>
+      <c r="J693" t="n">
+        <v>8</v>
+      </c>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L693" t="inlineStr"/>
+      <c r="M693" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N693" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O693" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P693" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q693" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R693" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S693" t="inlineStr"/>
+      <c r="T693" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U693" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V693" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>2102</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD NACIONAL ABIERTA Y A DISTANCIA UNAD</t>
+        </is>
+      </c>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F694" t="n">
+        <v>119034</v>
+      </c>
+      <c r="G694" t="inlineStr">
+        <is>
+          <t>INGENIERÍA EN INTELIGENCIA ARTIFICIAL Y CIENCIA DE DATOS</t>
+        </is>
+      </c>
+      <c r="H694" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I694" t="n">
+        <v>150</v>
+      </c>
+      <c r="J694" t="n">
+        <v>9</v>
+      </c>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L694" t="inlineStr"/>
+      <c r="M694" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N694" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O694" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P694" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q694" t="inlineStr">
+        <is>
+          <t>Tecnologías de la información  y la comunicación (TIC) no clasificada en otra parte</t>
+        </is>
+      </c>
+      <c r="R694" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S694" t="inlineStr"/>
+      <c r="T694" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U694" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V694" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>2715</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA DE POPAYAN</t>
+        </is>
+      </c>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr">
+        <is>
+          <t>Popayán</t>
+        </is>
+      </c>
+      <c r="F695" t="n">
+        <v>119068</v>
+      </c>
+      <c r="G695" t="inlineStr">
+        <is>
+          <t>COMUNICACIÓN SOCIAL</t>
+        </is>
+      </c>
+      <c r="H695" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I695" t="n">
+        <v>138</v>
+      </c>
+      <c r="J695" t="n">
+        <v>8</v>
+      </c>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L695" t="inlineStr"/>
+      <c r="M695" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N695" s="2" t="n">
+        <v>46125</v>
+      </c>
+      <c r="O695" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P695" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q695" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R695" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S695" t="inlineStr"/>
+      <c r="T695" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U695" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V695" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>2725</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr">
+        <is>
+          <t>POLITECNICO GRANCOLOMBIANO</t>
+        </is>
+      </c>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F696" t="n">
+        <v>119028</v>
+      </c>
+      <c r="G696" t="inlineStr">
+        <is>
+          <t>GOBIERNO Y RELACIONES INTERNACIONALES</t>
+        </is>
+      </c>
+      <c r="H696" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I696" t="n">
+        <v>143</v>
+      </c>
+      <c r="J696" t="n">
+        <v>8</v>
+      </c>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L696" t="inlineStr"/>
+      <c r="M696" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N696" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O696" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P696" t="inlineStr">
+        <is>
+          <t>Ciencias sociales y del comportamiento</t>
+        </is>
+      </c>
+      <c r="Q696" t="inlineStr">
+        <is>
+          <t>Ciencias políticas y educación cívica</t>
+        </is>
+      </c>
+      <c r="R696" t="inlineStr">
+        <is>
+          <t>Ciencia política, relaciones internacionales</t>
+        </is>
+      </c>
+      <c r="S696" t="inlineStr"/>
+      <c r="T696" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U696" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+      <c r="V696" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>2828</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL HUILA-CORHUILA-</t>
+        </is>
+      </c>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F697" t="n">
+        <v>118734</v>
+      </c>
+      <c r="G697" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>Híbrida (Presencial-Virtual)</t>
+        </is>
+      </c>
+      <c r="I697" t="n">
+        <v>144</v>
+      </c>
+      <c r="J697" t="n">
+        <v>8</v>
+      </c>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L697" t="inlineStr"/>
+      <c r="M697" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N697" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="O697" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P697" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q697" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R697" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S697" t="inlineStr"/>
+      <c r="T697" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U697" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V697" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>2828</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA DEL HUILA-CORHUILA-</t>
+        </is>
+      </c>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>Huila</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr">
+        <is>
+          <t>Neiva</t>
+        </is>
+      </c>
+      <c r="F698" t="n">
+        <v>118733</v>
+      </c>
+      <c r="G698" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SOFTWARE</t>
+        </is>
+      </c>
+      <c r="H698" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I698" t="n">
+        <v>144</v>
+      </c>
+      <c r="J698" t="n">
+        <v>8</v>
+      </c>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L698" t="inlineStr"/>
+      <c r="M698" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N698" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="O698" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="P698" t="inlineStr">
+        <is>
+          <t>Tecnologías de la Información y la Comunicación (TIC)</t>
+        </is>
+      </c>
+      <c r="Q698" t="inlineStr">
+        <is>
+          <t>Desarrollo y análisis de software y aplicaciones</t>
+        </is>
+      </c>
+      <c r="R698" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S698" t="inlineStr"/>
+      <c r="T698" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U698" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V698" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DEL PUTUMAYO</t>
+        </is>
+      </c>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr">
+        <is>
+          <t>Mocoa</t>
+        </is>
+      </c>
+      <c r="F699" t="n">
+        <v>118941</v>
+      </c>
+      <c r="G699" t="inlineStr">
+        <is>
+          <t>INGENIERÍA AGROPECUARIA</t>
+        </is>
+      </c>
+      <c r="H699" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I699" t="n">
+        <v>180</v>
+      </c>
+      <c r="J699" t="n">
+        <v>10</v>
+      </c>
+      <c r="K699" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L699" t="inlineStr"/>
+      <c r="M699" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N699" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O699" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P699" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q699" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R699" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S699" t="inlineStr"/>
+      <c r="T699" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U699" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V699" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA DEL PUTUMAYO</t>
+        </is>
+      </c>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr">
+        <is>
+          <t>Mocoa</t>
+        </is>
+      </c>
+      <c r="F700" t="n">
+        <v>118939</v>
+      </c>
+      <c r="G700" t="inlineStr">
+        <is>
+          <t>INGENIERÍA INDUSTRIAL</t>
+        </is>
+      </c>
+      <c r="H700" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I700" t="n">
+        <v>161</v>
+      </c>
+      <c r="J700" t="n">
+        <v>10</v>
+      </c>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L700" t="inlineStr"/>
+      <c r="M700" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N700" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="O700" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P700" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q700" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R700" t="inlineStr">
+        <is>
+          <t>Ingeniería industrial y afines</t>
+        </is>
+      </c>
+      <c r="S700" t="inlineStr"/>
+      <c r="T700" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U700" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V700" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>4817</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr">
+        <is>
+          <t>CORPORACION DE EDUCACIÓN SUPERIOR DEL LITORAL</t>
+        </is>
+      </c>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F701" t="n">
+        <v>119075</v>
+      </c>
+      <c r="G701" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="H701" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I701" t="n">
+        <v>144</v>
+      </c>
+      <c r="J701" t="n">
+        <v>8</v>
+      </c>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L701" t="inlineStr"/>
+      <c r="M701" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N701" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O701" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P701" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q701" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R701" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S701" t="inlineStr"/>
+      <c r="T701" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U701" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V701" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>4817</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr">
+        <is>
+          <t>CORPORACION DE EDUCACIÓN SUPERIOR DEL LITORAL</t>
+        </is>
+      </c>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F702" t="n">
+        <v>119076</v>
+      </c>
+      <c r="G702" t="inlineStr">
+        <is>
+          <t>INGENIERÍA DE SISTEMAS</t>
+        </is>
+      </c>
+      <c r="H702" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I702" t="n">
+        <v>144</v>
+      </c>
+      <c r="J702" t="n">
+        <v>8</v>
+      </c>
+      <c r="K702" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L702" t="inlineStr"/>
+      <c r="M702" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N702" s="2" t="n">
+        <v>46118</v>
+      </c>
+      <c r="O702" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P702" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q702" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R702" t="inlineStr">
+        <is>
+          <t>Ingeniería de sistemas, telemática y afines</t>
+        </is>
+      </c>
+      <c r="S702" t="inlineStr"/>
+      <c r="T702" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U702" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+      <c r="V702" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F703" t="n">
+        <v>119026</v>
+      </c>
+      <c r="G703" t="inlineStr">
+        <is>
+          <t>CONTADURÍA PUBLICA</t>
+        </is>
+      </c>
+      <c r="H703" t="inlineStr">
+        <is>
+          <t>A distancia</t>
+        </is>
+      </c>
+      <c r="I703" t="n">
+        <v>140</v>
+      </c>
+      <c r="J703" t="n">
+        <v>8</v>
+      </c>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L703" t="inlineStr"/>
+      <c r="M703" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N703" s="2" t="n">
+        <v>45796</v>
+      </c>
+      <c r="O703" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P703" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q703" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R703" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S703" t="inlineStr"/>
+      <c r="T703" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U703" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V703" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>9119</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr">
+        <is>
+          <t>CORPORACION UNIVERSITARIA AMERICANA</t>
+        </is>
+      </c>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F704" t="n">
+        <v>119027</v>
+      </c>
+      <c r="G704" t="inlineStr">
+        <is>
+          <t>CONTADURÍA PUBLICA</t>
+        </is>
+      </c>
+      <c r="H704" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I704" t="n">
+        <v>140</v>
+      </c>
+      <c r="J704" t="n">
+        <v>8</v>
+      </c>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L704" t="inlineStr"/>
+      <c r="M704" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N704" s="2" t="n">
+        <v>45796</v>
+      </c>
+      <c r="O704" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P704" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q704" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R704" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S704" t="inlineStr"/>
+      <c r="T704" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U704" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V704" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>9906</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN UNIVERSITARIA PARA EL DESARROLLO EMPRESARIAL Y SOCIAL - MISIÓN PAZ.</t>
+        </is>
+      </c>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F705" t="n">
+        <v>119084</v>
+      </c>
+      <c r="G705" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN DE EMPRESAS</t>
+        </is>
+      </c>
+      <c r="H705" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I705" t="n">
+        <v>144</v>
+      </c>
+      <c r="J705" t="n">
+        <v>8</v>
+      </c>
+      <c r="K705" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L705" t="inlineStr"/>
+      <c r="M705" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N705" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O705" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P705" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="Q705" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a administración de empresas y derecho</t>
+        </is>
+      </c>
+      <c r="R705" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S705" t="inlineStr"/>
+      <c r="T705" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U705" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+      <c r="V705" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>9906</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr">
+        <is>
+          <t>CORPORACIÓN UNIVERSITARIA PARA EL DESARROLLO EMPRESARIAL Y SOCIAL - MISIÓN PAZ.</t>
+        </is>
+      </c>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F706" t="n">
+        <v>119083</v>
+      </c>
+      <c r="G706" t="inlineStr">
+        <is>
+          <t>COMUNICACIÓN SOCIAL</t>
+        </is>
+      </c>
+      <c r="H706" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I706" t="n">
+        <v>144</v>
+      </c>
+      <c r="J706" t="n">
+        <v>8</v>
+      </c>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L706" t="inlineStr"/>
+      <c r="M706" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N706" s="2" t="n">
+        <v>46119</v>
+      </c>
+      <c r="O706" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P706" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q706" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R706" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="S706" t="inlineStr"/>
+      <c r="T706" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U706" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+      <c r="V706" t="inlineStr">
+        <is>
+          <t>Activo</t>
+        </is>
+      </c>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>9939</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr">
+        <is>
+          <t>FUNDACIÓN UNIVERSITARIA CATÓLICA DEL CARIBE</t>
+        </is>
+      </c>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F707" t="n">
+        <v>119029</v>
+      </c>
+      <c r="G707" t="inlineStr">
+        <is>
+          <t>ADMINISTRACIÓN EN SEGURIDAD Y SALUD EN EL TRABAJO</t>
+        </is>
+      </c>
+      <c r="H707" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I707" t="n">
+        <v>143</v>
+      </c>
+      <c r="J707" t="n">
+        <v>9</v>
+      </c>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L707" t="inlineStr"/>
+      <c r="M707" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N707" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="O707" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P707" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q707" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R707" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S707" t="inlineStr"/>
+      <c r="T707" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="U707" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+      <c r="V707" t="inlineStr">
         <is>
           <t>Activo</t>
         </is>
